--- a/data/exports/王颖瑜伽/dist_order_2026-10-30.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-10-30.xlsx
@@ -125,16 +125,16 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="0">
-        <v>51489339</v>
+        <v>52336900</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>春天来了</t>
+          <t>瀚海</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
+          <t>5天 新中老年生活英语营</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
@@ -144,17 +144,17 @@
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:18</t>
+          <t>2026-10-30 14:09:56</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -164,12 +164,12 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>彩虹-抖音1元瑜伽</t>
+          <t>Leon老师-抖音0元</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+          <t>WY-0元英语-微信内外落地页添加</t>
         </is>
       </c>
       <c r="K2" s="0" t="inlineStr">
@@ -180,21 +180,16 @@
       <c r="L2" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>4500000483202610107774759911</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="0">
-        <v>51489338</v>
+        <v>51489339</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>兰梅布艺</t>
+          <t>春天来了</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -219,7 +214,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:16</t>
+          <t>2026-10-10 19:47:18</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -249,17 +244,17 @@
       </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
-          <t>4500000481202610106676039209</t>
+          <t>4500000483202610107774759911</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="0">
-        <v>51489335</v>
+        <v>51489338</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>严伏秀</t>
+          <t>兰梅布艺</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -284,7 +279,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:19</t>
+          <t>2026-10-10 19:47:16</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -314,17 +309,17 @@
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
-          <t>4500000441202610104072684488</t>
+          <t>4500000481202610106676039209</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="0">
-        <v>51489332</v>
+        <v>51489335</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>圣美（罗）</t>
+          <t>严伏秀</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -349,7 +344,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:13</t>
+          <t>2026-10-10 19:47:19</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -379,17 +374,17 @@
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
-          <t>4500000439202610103437371955</t>
+          <t>4500000441202610104072684488</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="0">
-        <v>51333559</v>
+        <v>51489332</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>锦瑟流年</t>
+          <t>圣美（罗）</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -414,7 +409,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:13:07</t>
+          <t>2026-10-10 19:47:13</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -444,17 +439,17 @@
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
-          <t>4500000485202610069745624716</t>
+          <t>4500000439202610103437371955</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="0">
-        <v>51333506</v>
+        <v>51333559</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>桐泽</t>
+          <t>锦瑟流年</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -479,7 +474,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:11:49</t>
+          <t>2026-10-06 20:13:07</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -509,17 +504,17 @@
       </c>
       <c r="M7" s="0" t="inlineStr">
         <is>
-          <t>4500000492202610066600573090</t>
+          <t>4500000485202610069745624716</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="0">
-        <v>51333309</v>
+        <v>51333506</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>家乡的美</t>
+          <t>桐泽</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -544,7 +539,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:02:55</t>
+          <t>2026-10-06 20:11:49</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -574,17 +569,17 @@
       </c>
       <c r="M8" s="0" t="inlineStr">
         <is>
-          <t>4500000447202610065339769930</t>
+          <t>4500000492202610066600573090</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="0">
-        <v>51333299</v>
+        <v>51333309</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>老张</t>
+          <t>家乡的美</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -609,7 +604,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:02:41</t>
+          <t>2026-10-06 20:02:55</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -639,17 +634,17 @@
       </c>
       <c r="M9" s="0" t="inlineStr">
         <is>
-          <t>4500000477202610062734500506</t>
+          <t>4500000447202610065339769930</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="0">
-        <v>51333244</v>
+        <v>51333299</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>🥀এ᭄半颗糖ꦿ甜💔到伤ོ࿐ᩚ</t>
+          <t>老张</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -674,7 +669,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:00:22</t>
+          <t>2026-10-06 20:02:41</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -704,17 +699,17 @@
       </c>
       <c r="M10" s="0" t="inlineStr">
         <is>
-          <t>4500000457202610067152483447</t>
+          <t>4500000477202610062734500506</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="0">
-        <v>51333104</v>
+        <v>51333244</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>退休刘大哥</t>
+          <t>🥀এ᭄半颗糖ꦿ甜💔到伤ོ࿐ᩚ</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -739,7 +734,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:55:33</t>
+          <t>2026-10-06 20:00:22</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -769,17 +764,17 @@
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
-          <t>4500000454202610064881956893</t>
+          <t>4500000457202610067152483447</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="0">
-        <v>51333035</v>
+        <v>51333104</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>楊秀淑</t>
+          <t>退休刘大哥</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -804,7 +799,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:55:34</t>
+          <t>2026-10-06 19:55:33</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -834,17 +829,17 @@
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>4500000487202610062154380210</t>
+          <t>4500000454202610064881956893</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="0">
-        <v>51333012</v>
+        <v>51333035</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>爱美家家纺13478223890</t>
+          <t>楊秀淑</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -869,7 +864,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:53:01</t>
+          <t>2026-10-06 19:55:34</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -899,17 +894,17 @@
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
-          <t>4500000494202610066145995028</t>
+          <t>4500000487202610062154380210</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="0">
-        <v>51222028</v>
+        <v>51333012</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>小红</t>
+          <t>爱美家家纺13478223890</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -934,7 +929,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 20:08:14</t>
+          <t>2026-10-06 19:53:01</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -964,17 +959,17 @@
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>
-          <t>4500000467202610027273134898</t>
+          <t>4500000494202610066145995028</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="0">
-        <v>51221659</v>
+        <v>51222028</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>我只在乎你</t>
+          <t>小红</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:54:01</t>
+          <t>2026-10-02 20:08:14</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -1029,17 +1024,17 @@
       </c>
       <c r="M15" s="0" t="inlineStr">
         <is>
-          <t>4500000426202610025434647362</t>
+          <t>4500000467202610027273134898</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="0">
-        <v>51221634</v>
+        <v>51221659</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>米奶（葛）</t>
+          <t>我只在乎你</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -1064,7 +1059,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:19</t>
+          <t>2026-10-02 19:54:01</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1094,17 +1089,17 @@
       </c>
       <c r="M16" s="0" t="inlineStr">
         <is>
-          <t>4500000429202610023247688151</t>
+          <t>4500000426202610025434647362</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="0">
-        <v>51221626</v>
+        <v>51221634</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>健康是福</t>
+          <t>米奶（葛）</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1129,7 +1124,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:07</t>
+          <t>2026-10-02 19:52:19</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -1159,17 +1154,17 @@
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
-          <t>4500000478202610025848412155</t>
+          <t>4500000429202610023247688151</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="0">
-        <v>51221623</v>
+        <v>51221626</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>风中雨荷</t>
+          <t>健康是福</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -1194,7 +1189,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:49</t>
+          <t>2026-10-02 19:52:07</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -1224,17 +1219,17 @@
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
-          <t>4500000485202610022211801630</t>
+          <t>4500000478202610025848412155</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="0">
-        <v>51221622</v>
+        <v>51221623</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>小双子</t>
+          <t>风中雨荷</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -1259,7 +1254,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:53:38</t>
+          <t>2026-10-02 19:51:49</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -1289,17 +1284,17 @@
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>
-          <t>4500000430202610026316335585</t>
+          <t>4500000485202610022211801630</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="0">
-        <v>51221617</v>
+        <v>51221622</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>A英子</t>
+          <t>小双子</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -1324,7 +1319,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:03</t>
+          <t>2026-10-02 19:53:38</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1354,17 +1349,17 @@
       </c>
       <c r="M20" s="0" t="inlineStr">
         <is>
-          <t>4500000455202610022662444307</t>
+          <t>4500000430202610026316335585</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="0">
-        <v>51221616</v>
+        <v>51221617</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>阿庆</t>
+          <t>A英子</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -1389,7 +1384,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:43</t>
+          <t>2026-10-02 19:52:03</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1419,17 +1414,17 @@
       </c>
       <c r="M21" s="0" t="inlineStr">
         <is>
-          <t>4500000479202610025538878979</t>
+          <t>4500000455202610022662444307</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="0">
-        <v>51221615</v>
+        <v>51221616</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>然然</t>
+          <t>阿庆</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -1454,7 +1449,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:16</t>
+          <t>2026-10-02 19:51:43</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1484,17 +1479,17 @@
       </c>
       <c r="M22" s="0" t="inlineStr">
         <is>
-          <t>4500000458202610029251790963</t>
+          <t>4500000479202610025538878979</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="0">
-        <v>51221614</v>
+        <v>51221615</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>睦然</t>
+          <t>然然</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -1519,7 +1514,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:55</t>
+          <t>2026-10-02 19:52:16</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1549,17 +1544,17 @@
       </c>
       <c r="M23" s="0" t="inlineStr">
         <is>
-          <t>4500000481202610022649420793</t>
+          <t>4500000458202610029251790963</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="0">
-        <v>51221605</v>
+        <v>51221614</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>程方英13475802198</t>
+          <t>睦然</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1584,7 +1579,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:29</t>
+          <t>2026-10-02 19:51:55</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1614,22 +1609,17 @@
       </c>
       <c r="M24" s="0" t="inlineStr">
         <is>
-          <t>4500000427202610028110811278</t>
-        </is>
-      </c>
-      <c r="N24" s="0" t="inlineStr">
-        <is>
-          <t>青岛</t>
+          <t>4500000481202610022649420793</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="0">
-        <v>49457201</v>
+        <v>51221605</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>紫烨</t>
+          <t>程方英13475802198</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1654,7 +1644,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:24:21</t>
+          <t>2026-10-02 19:51:29</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1684,17 +1674,22 @@
       </c>
       <c r="M25" s="0" t="inlineStr">
         <is>
-          <t>4500000366202608212918307979</t>
+          <t>4500000427202610028110811278</t>
+        </is>
+      </c>
+      <c r="N25" s="0" t="inlineStr">
+        <is>
+          <t>青岛</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="0">
-        <v>49456963</v>
+        <v>49457201</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>月光宝盒🌺</t>
+          <t>紫烨</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1719,7 +1714,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:04:11</t>
+          <t>2026-08-21 00:24:21</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1749,17 +1744,17 @@
       </c>
       <c r="M26" s="0" t="inlineStr">
         <is>
-          <t>4500000370202608212773595140</t>
+          <t>4500000366202608212918307979</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="0">
-        <v>49456951</v>
+        <v>49456963</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>浅浅浅蓝</t>
+          <t>月光宝盒🌺</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1784,7 +1779,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:03:09</t>
+          <t>2026-08-21 00:04:11</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1814,17 +1809,17 @@
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608218688440287</t>
+          <t>4500000370202608212773595140</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="0">
-        <v>49451062</v>
+        <v>49456951</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>美丽天使</t>
+          <t>浅浅浅蓝</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1849,7 +1844,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:04:54</t>
+          <t>2026-08-21 00:03:09</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1879,17 +1874,17 @@
       </c>
       <c r="M28" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608206032862385</t>
+          <t>4500000333202608218688440287</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="0">
-        <v>49451061</v>
+        <v>49451062</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>尹璐-专业设计各类风水画</t>
+          <t>美丽天使</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -1914,7 +1909,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:04:51</t>
+          <t>2026-08-20 21:04:54</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1944,17 +1939,17 @@
       </c>
       <c r="M29" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608202974919363</t>
+          <t>4500000383202608206032862385</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="0">
-        <v>49451049</v>
+        <v>49451061</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>曾姐</t>
+          <t>尹璐-专业设计各类风水画</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -1979,7 +1974,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:05:13</t>
+          <t>2026-08-20 21:04:51</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -2009,17 +2004,17 @@
       </c>
       <c r="M30" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608208073638505</t>
+          <t>4500000321202608202974919363</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="0">
-        <v>49380753</v>
+        <v>49451049</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>月亮</t>
+          <t>曾姐</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -2044,7 +2039,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:10</t>
+          <t>2026-08-20 21:05:13</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -2074,17 +2069,17 @@
       </c>
       <c r="M31" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608199548973720</t>
+          <t>4500000353202608208073638505</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="0">
-        <v>49380751</v>
+        <v>49380753</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>荣兰</t>
+          <t>月亮</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -2109,7 +2104,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:34</t>
+          <t>2026-08-19 00:04:10</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -2139,17 +2134,17 @@
       </c>
       <c r="M32" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608192770223988</t>
+          <t>4500000340202608199548973720</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="0">
-        <v>49380749</v>
+        <v>49380751</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>琴</t>
+          <t>荣兰</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -2174,7 +2169,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:06</t>
+          <t>2026-08-19 00:04:34</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2204,17 +2199,17 @@
       </c>
       <c r="M33" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608197088116223</t>
+          <t>4500000376202608192770223988</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="0">
-        <v>49380733</v>
+        <v>49380749</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>风水道士何金权先生18885336852</t>
+          <t>琴</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -2239,7 +2234,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:03:55</t>
+          <t>2026-08-19 00:04:06</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2269,17 +2264,17 @@
       </c>
       <c r="M34" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608197323803505</t>
+          <t>4500000365202608197088116223</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="0">
-        <v>49378805</v>
+        <v>49380733</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>心想事成</t>
+          <t>风水道士何金权先生18885336852</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -2304,7 +2299,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:36:11</t>
+          <t>2026-08-19 00:03:55</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2334,17 +2329,17 @@
       </c>
       <c r="M35" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608187136696859</t>
+          <t>4500000361202608197323803505</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="0">
-        <v>49378780</v>
+        <v>49378805</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>ZCL</t>
+          <t>心想事成</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -2369,7 +2364,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:59</t>
+          <t>2026-08-18 22:36:11</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2399,17 +2394,17 @@
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608185058515299</t>
+          <t>4500000316202608187136696859</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="0">
-        <v>49378769</v>
+        <v>49378780</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>岁月如流水</t>
+          <t>ZCL</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -2434,7 +2429,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:45</t>
+          <t>2026-08-18 22:34:59</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2464,17 +2459,17 @@
       </c>
       <c r="M37" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608182677022834</t>
+          <t>4500000316202608185058515299</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="0">
-        <v>49378768</v>
+        <v>49378769</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>天天好心情</t>
+          <t>岁月如流水</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -2499,7 +2494,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:39</t>
+          <t>2026-08-18 22:34:45</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2529,17 +2524,17 @@
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608185835240274</t>
+          <t>4500000363202608182677022834</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="0">
-        <v>49375111</v>
+        <v>49378768</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>万事大吉</t>
+          <t>天天好心情</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -2564,7 +2559,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:05:57</t>
+          <t>2026-08-18 22:34:39</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2594,17 +2589,17 @@
       </c>
       <c r="M39" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608187074952472</t>
+          <t>4500000345202608185835240274</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="0">
-        <v>49375081</v>
+        <v>49375111</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>如鱼得水</t>
+          <t>万事大吉</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -2629,7 +2624,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:04:47</t>
+          <t>2026-08-18 21:05:57</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -2659,17 +2654,17 @@
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608189110994857</t>
+          <t>4500000344202608187074952472</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="0">
-        <v>49375015</v>
+        <v>49375081</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>母爱</t>
+          <t>如鱼得水</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -2694,7 +2689,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:52</t>
+          <t>2026-08-18 21:04:47</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -2724,17 +2719,17 @@
       </c>
       <c r="M41" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608186111867199</t>
+          <t>4500000369202608189110994857</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="0">
-        <v>49375001</v>
+        <v>49375015</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>郭正平</t>
+          <t>母爱</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -2759,7 +2754,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:41</t>
+          <t>2026-08-18 21:03:52</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2789,17 +2784,17 @@
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608187695923792</t>
+          <t>4500000365202608186111867199</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="0">
-        <v>49375000</v>
+        <v>49375001</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>云    朵</t>
+          <t>郭正平</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -2824,7 +2819,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:36</t>
+          <t>2026-08-18 21:03:41</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2854,17 +2849,17 @@
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608184692846233</t>
+          <t>4500000358202608187695923792</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="0">
-        <v>49371969</v>
+        <v>49375000</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>豆棋奶奶</t>
+          <t>云    朵</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -2889,7 +2884,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:53:16</t>
+          <t>2026-08-18 21:03:36</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2919,17 +2914,17 @@
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
-          <t>4500000381202608187462400910</t>
+          <t>4500000361202608184692846233</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="0">
-        <v>49370049</v>
+        <v>49371969</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>熊金娥</t>
+          <t>豆棋奶奶</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -2954,7 +2949,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:34:52</t>
+          <t>2026-08-18 19:53:16</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2984,17 +2979,17 @@
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608186456472403</t>
+          <t>4500000381202608187462400910</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="0">
-        <v>49370024</v>
+        <v>49370049</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>宏娇18906639773</t>
+          <t>熊金娥</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -3019,7 +3014,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:34:43</t>
+          <t>2026-08-18 19:34:52</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -3049,17 +3044,17 @@
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608181915925686</t>
+          <t>4500000343202608186456472403</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="0">
-        <v>49369533</v>
+        <v>49370024</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>周周有钱</t>
+          <t>宏娇18906639773</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -3084,7 +3079,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:32</t>
+          <t>2026-08-18 19:34:43</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -3114,17 +3109,17 @@
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608183864211631</t>
+          <t>4500000356202608181915925686</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="0">
-        <v>49369376</v>
+        <v>49369533</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>王兰允</t>
+          <t>周周有钱</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -3149,7 +3144,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:40</t>
+          <t>2026-08-18 19:33:32</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -3179,17 +3174,17 @@
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
-          <t>4500000372202608185572793801</t>
+          <t>4500000324202608183864211631</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="0">
-        <v>49369344</v>
+        <v>49369376</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>陈</t>
+          <t>王兰允</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -3214,7 +3209,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:15</t>
+          <t>2026-08-18 19:33:40</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -3244,17 +3239,17 @@
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608183479278224</t>
+          <t>4500000372202608185572793801</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="0">
-        <v>49369203</v>
+        <v>49369344</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>静心</t>
+          <t>陈</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3279,7 +3274,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:32:32</t>
+          <t>2026-08-18 19:33:15</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -3309,17 +3304,17 @@
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608182953367773</t>
+          <t>4500000361202608183479278224</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="0">
-        <v>49340095</v>
+        <v>49369203</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>小小</t>
+          <t>静心</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -3344,7 +3339,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:24:20</t>
+          <t>2026-08-18 19:32:32</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -3374,17 +3369,17 @@
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608185905136033</t>
+          <t>4500000377202608182953367773</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="0">
-        <v>49340080</v>
+        <v>49340095</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>封艳丽</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -3409,7 +3404,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:22:59</t>
+          <t>2026-08-18 00:24:20</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -3439,17 +3434,17 @@
       </c>
       <c r="M52" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608183466806505</t>
+          <t>4500000339202608185905136033</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="0">
-        <v>49339950</v>
+        <v>49340080</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>家和万事兴</t>
+          <t>封艳丽</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -3474,7 +3469,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:07</t>
+          <t>2026-08-18 00:22:59</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3504,22 +3499,17 @@
       </c>
       <c r="M53" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608183266732544</t>
-        </is>
-      </c>
-      <c r="N53" s="0" t="inlineStr">
-        <is>
-          <t>亳州</t>
+          <t>4500000320202608183466806505</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="0">
-        <v>49339947</v>
+        <v>49339950</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>温玉明</t>
+          <t>家和万事兴</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -3544,7 +3534,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:58</t>
+          <t>2026-08-18 00:04:07</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -3574,17 +3564,22 @@
       </c>
       <c r="M54" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608181657535231</t>
+          <t>4500000344202608183266732544</t>
+        </is>
+      </c>
+      <c r="N54" s="0" t="inlineStr">
+        <is>
+          <t>亳州</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="0">
-        <v>49339943</v>
+        <v>49339947</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>春梅</t>
+          <t>温玉明</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -3609,7 +3604,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:49</t>
+          <t>2026-08-18 00:04:58</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -3639,17 +3634,17 @@
       </c>
       <c r="M55" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608182239214659</t>
+          <t>4500000357202608181657535231</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="0">
-        <v>49339939</v>
+        <v>49339943</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>青青</t>
+          <t>春梅</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -3674,7 +3669,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:44</t>
+          <t>2026-08-18 00:03:49</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -3704,17 +3699,17 @@
       </c>
       <c r="M56" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608185247886970</t>
+          <t>4500000342202608182239214659</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="0">
-        <v>49339937</v>
+        <v>49339939</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>开心向日葵🌻</t>
+          <t>青青</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -3739,7 +3734,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:40</t>
+          <t>2026-08-18 00:03:44</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -3769,17 +3764,17 @@
       </c>
       <c r="M57" s="0" t="inlineStr">
         <is>
-          <t>4500000319202608184846762524</t>
+          <t>4500000355202608185247886970</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="0">
-        <v>49339936</v>
+        <v>49339937</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>彩之缘</t>
+          <t>开心向日葵🌻</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -3804,7 +3799,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:39</t>
+          <t>2026-08-18 00:03:40</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3834,17 +3829,17 @@
       </c>
       <c r="M58" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608186999829929</t>
+          <t>4500000319202608184846762524</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="0">
-        <v>49339931</v>
+        <v>49339936</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>彩之缘</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -3869,7 +3864,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:24</t>
+          <t>2026-08-18 00:03:39</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -3899,17 +3894,17 @@
       </c>
       <c r="M59" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608186968757749</t>
+          <t>4500000342202608186999829929</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="0">
-        <v>49339929</v>
+        <v>49339931</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>段桂富</t>
+          <t>my</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -3934,7 +3929,7 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:06</t>
+          <t>2026-08-18 00:03:24</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -3964,17 +3959,17 @@
       </c>
       <c r="M60" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608189428147476</t>
+          <t>4500000383202608186968757749</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="0">
-        <v>49339923</v>
+        <v>49339929</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>蓝天</t>
+          <t>段桂富</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -3999,7 +3994,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:07</t>
+          <t>2026-08-18 00:04:06</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -4029,17 +4024,17 @@
       </c>
       <c r="M61" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608189060114184</t>
+          <t>4500000349202608189428147476</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="0">
-        <v>49339921</v>
+        <v>49339923</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>陌上花开</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -4064,7 +4059,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:59</t>
+          <t>2026-08-18 00:03:07</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -4094,17 +4089,17 @@
       </c>
       <c r="M62" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608185881858135</t>
+          <t>4500000346202608189060114184</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="0">
-        <v>49339920</v>
+        <v>49339921</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>A红雨伞玲雪养发馆</t>
+          <t>陌上花开</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -4129,7 +4124,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:03</t>
+          <t>2026-08-18 00:03:59</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -4159,17 +4154,17 @@
       </c>
       <c r="M63" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608181810150616</t>
+          <t>4500000353202608185881858135</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="0">
-        <v>49339918</v>
+        <v>49339920</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>胡璎桉</t>
+          <t>A红雨伞玲雪养发馆</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -4194,7 +4189,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:05:04</t>
+          <t>2026-08-18 00:03:03</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -4224,17 +4219,17 @@
       </c>
       <c r="M64" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608188854566939</t>
+          <t>4500000344202608181810150616</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="0">
-        <v>49337893</v>
+        <v>49339918</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>郑洁玲</t>
+          <t>胡璎桉</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -4259,7 +4254,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:36:14</t>
+          <t>2026-08-18 00:05:04</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -4289,17 +4284,17 @@
       </c>
       <c r="M65" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608171736033078</t>
+          <t>4500000354202608188854566939</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="0">
-        <v>49337886</v>
+        <v>49337893</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>浪漫樱花</t>
+          <t>郑洁玲</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -4324,7 +4319,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:44</t>
+          <t>2026-08-17 22:36:14</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4354,17 +4349,17 @@
       </c>
       <c r="M66" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176588884719</t>
+          <t>4500000340202608171736033078</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="0">
-        <v>49337882</v>
+        <v>49337886</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>王仲槐</t>
+          <t>浪漫樱花</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -4389,7 +4384,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:25</t>
+          <t>2026-08-17 22:35:44</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4419,17 +4414,17 @@
       </c>
       <c r="M67" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608171381637652</t>
+          <t>4500000362202608176588884719</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="0">
-        <v>49337868</v>
+        <v>49337882</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>黄建17373719413</t>
+          <t>王仲槐</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -4454,7 +4449,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:03</t>
+          <t>2026-08-17 22:35:25</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -4484,17 +4479,17 @@
       </c>
       <c r="M68" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608175713808624</t>
+          <t>4500000339202608171381637652</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="0">
-        <v>49337865</v>
+        <v>49337868</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>晓燕</t>
+          <t>黄建17373719413</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -4519,7 +4514,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:01</t>
+          <t>2026-08-17 22:35:03</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -4549,17 +4544,17 @@
       </c>
       <c r="M69" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608175538967169</t>
+          <t>4500000357202608175713808624</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="0">
-        <v>49337857</v>
+        <v>49337865</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>真心真意</t>
+          <t>晓燕</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -4584,7 +4579,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:34:43</t>
+          <t>2026-08-17 22:35:01</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -4614,17 +4609,17 @@
       </c>
       <c r="M70" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176387457203</t>
+          <t>4500000380202608175538967169</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="0">
-        <v>49334810</v>
+        <v>49337857</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>candy🧬甘💕</t>
+          <t>真心真意</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -4649,7 +4644,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:25:31</t>
+          <t>2026-08-17 22:34:43</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -4679,17 +4674,17 @@
       </c>
       <c r="M71" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608173665178011</t>
+          <t>4500000362202608176387457203</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="0">
-        <v>49334746</v>
+        <v>49334810</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>雨落弦音</t>
+          <t>candy🧬甘💕</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -4714,7 +4709,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:24:18</t>
+          <t>2026-08-17 21:25:31</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -4744,17 +4739,17 @@
       </c>
       <c r="M72" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608175925050310</t>
+          <t>4500000379202608173665178011</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="0">
-        <v>49334683</v>
+        <v>49334746</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>🌹六福A413🌹</t>
+          <t>雨落弦音</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -4779,7 +4774,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:23:16</t>
+          <t>2026-08-17 21:24:18</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -4809,17 +4804,17 @@
       </c>
       <c r="M73" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608175320562123</t>
+          <t>4500000324202608175925050310</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="0">
-        <v>49333672</v>
+        <v>49334683</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>☀️知足常乐😊</t>
+          <t>🌹六福A413🌹</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -4844,7 +4839,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:44</t>
+          <t>2026-08-17 21:23:16</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -4874,17 +4869,17 @@
       </c>
       <c r="M74" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608178190501918</t>
+          <t>4500000337202608175320562123</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="0">
-        <v>49333665</v>
+        <v>49333672</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>在水一方</t>
+          <t>☀️知足常乐😊</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -4909,7 +4904,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:41</t>
+          <t>2026-08-17 21:01:44</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -4939,17 +4934,17 @@
       </c>
       <c r="M75" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608175675285016</t>
+          <t>4500000380202608178190501918</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="0">
-        <v>49333658</v>
+        <v>49333665</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>牛牛</t>
+          <t>在水一方</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -4974,7 +4969,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:31</t>
+          <t>2026-08-17 21:01:41</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -5004,17 +4999,17 @@
       </c>
       <c r="M76" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608171889470116</t>
+          <t>4500000333202608175675285016</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="0">
-        <v>49333657</v>
+        <v>49333658</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>鲍镇定</t>
+          <t>牛牛</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -5039,7 +5034,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:38</t>
+          <t>2026-08-17 21:01:31</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -5069,17 +5064,17 @@
       </c>
       <c r="M77" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608179201028350</t>
+          <t>4500000380202608171889470116</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="0">
-        <v>49333649</v>
+        <v>49333657</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>:-D开心果O:-)</t>
+          <t>鲍镇定</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -5104,7 +5099,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:27</t>
+          <t>2026-08-17 21:01:38</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -5134,17 +5129,17 @@
       </c>
       <c r="M78" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608172428227717</t>
+          <t>4500000321202608179201028350</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="0">
-        <v>49333640</v>
+        <v>49333649</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>黛黛</t>
+          <t>:-D开心果O:-)</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -5169,7 +5164,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:30</t>
+          <t>2026-08-17 21:01:27</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -5199,17 +5194,17 @@
       </c>
       <c r="M79" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608177275411312</t>
+          <t>4500000344202608172428227717</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="0">
-        <v>49330491</v>
+        <v>49333640</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>兰花草</t>
+          <t>黛黛</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -5234,7 +5229,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:31</t>
+          <t>2026-08-17 21:01:30</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -5264,17 +5259,17 @@
       </c>
       <c r="M80" s="0" t="inlineStr">
         <is>
-          <t>4500000341202608178144232010</t>
+          <t>4500000316202608177275411312</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="0">
-        <v>49330472</v>
+        <v>49330491</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>郝杏月</t>
+          <t>兰花草</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -5299,7 +5294,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:27</t>
+          <t>2026-08-17 19:53:31</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -5329,17 +5324,17 @@
       </c>
       <c r="M81" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608176551746821</t>
+          <t>4500000341202608178144232010</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="0">
-        <v>49330471</v>
+        <v>49330472</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>金泽湖水</t>
+          <t>郝杏月</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -5364,7 +5359,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:46</t>
+          <t>2026-08-17 19:53:27</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -5394,17 +5389,17 @@
       </c>
       <c r="M82" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608175707490842</t>
+          <t>4500000337202608176551746821</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="0">
-        <v>49330470</v>
+        <v>49330471</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>乐惠</t>
+          <t>金泽湖水</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -5429,7 +5424,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:54</t>
+          <t>2026-08-17 19:52:46</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5459,17 +5454,17 @@
       </c>
       <c r="M83" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608179365238894</t>
+          <t>4500000374202608175707490842</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="0">
-        <v>49302015</v>
+        <v>49330470</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>辰悦</t>
+          <t>乐惠</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -5494,7 +5489,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:22:50</t>
+          <t>2026-08-17 19:52:54</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -5524,17 +5519,17 @@
       </c>
       <c r="M84" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608175953744348</t>
+          <t>4500000347202608179365238894</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="0">
-        <v>49301896</v>
+        <v>49302015</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>简简单单</t>
+          <t>辰悦</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -5559,7 +5554,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:05:28</t>
+          <t>2026-08-17 00:22:50</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -5589,17 +5584,17 @@
       </c>
       <c r="M85" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608175217008588</t>
+          <t>4500000368202608175953744348</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="0">
-        <v>49301861</v>
+        <v>49301896</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>小优不忘初心</t>
+          <t>简简单单</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -5624,7 +5619,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:03</t>
+          <t>2026-08-17 00:05:28</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -5654,17 +5649,17 @@
       </c>
       <c r="M86" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608176836637946</t>
+          <t>4500000353202608175217008588</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="0">
-        <v>49301860</v>
+        <v>49301861</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>半夏轻浅</t>
+          <t>小优不忘初心</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -5689,7 +5684,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:08</t>
+          <t>2026-08-17 00:04:03</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -5719,17 +5714,17 @@
       </c>
       <c r="M87" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608175019525500</t>
+          <t>4500000330202608176836637946</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="0">
-        <v>49301859</v>
+        <v>49301860</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>小璇一（龙树门业</t>
+          <t>半夏轻浅</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -5754,7 +5749,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:52</t>
+          <t>2026-08-17 00:04:08</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -5784,17 +5779,17 @@
       </c>
       <c r="M88" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608177884628709</t>
+          <t>4500000338202608175019525500</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="0">
-        <v>49301854</v>
+        <v>49301859</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
+          <t>小璇一（龙树门业</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -5819,7 +5814,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:00</t>
+          <t>2026-08-17 00:03:52</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -5849,17 +5844,17 @@
       </c>
       <c r="M89" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608177813577730</t>
+          <t>4500000347202608177884628709</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="0">
-        <v>49301853</v>
+        <v>49301854</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>祥云母婴春姐</t>
+          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -5884,7 +5879,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:49</t>
+          <t>2026-08-17 00:04:00</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -5914,17 +5909,17 @@
       </c>
       <c r="M90" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608178418886316</t>
+          <t>4500000352202608177813577730</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="0">
-        <v>49301852</v>
+        <v>49301853</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>白迎春</t>
+          <t>祥云母婴春姐</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -5949,7 +5944,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:46</t>
+          <t>2026-08-17 00:03:49</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -5979,17 +5974,17 @@
       </c>
       <c r="M91" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608174681213879</t>
+          <t>4500000337202608178418886316</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="0">
-        <v>49301850</v>
+        <v>49301852</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>人心易冷</t>
+          <t>白迎春</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -6014,7 +6009,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:04</t>
+          <t>2026-08-17 00:03:46</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -6044,17 +6039,17 @@
       </c>
       <c r="M92" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608172769831285</t>
+          <t>4500000377202608174681213879</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="0">
-        <v>49301846</v>
+        <v>49301850</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>心静自然凉</t>
+          <t>人心易冷</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -6079,7 +6074,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:51</t>
+          <t>2026-08-17 00:04:04</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -6109,17 +6104,17 @@
       </c>
       <c r="M93" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608177412373514</t>
+          <t>4500000349202608172769831285</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="0">
-        <v>49301843</v>
+        <v>49301846</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
+          <t>心静自然凉</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -6144,7 +6139,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:40</t>
+          <t>2026-08-17 00:03:51</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -6174,17 +6169,17 @@
       </c>
       <c r="M94" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608176220568550</t>
+          <t>4500000354202608177412373514</t>
         </is>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="0">
-        <v>49300670</v>
+        <v>49301843</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>看透人心，</t>
+          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -6209,7 +6204,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:07</t>
+          <t>2026-08-17 00:03:40</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -6239,17 +6234,17 @@
       </c>
       <c r="M95" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608165434325764</t>
+          <t>4500000320202608176220568550</t>
         </is>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="0">
-        <v>49300667</v>
+        <v>49300670</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>童心依旧</t>
+          <t>看透人心，</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -6274,7 +6269,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:03</t>
+          <t>2026-08-16 22:56:07</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -6304,17 +6299,17 @@
       </c>
       <c r="M96" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608161482824495</t>
+          <t>4500000365202608165434325764</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="0">
-        <v>49300135</v>
+        <v>49300667</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>秋韵</t>
+          <t>童心依旧</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -6339,7 +6334,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:34</t>
+          <t>2026-08-16 22:56:03</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -6369,17 +6364,17 @@
       </c>
       <c r="M97" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608167344457159</t>
+          <t>4500000369202608161482824495</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="0">
-        <v>49300112</v>
+        <v>49300135</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>平安福贵</t>
+          <t>秋韵</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -6404,7 +6399,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:27</t>
+          <t>2026-08-16 22:36:34</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -6434,17 +6429,17 @@
       </c>
       <c r="M98" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608162072183782</t>
+          <t>4500000322202608167344457159</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="0">
-        <v>49300100</v>
+        <v>49300112</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>萱奶奶</t>
+          <t>平安福贵</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -6469,7 +6464,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:45</t>
+          <t>2026-08-16 22:36:27</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -6499,17 +6494,17 @@
       </c>
       <c r="M99" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608164279026924</t>
+          <t>4500000329202608162072183782</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="0">
-        <v>49300096</v>
+        <v>49300100</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>泓涧（红健）</t>
+          <t>萱奶奶</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -6534,7 +6529,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:31</t>
+          <t>2026-08-16 22:35:45</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -6564,17 +6559,17 @@
       </c>
       <c r="M100" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608161591115326</t>
+          <t>4500000345202608164279026924</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="0">
-        <v>49300095</v>
+        <v>49300096</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>风行云🏇</t>
+          <t>泓涧（红健）</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -6599,7 +6594,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:13</t>
+          <t>2026-08-16 22:35:31</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -6629,17 +6624,17 @@
       </c>
       <c r="M101" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608165318502823</t>
+          <t>4500000324202608161591115326</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="0">
-        <v>49300083</v>
+        <v>49300095</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>才秀</t>
+          <t>风行云🏇</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -6664,7 +6659,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:11</t>
+          <t>2026-08-16 22:36:13</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -6694,22 +6689,17 @@
       </c>
       <c r="M102" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608161669406907</t>
-        </is>
-      </c>
-      <c r="N102" s="0" t="inlineStr">
-        <is>
-          <t>奉贤</t>
+          <t>4500000358202608165318502823</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="0">
-        <v>49300055</v>
+        <v>49300083</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>冰心</t>
+          <t>才秀</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -6734,7 +6724,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:49</t>
+          <t>2026-08-16 22:35:11</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -6764,17 +6754,22 @@
       </c>
       <c r="M103" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608167949730522</t>
+          <t>4500000330202608161669406907</t>
+        </is>
+      </c>
+      <c r="N103" s="0" t="inlineStr">
+        <is>
+          <t>奉贤</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="0">
-        <v>49300045</v>
+        <v>49300055</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>冰心</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -6799,7 +6794,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:20</t>
+          <t>2026-08-16 22:34:49</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -6829,22 +6824,17 @@
       </c>
       <c r="M104" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608162476754389</t>
-        </is>
-      </c>
-      <c r="N104" s="0" t="inlineStr">
-        <is>
-          <t>荆州</t>
+          <t>4500000317202608167949730522</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="0">
-        <v>49300042</v>
+        <v>49300045</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>赵萍</t>
+          <t>平</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -6869,7 +6859,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:13</t>
+          <t>2026-08-16 22:34:20</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -6899,17 +6889,22 @@
       </c>
       <c r="M105" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608168494549151</t>
+          <t>4500000353202608162476754389</t>
+        </is>
+      </c>
+      <c r="N105" s="0" t="inlineStr">
+        <is>
+          <t>荆州</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="0">
-        <v>49300034</v>
+        <v>49300042</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>刘华</t>
+          <t>赵萍</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -6934,7 +6929,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:07</t>
+          <t>2026-08-16 22:34:13</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -6964,17 +6959,17 @@
       </c>
       <c r="M106" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608165458621611</t>
+          <t>4500000346202608168494549151</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="0">
-        <v>49297749</v>
+        <v>49300034</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>沈雨凤</t>
+          <t>刘华</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -6999,7 +6994,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:24</t>
+          <t>2026-08-16 22:35:07</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -7029,17 +7024,17 @@
       </c>
       <c r="M107" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608164415130639</t>
+          <t>4500000333202608165458621611</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="0">
-        <v>49297736</v>
+        <v>49297749</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>莉莉</t>
+          <t>沈雨凤</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -7064,7 +7059,7 @@
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:09</t>
+          <t>2026-08-16 21:27:24</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -7094,17 +7089,17 @@
       </c>
       <c r="M108" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163428098661</t>
+          <t>4500000375202608164415130639</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="0">
-        <v>49297681</v>
+        <v>49297736</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>一生平安</t>
+          <t>莉莉</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -7129,7 +7124,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:46</t>
+          <t>2026-08-16 21:27:09</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -7159,17 +7154,17 @@
       </c>
       <c r="M109" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608163491096965</t>
+          <t>4500000369202608163428098661</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="0">
-        <v>49297679</v>
+        <v>49297681</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>孔平</t>
+          <t>一生平安</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -7194,7 +7189,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:57</t>
+          <t>2026-08-16 21:25:46</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -7224,17 +7219,17 @@
       </c>
       <c r="M110" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608165709204884</t>
+          <t>4500000368202608163491096965</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="0">
-        <v>49296893</v>
+        <v>49297679</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>逍遥仙子</t>
+          <t>孔平</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -7259,7 +7254,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:30</t>
+          <t>2026-08-16 21:25:57</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -7289,17 +7284,17 @@
       </c>
       <c r="M111" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608167690459739</t>
+          <t>4500000367202608165709204884</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="0">
-        <v>49296884</v>
+        <v>49296893</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>丽红</t>
+          <t>逍遥仙子</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -7324,7 +7319,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:16</t>
+          <t>2026-08-16 21:04:30</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -7354,17 +7349,17 @@
       </c>
       <c r="M112" s="0" t="inlineStr">
         <is>
-          <t>4500000332202608162032983613</t>
+          <t>4500000316202608167690459739</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="0">
-        <v>49296874</v>
+        <v>49296884</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>海  角</t>
+          <t>丽红</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -7389,7 +7384,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:57</t>
+          <t>2026-08-16 21:04:16</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -7419,17 +7414,17 @@
       </c>
       <c r="M113" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163623487097</t>
+          <t>4500000332202608162032983613</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="0">
-        <v>49296864</v>
+        <v>49296874</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>曹景玉</t>
+          <t>海  角</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -7454,7 +7449,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:45</t>
+          <t>2026-08-16 21:03:57</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -7484,17 +7479,17 @@
       </c>
       <c r="M114" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608163779658463</t>
+          <t>4500000369202608163623487097</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="0">
-        <v>49296863</v>
+        <v>49296864</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>石陆萍</t>
+          <t>曹景玉</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -7519,7 +7514,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:13</t>
+          <t>2026-08-16 21:03:45</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -7549,17 +7544,17 @@
       </c>
       <c r="M115" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608161473678444</t>
+          <t>4500000331202608163779658463</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="0">
-        <v>49296849</v>
+        <v>49296863</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>阿荣</t>
+          <t>石陆萍</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -7584,7 +7579,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:43</t>
+          <t>2026-08-16 21:04:13</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -7614,17 +7609,17 @@
       </c>
       <c r="M116" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608169868333535</t>
+          <t>4500000351202608161473678444</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="0">
-        <v>49296823</v>
+        <v>49296849</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>周少丽</t>
+          <t>阿荣</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -7649,7 +7644,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:17</t>
+          <t>2026-08-16 21:03:43</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -7679,17 +7674,17 @@
       </c>
       <c r="M117" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608169179019788</t>
+          <t>4500000318202608169868333535</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="0">
-        <v>49296822</v>
+        <v>49296823</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>雨花石</t>
+          <t>周少丽</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -7714,7 +7709,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:16</t>
+          <t>2026-08-16 21:03:17</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -7744,17 +7739,17 @@
       </c>
       <c r="M118" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608166345332381</t>
+          <t>4500000315202608169179019788</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="0">
-        <v>49293860</v>
+        <v>49296822</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>树玲</t>
+          <t>雨花石</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -7779,7 +7774,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:26</t>
+          <t>2026-08-16 21:03:16</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -7809,17 +7804,17 @@
       </c>
       <c r="M119" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608168589310428</t>
+          <t>4500000367202608166345332381</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="0">
-        <v>49293858</v>
+        <v>49293860</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>芬芳</t>
+          <t>树玲</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -7844,7 +7839,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:42</t>
+          <t>2026-08-16 19:55:26</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -7874,17 +7869,17 @@
       </c>
       <c r="M120" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608162910375128</t>
+          <t>4500000342202608168589310428</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="0">
-        <v>49197594</v>
+        <v>49293858</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>李秀燕健康顾问</t>
+          <t>芬芳</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -7909,7 +7904,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:55</t>
+          <t>2026-08-16 19:55:42</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -7939,17 +7934,17 @@
       </c>
       <c r="M121" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608135550322726</t>
+          <t>4500000358202608162910375128</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="0">
-        <v>49197555</v>
+        <v>49197594</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>FXH*</t>
+          <t>李秀燕健康顾问</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -7974,7 +7969,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:10</t>
+          <t>2026-08-13 21:55:55</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -8004,17 +7999,17 @@
       </c>
       <c r="M122" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608139667116905</t>
+          <t>4500000383202608135550322726</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="0">
-        <v>49197551</v>
+        <v>49197555</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>书英</t>
+          <t>FXH*</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -8039,7 +8034,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:09</t>
+          <t>2026-08-13 21:55:10</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
@@ -8069,17 +8064,17 @@
       </c>
       <c r="M123" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608135183726220</t>
+          <t>4500000376202608139667116905</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="0">
-        <v>49197500</v>
+        <v>49197551</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>求智慧</t>
+          <t>书英</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
@@ -8104,7 +8099,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:54:20</t>
+          <t>2026-08-13 21:55:09</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -8134,17 +8129,17 @@
       </c>
       <c r="M124" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608136477567012</t>
+          <t>4500000363202608135183726220</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="0">
-        <v>49196660</v>
+        <v>49197500</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>陈书先</t>
+          <t>求智慧</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -8169,7 +8164,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:55</t>
+          <t>2026-08-13 21:54:20</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -8199,17 +8194,17 @@
       </c>
       <c r="M125" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608137513582005</t>
+          <t>4500000356202608136477567012</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="0">
-        <v>49196649</v>
+        <v>49196660</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>chenchen</t>
+          <t>陈书先</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -8234,7 +8229,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:37</t>
+          <t>2026-08-13 21:35:55</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -8264,17 +8259,17 @@
       </c>
       <c r="M126" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608131193472561</t>
+          <t>4500000362202608137513582005</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="0">
-        <v>49196616</v>
+        <v>49196649</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>因子</t>
+          <t>chenchen</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
@@ -8299,7 +8294,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:34</t>
+          <t>2026-08-13 21:35:37</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -8329,17 +8324,17 @@
       </c>
       <c r="M127" s="0" t="inlineStr">
         <is>
-          <t>4500000381202608131084069069</t>
+          <t>4500000360202608131193472561</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="0">
-        <v>49196580</v>
+        <v>49196616</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>包容</t>
+          <t>因子</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -8364,7 +8359,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:49</t>
+          <t>2026-08-13 21:35:34</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -8394,17 +8389,17 @@
       </c>
       <c r="M128" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608134515206220</t>
+          <t>4500000381202608131084069069</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="0">
-        <v>49196556</v>
+        <v>49196580</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>小芳</t>
+          <t>包容</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -8429,7 +8424,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:00</t>
+          <t>2026-08-13 21:34:49</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -8459,17 +8454,17 @@
       </c>
       <c r="M129" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608131586040016</t>
+          <t>4500000329202608134515206220</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="0">
-        <v>49196547</v>
+        <v>49196556</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>雷宁</t>
+          <t>小芳</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -8494,7 +8489,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:30</t>
+          <t>2026-08-13 21:34:00</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -8524,17 +8519,17 @@
       </c>
       <c r="M130" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608133116145497</t>
+          <t>4500000380202608131586040016</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="0">
-        <v>49196546</v>
+        <v>49196547</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>兰莓</t>
+          <t>雷宁</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -8559,7 +8554,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:56:17</t>
+          <t>2026-08-13 21:34:30</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -8589,17 +8584,17 @@
       </c>
       <c r="M131" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608136989637138</t>
+          <t>4500000368202608133116145497</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="0">
-        <v>49196528</v>
+        <v>49196546</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>赵子睿奶奶</t>
+          <t>兰莓</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -8624,7 +8619,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:22</t>
+          <t>2026-08-13 21:56:17</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -8654,17 +8649,17 @@
       </c>
       <c r="M132" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608137236789446</t>
+          <t>4500000352202608136989637138</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="0">
-        <v>49196510</v>
+        <v>49196528</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>山岭巨人</t>
+          <t>赵子睿奶奶</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
@@ -8689,7 +8684,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:22</t>
+          <t>2026-08-13 21:33:22</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -8719,17 +8714,17 @@
       </c>
       <c r="M133" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608138809307553</t>
+          <t>4500000345202608137236789446</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="0">
-        <v>49196507</v>
+        <v>49196510</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>香字钟培芷</t>
+          <t>山岭巨人</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -8754,7 +8749,7 @@
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:53</t>
+          <t>2026-08-13 21:35:22</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -8784,17 +8779,17 @@
       </c>
       <c r="M134" s="0" t="inlineStr">
         <is>
-          <t>4500000370202608133660294135</t>
+          <t>4500000324202608138809307553</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="0">
-        <v>49196498</v>
+        <v>49196507</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>孟光宗</t>
+          <t>香字钟培芷</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -8819,7 +8814,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:37:14</t>
+          <t>2026-08-13 21:32:53</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -8849,17 +8844,17 @@
       </c>
       <c r="M135" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608138859211736</t>
+          <t>4500000370202608133660294135</t>
         </is>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="0">
-        <v>49196495</v>
+        <v>49196498</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>夏雨晴的妈妈（天发水芹</t>
+          <t>孟光宗</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -8884,7 +8879,7 @@
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:37:14</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -8914,22 +8909,17 @@
       </c>
       <c r="M136" s="0" t="inlineStr">
         <is>
-          <t>4500000371202608138873102820</t>
-        </is>
-      </c>
-      <c r="N136" s="0" t="inlineStr">
-        <is>
-          <t>湾仔区</t>
+          <t>4500000363202608138859211736</t>
         </is>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="0">
-        <v>49196485</v>
+        <v>49196495</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>法苑文印广告</t>
+          <t>夏雨晴的妈妈（天发水芹</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
@@ -8954,7 +8944,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:06</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -8984,17 +8974,22 @@
       </c>
       <c r="M137" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608139506557676</t>
+          <t>4500000371202608138873102820</t>
+        </is>
+      </c>
+      <c r="N137" s="0" t="inlineStr">
+        <is>
+          <t>湾仔区</t>
         </is>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="0">
-        <v>49196481</v>
+        <v>49196485</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>四季果</t>
+          <t>法苑文印广告</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
@@ -9019,7 +9014,7 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:08</t>
+          <t>2026-08-13 21:33:06</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -9049,17 +9044,17 @@
       </c>
       <c r="M138" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608134787426208</t>
+          <t>4500000379202608139506557676</t>
         </is>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="0">
-        <v>49196479</v>
+        <v>49196481</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>仇尚妹</t>
+          <t>四季果</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
@@ -9084,7 +9079,7 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:43</t>
+          <t>2026-08-13 21:33:08</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -9114,17 +9109,17 @@
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608136810799236</t>
+          <t>4500000335202608134787426208</t>
         </is>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="0">
-        <v>49196478</v>
+        <v>49196479</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>A古庄店大新手机卖场库琳琳</t>
+          <t>仇尚妹</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -9149,7 +9144,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:42</t>
+          <t>2026-08-13 21:32:43</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -9179,17 +9174,17 @@
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608137311399529</t>
+          <t>4500000374202608136810799236</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="0">
-        <v>49196473</v>
+        <v>49196478</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>刘玉云机械租赁服务部15905691602</t>
+          <t>A古庄店大新手机卖场库琳琳</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -9214,7 +9209,7 @@
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:30</t>
+          <t>2026-08-13 21:32:42</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -9244,17 +9239,17 @@
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608134297741797</t>
+          <t>4500000373202608137311399529</t>
         </is>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="0">
-        <v>49196470</v>
+        <v>49196473</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>众舍康安二手房丽姐</t>
+          <t>刘玉云机械租赁服务部15905691602</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
@@ -9279,7 +9274,7 @@
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:28</t>
+          <t>2026-08-13 21:32:30</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -9309,17 +9304,17 @@
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608137489426707</t>
+          <t>4500000315202608134297741797</t>
         </is>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="0">
-        <v>49196462</v>
+        <v>49196470</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>欢欢</t>
+          <t>众舍康安二手房丽姐</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -9344,7 +9339,7 @@
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:31</t>
+          <t>2026-08-13 21:32:28</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -9374,17 +9369,17 @@
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608136078541008</t>
+          <t>4500000325202608137489426707</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="0">
-        <v>49196456</v>
+        <v>49196462</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>润花</t>
+          <t>欢欢</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -9409,7 +9404,7 @@
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:32:31</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -9439,17 +9434,17 @@
       </c>
       <c r="M144" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608139285322594</t>
+          <t>4500000382202608136078541008</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="0">
-        <v>49196455</v>
+        <v>49196456</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>风之韵</t>
+          <t>润花</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -9474,7 +9469,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:34</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -9504,17 +9499,17 @@
       </c>
       <c r="M145" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608137054529020</t>
+          <t>4500000365202608139285322594</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="0">
-        <v>49196452</v>
+        <v>49196455</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>开心每一天</t>
+          <t>风之韵</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -9539,7 +9534,7 @@
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:40</t>
+          <t>2026-08-13 21:32:34</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -9569,22 +9564,17 @@
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608131603927208</t>
-        </is>
-      </c>
-      <c r="N146" s="0" t="inlineStr">
-        <is>
-          <t>连云港</t>
+          <t>4500000339202608137054529020</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="0">
-        <v>49196449</v>
+        <v>49196452</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>吉乐常伴</t>
+          <t>开心每一天</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -9609,7 +9599,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:32:40</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -9639,17 +9629,22 @@
       </c>
       <c r="M147" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608139313739490</t>
+          <t>4500000327202608131603927208</t>
+        </is>
+      </c>
+      <c r="N147" s="0" t="inlineStr">
+        <is>
+          <t>连云港</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="0">
-        <v>49196445</v>
+        <v>49196449</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>快乐宝贝</t>
+          <t>吉乐常伴</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -9674,7 +9669,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:15</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -9704,17 +9699,17 @@
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133056225424</t>
+          <t>4500000340202608139313739490</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="0">
-        <v>49196441</v>
+        <v>49196445</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>感恩快乐每一天</t>
+          <t>快乐宝贝</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -9739,7 +9734,7 @@
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:13</t>
+          <t>2026-08-13 21:32:15</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -9769,17 +9764,17 @@
       </c>
       <c r="M149" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608132236113522</t>
+          <t>4500000326202608133056225424</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="0">
-        <v>49196439</v>
+        <v>49196441</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>翰林世家京墨18240001035</t>
+          <t>感恩快乐每一天</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -9804,7 +9799,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:18</t>
+          <t>2026-08-13 21:32:13</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -9834,17 +9829,17 @@
       </c>
       <c r="M150" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608131410776307</t>
+          <t>4500000383202608132236113522</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="0">
-        <v>49196437</v>
+        <v>49196439</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>悦朵宝贝</t>
+          <t>翰林世家京墨18240001035</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -9869,7 +9864,7 @@
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:06</t>
+          <t>2026-08-13 21:32:18</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -9899,17 +9894,17 @@
       </c>
       <c r="M151" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608135681746747</t>
+          <t>4500000315202608131410776307</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="0">
-        <v>49196435</v>
+        <v>49196437</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>我的幸福</t>
+          <t>悦朵宝贝</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
@@ -9934,7 +9929,7 @@
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:32:06</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -9964,17 +9959,17 @@
       </c>
       <c r="M152" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608138821842807</t>
+          <t>4500000343202608135681746747</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="0">
-        <v>49196433</v>
+        <v>49196435</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>程胜英</t>
+          <t>我的幸福</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -9999,7 +9994,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:33</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -10029,17 +10024,17 @@
       </c>
       <c r="M153" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608136558136840</t>
+          <t>4500000331202608138821842807</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="0">
-        <v>49196424</v>
+        <v>49196433</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>甘峰源奶奶</t>
+          <t>程胜英</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -10064,7 +10059,7 @@
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:16</t>
+          <t>2026-08-13 21:32:33</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -10094,17 +10089,17 @@
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608139681236972</t>
+          <t>4500000338202608136558136840</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="0">
-        <v>49196412</v>
+        <v>49196424</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>贝贝老妈</t>
+          <t>甘峰源奶奶</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -10129,7 +10124,7 @@
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:49</t>
+          <t>2026-08-13 21:32:16</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -10159,17 +10154,17 @@
       </c>
       <c r="M155" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608138627203805</t>
+          <t>4500000374202608139681236972</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="0">
-        <v>49196406</v>
+        <v>49196412</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>过好每一天</t>
+          <t>贝贝老妈</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -10194,7 +10189,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:55</t>
+          <t>2026-08-13 21:31:49</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -10224,17 +10219,17 @@
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608139484061741</t>
+          <t>4500000360202608138627203805</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="0">
-        <v>49196403</v>
+        <v>49196406</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>迪迪</t>
+          <t>过好每一天</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -10259,7 +10254,7 @@
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:58</t>
+          <t>2026-08-13 21:31:55</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -10289,17 +10284,17 @@
       </c>
       <c r="M157" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608138209731181</t>
+          <t>4500000384202608139484061741</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="0">
-        <v>49196399</v>
+        <v>49196403</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>境随心转</t>
+          <t>迪迪</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -10324,7 +10319,7 @@
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:47</t>
+          <t>2026-08-13 21:31:58</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -10354,17 +10349,17 @@
       </c>
       <c r="M158" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608138946210876</t>
+          <t>4500000326202608138209731181</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="0">
-        <v>49196391</v>
+        <v>49196399</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>💖越来越好💖</t>
+          <t>境随心转</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -10389,7 +10384,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:01</t>
+          <t>2026-08-13 21:31:47</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -10419,17 +10414,17 @@
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133672869122</t>
+          <t>4500000380202608138946210876</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="0">
-        <v>49196390</v>
+        <v>49196391</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>翠翠</t>
+          <t>💖越来越好💖</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -10454,7 +10449,7 @@
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:38</t>
+          <t>2026-08-13 21:32:01</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -10484,22 +10479,17 @@
       </c>
       <c r="M160" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608139683947334</t>
-        </is>
-      </c>
-      <c r="N160" s="0" t="inlineStr">
-        <is>
-          <t>广州</t>
+          <t>4500000326202608133672869122</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="0">
-        <v>49196389</v>
+        <v>49196390</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>漫步繁华街</t>
+          <t>翠翠</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -10524,7 +10514,7 @@
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:39</t>
+          <t>2026-08-13 21:31:38</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -10554,17 +10544,22 @@
       </c>
       <c r="M161" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608135974835236</t>
+          <t>4500000351202608139683947334</t>
+        </is>
+      </c>
+      <c r="N161" s="0" t="inlineStr">
+        <is>
+          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="0">
-        <v>49196385</v>
+        <v>49196389</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>平淡人生🌲</t>
+          <t>漫步繁华街</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -10589,7 +10584,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:35</t>
+          <t>2026-08-13 21:32:39</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -10619,17 +10614,17 @@
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608136587117638</t>
+          <t>4500000375202608135974835236</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="0">
-        <v>49196384</v>
+        <v>49196385</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>眼镜灯饰城3楼76号15923959748</t>
+          <t>平淡人生🌲</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -10654,7 +10649,7 @@
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:34</t>
+          <t>2026-08-13 21:31:35</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -10684,17 +10679,17 @@
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608139966140440</t>
+          <t>4500000359202608136587117638</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="0">
-        <v>49196383</v>
+        <v>49196384</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>喜枝</t>
+          <t>眼镜灯饰城3楼76号15923959748</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -10719,7 +10714,7 @@
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:45</t>
+          <t>2026-08-13 21:31:34</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -10749,17 +10744,17 @@
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608138694510811</t>
+          <t>4500000333202608139966140440</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="0">
-        <v>49155446</v>
+        <v>49196383</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>笑口常开</t>
+          <t>喜枝</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -10784,7 +10779,7 @@
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:36:06</t>
+          <t>2026-08-13 21:31:45</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -10814,17 +10809,17 @@
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608121856487760</t>
+          <t>4500000333202608138694510811</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="0">
-        <v>49155389</v>
+        <v>49155446</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>奥普郭彦丽13937990394</t>
+          <t>笑口常开</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
@@ -10849,7 +10844,7 @@
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:44</t>
+          <t>2026-08-12 21:36:06</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -10879,17 +10874,17 @@
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608124582542642</t>
+          <t>4500000376202608121856487760</t>
         </is>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="0">
-        <v>49155374</v>
+        <v>49155389</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>流星雨文华</t>
+          <t>奥普郭彦丽13937990394</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
@@ -10914,7 +10909,7 @@
       </c>
       <c r="G167" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:26</t>
+          <t>2026-08-12 21:35:44</t>
         </is>
       </c>
       <c r="H167" s="0" t="inlineStr">
@@ -10944,17 +10939,17 @@
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608121430434820</t>
+          <t>4500000324202608124582542642</t>
         </is>
       </c>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="0">
-        <v>49155368</v>
+        <v>49155374</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>笑对人生</t>
+          <t>流星雨文华</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
@@ -10979,7 +10974,7 @@
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:56</t>
+          <t>2026-08-12 21:35:26</t>
         </is>
       </c>
       <c r="H168" s="0" t="inlineStr">
@@ -11009,17 +11004,17 @@
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608126193240482</t>
+          <t>4500000377202608121430434820</t>
         </is>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="0">
-        <v>49155365</v>
+        <v>49155368</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>秀</t>
+          <t>笑对人生</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
@@ -11044,7 +11039,7 @@
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:41</t>
+          <t>2026-08-12 21:34:56</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -11074,17 +11069,17 @@
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608121090433848</t>
+          <t>4500000316202608126193240482</t>
         </is>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="0">
-        <v>49155364</v>
+        <v>49155365</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>冯衣制版18966913385</t>
+          <t>秀</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
@@ -11109,7 +11104,7 @@
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:09</t>
+          <t>2026-08-12 21:34:41</t>
         </is>
       </c>
       <c r="H170" s="0" t="inlineStr">
@@ -11139,17 +11134,17 @@
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608122728123344</t>
+          <t>4500000363202608121090433848</t>
         </is>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="0">
-        <v>49155363</v>
+        <v>49155364</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>冯衣制版18966913385</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -11174,7 +11169,7 @@
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:54</t>
+          <t>2026-08-12 21:35:09</t>
         </is>
       </c>
       <c r="H171" s="0" t="inlineStr">
@@ -11204,17 +11199,17 @@
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608128317430099</t>
+          <t>4500000348202608122728123344</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="0">
-        <v>49155361</v>
+        <v>49155363</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>春华秋实</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -11239,7 +11234,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:48</t>
+          <t>2026-08-12 21:34:54</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -11269,17 +11264,17 @@
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608121174096033</t>
+          <t>4500000320202608128317430099</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="0">
-        <v>49155359</v>
+        <v>49155361</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>春梅。</t>
+          <t>春华秋实</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -11304,7 +11299,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:36</t>
+          <t>2026-08-12 21:34:48</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -11334,17 +11329,17 @@
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608123637081551</t>
+          <t>4500000346202608121174096033</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="0">
-        <v>49155344</v>
+        <v>49155359</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>自由人生</t>
+          <t>春梅。</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -11369,7 +11364,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:25</t>
+          <t>2026-08-12 21:34:36</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -11399,17 +11394,17 @@
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608129865186226</t>
+          <t>4500000374202608123637081551</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="0">
-        <v>49155337</v>
+        <v>49155344</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>红红</t>
+          <t>自由人生</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -11434,7 +11429,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:50</t>
+          <t>2026-08-12 21:34:25</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -11464,17 +11459,17 @@
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608125530964720</t>
+          <t>4500000317202608129865186226</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="0">
-        <v>49155330</v>
+        <v>49155337</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>徐淑香</t>
+          <t>红红</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -11499,7 +11494,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:20</t>
+          <t>2026-08-12 21:34:50</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -11529,17 +11524,17 @@
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608124983971576</t>
+          <t>4500000327202608125530964720</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="0">
-        <v>49155314</v>
+        <v>49155330</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>H叶</t>
+          <t>徐淑香</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -11564,7 +11559,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:57</t>
+          <t>2026-08-12 21:34:20</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -11594,17 +11589,17 @@
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608128162955185</t>
+          <t>4500000359202608124983971576</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="0">
-        <v>49155309</v>
+        <v>49155314</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>A0000刘氏修脚红姐</t>
+          <t>H叶</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -11629,7 +11624,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:47</t>
+          <t>2026-08-12 21:33:57</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -11659,17 +11654,17 @@
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127176361921</t>
+          <t>4500000322202608128162955185</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="0">
-        <v>49155304</v>
+        <v>49155309</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>万树红</t>
+          <t>A0000刘氏修脚红姐</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -11694,7 +11689,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:52</t>
+          <t>2026-08-12 21:33:47</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -11724,17 +11719,17 @@
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608123430987084</t>
+          <t>4500000333202608127176361921</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="0">
-        <v>49155293</v>
+        <v>49155304</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>往事如烟</t>
+          <t>万树红</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -11759,7 +11754,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:33</t>
+          <t>2026-08-12 21:33:52</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -11789,17 +11784,17 @@
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608121388094535</t>
+          <t>4500000379202608123430987084</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="0">
-        <v>49155283</v>
+        <v>49155293</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>雪洁</t>
+          <t>往事如烟</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
@@ -11824,7 +11819,7 @@
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:27</t>
+          <t>2026-08-12 21:33:33</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -11854,17 +11849,17 @@
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608125072492429</t>
+          <t>4500000360202608121388094535</t>
         </is>
       </c>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="0">
-        <v>49155274</v>
+        <v>49155283</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>文英</t>
+          <t>雪洁</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
@@ -11889,7 +11884,7 @@
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:24</t>
+          <t>2026-08-12 21:33:27</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -11919,17 +11914,17 @@
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608127495955817</t>
+          <t>4500000369202608125072492429</t>
         </is>
       </c>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="0">
-        <v>49155273</v>
+        <v>49155274</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>宫本江</t>
+          <t>文英</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
@@ -11954,7 +11949,7 @@
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:24</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -11984,17 +11979,17 @@
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608122111396208</t>
+          <t>4500000373202608127495955817</t>
         </is>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="0">
-        <v>49155272</v>
+        <v>49155273</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>悠闲的人</t>
+          <t>宫本江</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
@@ -12019,7 +12014,7 @@
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:13</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -12049,17 +12044,17 @@
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608122303219210</t>
+          <t>4500000346202608122111396208</t>
         </is>
       </c>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="0">
-        <v>49155271</v>
+        <v>49155272</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>幸福人生</t>
+          <t>悠闲的人</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
@@ -12084,7 +12079,7 @@
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:08</t>
+          <t>2026-08-12 21:33:13</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
@@ -12114,17 +12109,17 @@
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608124799146350</t>
+          <t>4500000331202608122303219210</t>
         </is>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="0">
-        <v>49155270</v>
+        <v>49155271</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>雾里看花</t>
+          <t>幸福人生</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
@@ -12149,7 +12144,7 @@
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:15</t>
+          <t>2026-08-12 21:34:08</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
@@ -12179,17 +12174,17 @@
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608123995555310</t>
+          <t>4500000333202608124799146350</t>
         </is>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="0">
-        <v>49155266</v>
+        <v>49155270</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>清风绕指柔</t>
+          <t>雾里看花</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
@@ -12214,7 +12209,7 @@
       </c>
       <c r="G187" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:31</t>
+          <t>2026-08-12 21:33:15</t>
         </is>
       </c>
       <c r="H187" s="0" t="inlineStr">
@@ -12244,17 +12239,17 @@
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127946689166</t>
+          <t>4500000331202608123995555310</t>
         </is>
       </c>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="0">
-        <v>49155265</v>
+        <v>49155266</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>心想事成南无阿弥陀佛</t>
+          <t>清风绕指柔</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
@@ -12279,7 +12274,7 @@
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:42</t>
+          <t>2026-08-12 21:33:31</t>
         </is>
       </c>
       <c r="H188" s="0" t="inlineStr">
@@ -12309,17 +12304,17 @@
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608126996164764</t>
+          <t>4500000333202608127946689166</t>
         </is>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="0">
-        <v>49155264</v>
+        <v>49155265</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>刘凤辉</t>
+          <t>心想事成南无阿弥陀佛</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
@@ -12344,7 +12339,7 @@
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:42</t>
         </is>
       </c>
       <c r="H189" s="0" t="inlineStr">
@@ -12374,17 +12369,17 @@
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608124680304775</t>
+          <t>4500000330202608126996164764</t>
         </is>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="0">
-        <v>49155263</v>
+        <v>49155264</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>朱叶</t>
+          <t>刘凤辉</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
@@ -12409,7 +12404,7 @@
       </c>
       <c r="G190" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:18</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H190" s="0" t="inlineStr">
@@ -12439,17 +12434,17 @@
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608124445297817</t>
+          <t>4500000330202608124680304775</t>
         </is>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="0">
-        <v>49155253</v>
+        <v>49155263</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>一顺百顺。好运来</t>
+          <t>朱叶</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
@@ -12474,7 +12469,7 @@
       </c>
       <c r="G191" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:51</t>
+          <t>2026-08-12 21:33:18</t>
         </is>
       </c>
       <c r="H191" s="0" t="inlineStr">
@@ -12504,17 +12499,17 @@
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608122909608257</t>
+          <t>4500000345202608124445297817</t>
         </is>
       </c>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="0">
-        <v>49155246</v>
+        <v>49155253</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>陈桂芳</t>
+          <t>一顺百顺。好运来</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
@@ -12539,7 +12534,7 @@
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:33:51</t>
         </is>
       </c>
       <c r="H192" s="0" t="inlineStr">
@@ -12569,17 +12564,17 @@
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608126828589764</t>
+          <t>4500000326202608122909608257</t>
         </is>
       </c>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="0">
-        <v>49155234</v>
+        <v>49155246</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>黄仲芬15683592716</t>
+          <t>陈桂芳</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
@@ -12604,7 +12599,7 @@
       </c>
       <c r="G193" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H193" s="0" t="inlineStr">
@@ -12634,17 +12629,17 @@
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608129237945248</t>
+          <t>4500000378202608126828589764</t>
         </is>
       </c>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="0">
-        <v>49155233</v>
+        <v>49155234</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>幸福姐赵会玲</t>
+          <t>黄仲芬15683592716</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
@@ -12669,7 +12664,7 @@
       </c>
       <c r="G194" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:04</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H194" s="0" t="inlineStr">
@@ -12699,17 +12694,17 @@
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608128379976752</t>
+          <t>4500000325202608129237945248</t>
         </is>
       </c>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="0">
-        <v>49155230</v>
+        <v>49155233</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>锦鲤果果</t>
+          <t>幸福姐赵会玲</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
@@ -12734,7 +12729,7 @@
       </c>
       <c r="G195" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:20</t>
+          <t>2026-08-12 21:34:04</t>
         </is>
       </c>
       <c r="H195" s="0" t="inlineStr">
@@ -12764,17 +12759,17 @@
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608129199323858</t>
+          <t>4500000317202608128379976752</t>
         </is>
       </c>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="0">
-        <v>49155226</v>
+        <v>49155230</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>戎戎</t>
+          <t>锦鲤果果</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
@@ -12799,7 +12794,7 @@
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:05</t>
+          <t>2026-08-12 21:33:20</t>
         </is>
       </c>
       <c r="H196" s="0" t="inlineStr">
@@ -12829,17 +12824,17 @@
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608125827170254</t>
+          <t>4500000322202608129199323858</t>
         </is>
       </c>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="0">
-        <v>49155220</v>
+        <v>49155226</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>阿玉</t>
+          <t>戎戎</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
@@ -12864,7 +12859,7 @@
       </c>
       <c r="G197" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:05</t>
         </is>
       </c>
       <c r="H197" s="0" t="inlineStr">
@@ -12894,17 +12889,17 @@
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608129272259118</t>
+          <t>4500000331202608125827170254</t>
         </is>
       </c>
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="0">
-        <v>49155219</v>
+        <v>49155220</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>沉淀、</t>
+          <t>阿玉</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
@@ -12929,7 +12924,7 @@
       </c>
       <c r="G198" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H198" s="0" t="inlineStr">
@@ -12959,17 +12954,17 @@
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
-          <t>4500000372202608124305947387</t>
+          <t>4500000345202608129272259118</t>
         </is>
       </c>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="0">
-        <v>49155216</v>
+        <v>49155219</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>晴天</t>
+          <t>沉淀、</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
@@ -12994,7 +12989,7 @@
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H199" s="0" t="inlineStr">
@@ -13024,17 +13019,17 @@
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608122833385690</t>
+          <t>4500000372202608124305947387</t>
         </is>
       </c>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="0">
-        <v>49155210</v>
+        <v>49155216</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>开正商行</t>
+          <t>晴天</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
@@ -13059,7 +13054,7 @@
       </c>
       <c r="G200" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H200" s="0" t="inlineStr">
@@ -13089,17 +13084,17 @@
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608127466098812</t>
+          <t>4500000334202608122833385690</t>
         </is>
       </c>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="0">
-        <v>49155208</v>
+        <v>49155210</v>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>傻傻的幸福</t>
+          <t>开正商行</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
@@ -13124,7 +13119,7 @@
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H201" s="0" t="inlineStr">
@@ -13154,17 +13149,17 @@
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608122593720010</t>
+          <t>4500000348202608127466098812</t>
         </is>
       </c>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="0">
-        <v>49155205</v>
+        <v>49155208</v>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>你好</t>
+          <t>傻傻的幸福</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
@@ -13189,7 +13184,7 @@
       </c>
       <c r="G202" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H202" s="0" t="inlineStr">
@@ -13219,17 +13214,17 @@
       </c>
       <c r="M202" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608122478222937</t>
+          <t>4500000378202608122593720010</t>
         </is>
       </c>
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="0">
-        <v>49155203</v>
+        <v>49155205</v>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>一生有你</t>
+          <t>你好</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
@@ -13254,7 +13249,7 @@
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H203" s="0" t="inlineStr">
@@ -13284,17 +13279,17 @@
       </c>
       <c r="M203" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608129324316511</t>
+          <t>4500000335202608122478222937</t>
         </is>
       </c>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="0">
-        <v>49155200</v>
+        <v>49155203</v>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>一生有你</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
@@ -13319,7 +13314,7 @@
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:09</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H204" s="0" t="inlineStr">
@@ -13349,17 +13344,17 @@
       </c>
       <c r="M204" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608125850014769</t>
+          <t>4500000369202608129324316511</t>
         </is>
       </c>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="0">
-        <v>49155197</v>
+        <v>49155200</v>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>桂芝改名叫张淑玮</t>
+          <t>618</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
@@ -13384,7 +13379,7 @@
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:33:09</t>
         </is>
       </c>
       <c r="H205" s="0" t="inlineStr">
@@ -13414,17 +13409,17 @@
       </c>
       <c r="M205" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608121228274851</t>
+          <t>4500000384202608125850014769</t>
         </is>
       </c>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="0">
-        <v>49155194</v>
+        <v>49155197</v>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>自强不息</t>
+          <t>桂芝改名叫张淑玮</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
@@ -13449,7 +13444,7 @@
       </c>
       <c r="G206" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H206" s="0" t="inlineStr">
@@ -13479,17 +13474,17 @@
       </c>
       <c r="M206" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608124140031616</t>
+          <t>4500000351202608121228274851</t>
         </is>
       </c>
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="0">
-        <v>49155192</v>
+        <v>49155194</v>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>时光如水</t>
+          <t>自强不息</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
@@ -13514,7 +13509,7 @@
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:03</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H207" s="0" t="inlineStr">
@@ -13544,17 +13539,17 @@
       </c>
       <c r="M207" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608128865933230</t>
+          <t>4500000356202608124140031616</t>
         </is>
       </c>
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="0">
-        <v>49155187</v>
+        <v>49155192</v>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>时光如水</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
@@ -13579,7 +13574,7 @@
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:03</t>
         </is>
       </c>
       <c r="H208" s="0" t="inlineStr">
@@ -13609,17 +13604,17 @@
       </c>
       <c r="M208" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608125275144248</t>
+          <t>4500000364202608128865933230</t>
         </is>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="A209" s="0">
-        <v>49155186</v>
+        <v>49155187</v>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>星辰</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="C209" s="0" t="inlineStr">
@@ -13644,7 +13639,7 @@
       </c>
       <c r="G209" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H209" s="0" t="inlineStr">
@@ -13674,17 +13669,17 @@
       </c>
       <c r="M209" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608121378976306</t>
+          <t>4500000334202608125275144248</t>
         </is>
       </c>
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="0">
-        <v>49155185</v>
+        <v>49155186</v>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>天津温室大棚光伏厂家18920981728</t>
+          <t>星辰</t>
         </is>
       </c>
       <c r="C210" s="0" t="inlineStr">
@@ -13709,7 +13704,7 @@
       </c>
       <c r="G210" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:32</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H210" s="0" t="inlineStr">
@@ -13739,17 +13734,17 @@
       </c>
       <c r="M210" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608125631581660</t>
+          <t>4500000373202608121378976306</t>
         </is>
       </c>
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="0">
-        <v>49155184</v>
+        <v>49155185</v>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>惠民</t>
+          <t>天津温室大棚光伏厂家18920981728</t>
         </is>
       </c>
       <c r="C211" s="0" t="inlineStr">
@@ -13774,7 +13769,7 @@
       </c>
       <c r="G211" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:08</t>
+          <t>2026-08-12 21:33:32</t>
         </is>
       </c>
       <c r="H211" s="0" t="inlineStr">
@@ -13804,17 +13799,17 @@
       </c>
       <c r="M211" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608121279528970</t>
+          <t>4500000318202608125631581660</t>
         </is>
       </c>
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="0">
-        <v>49155180</v>
+        <v>49155184</v>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>常青树</t>
+          <t>惠民</t>
         </is>
       </c>
       <c r="C212" s="0" t="inlineStr">
@@ -13839,7 +13834,7 @@
       </c>
       <c r="G212" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:06</t>
+          <t>2026-08-12 21:33:08</t>
         </is>
       </c>
       <c r="H212" s="0" t="inlineStr">
@@ -13869,17 +13864,17 @@
       </c>
       <c r="M212" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125426925788</t>
+          <t>4500000355202608121279528970</t>
         </is>
       </c>
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="0">
-        <v>49155178</v>
+        <v>49155180</v>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>玉伟</t>
+          <t>常青树</t>
         </is>
       </c>
       <c r="C213" s="0" t="inlineStr">
@@ -13904,7 +13899,7 @@
       </c>
       <c r="G213" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:33:06</t>
         </is>
       </c>
       <c r="H213" s="0" t="inlineStr">
@@ -13934,17 +13929,17 @@
       </c>
       <c r="M213" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608125205677586</t>
+          <t>4500000357202608125426925788</t>
         </is>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="0">
-        <v>49155171</v>
+        <v>49155178</v>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>秦晓娟～中医五官排毒</t>
+          <t>玉伟</t>
         </is>
       </c>
       <c r="C214" s="0" t="inlineStr">
@@ -13969,7 +13964,7 @@
       </c>
       <c r="G214" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H214" s="0" t="inlineStr">
@@ -13999,17 +13994,17 @@
       </c>
       <c r="M214" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608129265074581</t>
+          <t>4500000364202608125205677586</t>
         </is>
       </c>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="0">
-        <v>49155167</v>
+        <v>49155171</v>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>水琴</t>
+          <t>秦晓娟～中医五官排毒</t>
         </is>
       </c>
       <c r="C215" s="0" t="inlineStr">
@@ -14034,7 +14029,7 @@
       </c>
       <c r="G215" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H215" s="0" t="inlineStr">
@@ -14064,17 +14059,17 @@
       </c>
       <c r="M215" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608128554791016</t>
+          <t>4500000365202608129265074581</t>
         </is>
       </c>
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="0">
-        <v>49155163</v>
+        <v>49155167</v>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>祥云ಠ_ಠ</t>
+          <t>水琴</t>
         </is>
       </c>
       <c r="C216" s="0" t="inlineStr">
@@ -14099,7 +14094,7 @@
       </c>
       <c r="G216" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H216" s="0" t="inlineStr">
@@ -14129,17 +14124,17 @@
       </c>
       <c r="M216" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608126804876906</t>
+          <t>4500000315202608128554791016</t>
         </is>
       </c>
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="0">
-        <v>49155162</v>
+        <v>49155163</v>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>雪绒花</t>
+          <t>祥云ಠ_ಠ</t>
         </is>
       </c>
       <c r="C217" s="0" t="inlineStr">
@@ -14164,7 +14159,7 @@
       </c>
       <c r="G217" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H217" s="0" t="inlineStr">
@@ -14194,17 +14189,17 @@
       </c>
       <c r="M217" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608122943306781</t>
+          <t>4500000344202608126804876906</t>
         </is>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="A218" s="0">
-        <v>49155161</v>
+        <v>49155162</v>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>        糖果</t>
+          <t>雪绒花</t>
         </is>
       </c>
       <c r="C218" s="0" t="inlineStr">
@@ -14229,7 +14224,7 @@
       </c>
       <c r="G218" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H218" s="0" t="inlineStr">
@@ -14259,17 +14254,17 @@
       </c>
       <c r="M218" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608121712400624</t>
+          <t>4500000343202608122943306781</t>
         </is>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="A219" s="0">
-        <v>49155157</v>
+        <v>49155161</v>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>流失的岁月</t>
+          <t>        糖果</t>
         </is>
       </c>
       <c r="C219" s="0" t="inlineStr">
@@ -14294,7 +14289,7 @@
       </c>
       <c r="G219" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:11</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H219" s="0" t="inlineStr">
@@ -14324,17 +14319,17 @@
       </c>
       <c r="M219" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608126379751055</t>
+          <t>4500000384202608121712400624</t>
         </is>
       </c>
     </row>
     <row r="220" spans="1:14">
       <c r="A220" s="0">
-        <v>49155152</v>
+        <v>49155157</v>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>夏末幽荷</t>
+          <t>流失的岁月</t>
         </is>
       </c>
       <c r="C220" s="0" t="inlineStr">
@@ -14359,7 +14354,7 @@
       </c>
       <c r="G220" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:33:11</t>
         </is>
       </c>
       <c r="H220" s="0" t="inlineStr">
@@ -14389,17 +14384,17 @@
       </c>
       <c r="M220" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608128669470764</t>
+          <t>4500000379202608126379751055</t>
         </is>
       </c>
     </row>
     <row r="221" spans="1:14">
       <c r="A221" s="0">
-        <v>49155150</v>
+        <v>49155152</v>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>药曼</t>
+          <t>夏末幽荷</t>
         </is>
       </c>
       <c r="C221" s="0" t="inlineStr">
@@ -14424,7 +14419,7 @@
       </c>
       <c r="G221" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H221" s="0" t="inlineStr">
@@ -14454,17 +14449,17 @@
       </c>
       <c r="M221" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608127294126669</t>
+          <t>4500000337202608128669470764</t>
         </is>
       </c>
     </row>
     <row r="222" spans="1:14">
       <c r="A222" s="0">
-        <v>49155149</v>
+        <v>49155150</v>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>🌺 谭谭🌺</t>
+          <t>药曼</t>
         </is>
       </c>
       <c r="C222" s="0" t="inlineStr">
@@ -14489,7 +14484,7 @@
       </c>
       <c r="G222" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:58</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H222" s="0" t="inlineStr">
@@ -14519,17 +14514,17 @@
       </c>
       <c r="M222" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608121029117778</t>
+          <t>4500000345202608127294126669</t>
         </is>
       </c>
     </row>
     <row r="223" spans="1:14">
       <c r="A223" s="0">
-        <v>49155148</v>
+        <v>49155149</v>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>王玉(邮局对面卖手机)</t>
+          <t>🌺 谭谭🌺</t>
         </is>
       </c>
       <c r="C223" s="0" t="inlineStr">
@@ -14554,7 +14549,7 @@
       </c>
       <c r="G223" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:58</t>
         </is>
       </c>
       <c r="H223" s="0" t="inlineStr">
@@ -14584,17 +14579,17 @@
       </c>
       <c r="M223" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608126218721690</t>
+          <t>4500000350202608121029117778</t>
         </is>
       </c>
     </row>
     <row r="224" spans="1:14">
       <c r="A224" s="0">
-        <v>49155147</v>
+        <v>49155148</v>
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
-          <t>美好夕阳</t>
+          <t>王玉(邮局对面卖手机)</t>
         </is>
       </c>
       <c r="C224" s="0" t="inlineStr">
@@ -14619,7 +14614,7 @@
       </c>
       <c r="G224" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H224" s="0" t="inlineStr">
@@ -14649,17 +14644,17 @@
       </c>
       <c r="M224" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608128224202725</t>
+          <t>4500000342202608126218721690</t>
         </is>
       </c>
     </row>
     <row r="225" spans="1:14">
       <c r="A225" s="0">
-        <v>49155145</v>
+        <v>49155147</v>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>平凡</t>
+          <t>美好夕阳</t>
         </is>
       </c>
       <c r="C225" s="0" t="inlineStr">
@@ -14684,7 +14679,7 @@
       </c>
       <c r="G225" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H225" s="0" t="inlineStr">
@@ -14714,17 +14709,17 @@
       </c>
       <c r="M225" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608122476247171</t>
+          <t>4500000343202608128224202725</t>
         </is>
       </c>
     </row>
     <row r="226" spans="1:14">
       <c r="A226" s="0">
-        <v>49155143</v>
+        <v>49155145</v>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>唐洪</t>
+          <t>平凡</t>
         </is>
       </c>
       <c r="C226" s="0" t="inlineStr">
@@ -14749,7 +14744,7 @@
       </c>
       <c r="G226" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:45</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H226" s="0" t="inlineStr">
@@ -14779,17 +14774,17 @@
       </c>
       <c r="M226" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608125309483592</t>
+          <t>4500000359202608122476247171</t>
         </is>
       </c>
     </row>
     <row r="227" spans="1:14">
       <c r="A227" s="0">
-        <v>49155140</v>
+        <v>49155143</v>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>浅笑</t>
+          <t>唐洪</t>
         </is>
       </c>
       <c r="C227" s="0" t="inlineStr">
@@ -14814,7 +14809,7 @@
       </c>
       <c r="G227" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:32:45</t>
         </is>
       </c>
       <c r="H227" s="0" t="inlineStr">
@@ -14844,17 +14839,17 @@
       </c>
       <c r="M227" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608123442658613</t>
+          <t>4500000350202608125309483592</t>
         </is>
       </c>
     </row>
     <row r="228" spans="1:14">
       <c r="A228" s="0">
-        <v>49155137</v>
+        <v>49155140</v>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>梅放芳香</t>
+          <t>浅笑</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
@@ -14879,7 +14874,7 @@
       </c>
       <c r="G228" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H228" s="0" t="inlineStr">
@@ -14909,17 +14904,17 @@
       </c>
       <c r="M228" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608127843962862</t>
+          <t>4500000360202608123442658613</t>
         </is>
       </c>
     </row>
     <row r="229" spans="1:14">
       <c r="A229" s="0">
-        <v>49155135</v>
+        <v>49155137</v>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>吴素华</t>
+          <t>梅放芳香</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
@@ -14944,7 +14939,7 @@
       </c>
       <c r="G229" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H229" s="0" t="inlineStr">
@@ -14974,17 +14969,17 @@
       </c>
       <c r="M229" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608124292727044</t>
+          <t>4500000356202608127843962862</t>
         </is>
       </c>
     </row>
     <row r="230" spans="1:14">
       <c r="A230" s="0">
-        <v>49155132</v>
+        <v>49155135</v>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
+          <t>吴素华</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
@@ -15009,7 +15004,7 @@
       </c>
       <c r="G230" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H230" s="0" t="inlineStr">
@@ -15039,17 +15034,17 @@
       </c>
       <c r="M230" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608123141162109</t>
+          <t>4500000339202608124292727044</t>
         </is>
       </c>
     </row>
     <row r="231" spans="1:14">
       <c r="A231" s="0">
-        <v>49155131</v>
+        <v>49155132</v>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>瓷星.</t>
+          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
@@ -15074,7 +15069,7 @@
       </c>
       <c r="G231" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:32:46</t>
         </is>
       </c>
       <c r="H231" s="0" t="inlineStr">
@@ -15104,17 +15099,17 @@
       </c>
       <c r="M231" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608121548709297</t>
+          <t>4500000322202608123141162109</t>
         </is>
       </c>
     </row>
     <row r="232" spans="1:14">
       <c r="A232" s="0">
-        <v>49155129</v>
+        <v>49155131</v>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>妈咪宝贝</t>
+          <t>瓷星.</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
@@ -15139,7 +15134,7 @@
       </c>
       <c r="G232" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:42</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H232" s="0" t="inlineStr">
@@ -15169,17 +15164,17 @@
       </c>
       <c r="M232" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608127726342481</t>
+          <t>4500000383202608121548709297</t>
         </is>
       </c>
     </row>
     <row r="233" spans="1:14">
       <c r="A233" s="0">
-        <v>49155128</v>
+        <v>49155129</v>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>愿结天下有缘人</t>
+          <t>妈咪宝贝</t>
         </is>
       </c>
       <c r="C233" s="0" t="inlineStr">
@@ -15204,7 +15199,7 @@
       </c>
       <c r="G233" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:32:42</t>
         </is>
       </c>
       <c r="H233" s="0" t="inlineStr">
@@ -15234,17 +15229,17 @@
       </c>
       <c r="M233" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608128699617090</t>
+          <t>4500000347202608127726342481</t>
         </is>
       </c>
     </row>
     <row r="234" spans="1:14">
       <c r="A234" s="0">
-        <v>49155124</v>
+        <v>49155128</v>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>勿忘初心</t>
+          <t>愿结天下有缘人</t>
         </is>
       </c>
       <c r="C234" s="0" t="inlineStr">
@@ -15269,7 +15264,7 @@
       </c>
       <c r="G234" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:46</t>
         </is>
       </c>
       <c r="H234" s="0" t="inlineStr">
@@ -15299,17 +15294,17 @@
       </c>
       <c r="M234" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608128217629837</t>
+          <t>4500000321202608128699617090</t>
         </is>
       </c>
     </row>
     <row r="235" spans="1:14">
       <c r="A235" s="0">
-        <v>49155123</v>
+        <v>49155124</v>
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
-          <t>芳草天涯</t>
+          <t>勿忘初心</t>
         </is>
       </c>
       <c r="C235" s="0" t="inlineStr">
@@ -15334,7 +15329,7 @@
       </c>
       <c r="G235" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H235" s="0" t="inlineStr">
@@ -15364,22 +15359,17 @@
       </c>
       <c r="M235" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608123653997556</t>
-        </is>
-      </c>
-      <c r="N235" s="0" t="inlineStr">
-        <is>
-          <t>合肥</t>
+          <t>4500000373202608128217629837</t>
         </is>
       </c>
     </row>
     <row r="236" spans="1:14">
       <c r="A236" s="0">
-        <v>49155120</v>
+        <v>49155123</v>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>记忆中的你</t>
+          <t>芳草天涯</t>
         </is>
       </c>
       <c r="C236" s="0" t="inlineStr">
@@ -15404,7 +15394,7 @@
       </c>
       <c r="G236" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:53</t>
+          <t>2026-08-12 21:32:32</t>
         </is>
       </c>
       <c r="H236" s="0" t="inlineStr">
@@ -15434,17 +15424,22 @@
       </c>
       <c r="M236" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608124401684219</t>
+          <t>4500000321202608123653997556</t>
+        </is>
+      </c>
+      <c r="N236" s="0" t="inlineStr">
+        <is>
+          <t>合肥</t>
         </is>
       </c>
     </row>
     <row r="237" spans="1:14">
       <c r="A237" s="0">
-        <v>49155114</v>
+        <v>49155120</v>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>微笑取暖</t>
+          <t>记忆中的你</t>
         </is>
       </c>
       <c r="C237" s="0" t="inlineStr">
@@ -15469,7 +15464,7 @@
       </c>
       <c r="G237" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:38</t>
+          <t>2026-08-12 21:32:53</t>
         </is>
       </c>
       <c r="H237" s="0" t="inlineStr">
@@ -15499,17 +15494,17 @@
       </c>
       <c r="M237" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608121874803628</t>
+          <t>4500000326202608124401684219</t>
         </is>
       </c>
     </row>
     <row r="238" spans="1:14">
       <c r="A238" s="0">
-        <v>49155112</v>
+        <v>49155114</v>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>净心李芸</t>
+          <t>微笑取暖</t>
         </is>
       </c>
       <c r="C238" s="0" t="inlineStr">
@@ -15534,7 +15529,7 @@
       </c>
       <c r="G238" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:33</t>
+          <t>2026-08-12 21:33:38</t>
         </is>
       </c>
       <c r="H238" s="0" t="inlineStr">
@@ -15564,17 +15559,17 @@
       </c>
       <c r="M238" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608126115898528</t>
+          <t>4500000325202608121874803628</t>
         </is>
       </c>
     </row>
     <row r="239" spans="1:14">
       <c r="A239" s="0">
-        <v>49155108</v>
+        <v>49155112</v>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>衡澜</t>
+          <t>净心李芸</t>
         </is>
       </c>
       <c r="C239" s="0" t="inlineStr">
@@ -15599,7 +15594,7 @@
       </c>
       <c r="G239" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:33</t>
         </is>
       </c>
       <c r="H239" s="0" t="inlineStr">
@@ -15629,17 +15624,17 @@
       </c>
       <c r="M239" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608128833814214</t>
+          <t>4500000351202608126115898528</t>
         </is>
       </c>
     </row>
     <row r="240" spans="1:14">
       <c r="A240" s="0">
-        <v>49155098</v>
+        <v>49155108</v>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>珂</t>
+          <t>衡澜</t>
         </is>
       </c>
       <c r="C240" s="0" t="inlineStr">
@@ -15664,7 +15659,7 @@
       </c>
       <c r="G240" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:39</t>
+          <t>2026-08-12 21:32:32</t>
         </is>
       </c>
       <c r="H240" s="0" t="inlineStr">
@@ -15694,17 +15689,17 @@
       </c>
       <c r="M240" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608128766183266</t>
+          <t>4500000360202608128833814214</t>
         </is>
       </c>
     </row>
     <row r="241" spans="1:14">
       <c r="A241" s="0">
-        <v>49155095</v>
+        <v>49155098</v>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>平安保险~王家宝</t>
+          <t>珂</t>
         </is>
       </c>
       <c r="C241" s="0" t="inlineStr">
@@ -15729,7 +15724,7 @@
       </c>
       <c r="G241" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:32:39</t>
         </is>
       </c>
       <c r="H241" s="0" t="inlineStr">
@@ -15759,17 +15754,17 @@
       </c>
       <c r="M241" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608129139460754</t>
+          <t>4500000344202608128766183266</t>
         </is>
       </c>
     </row>
     <row r="242" spans="1:14">
       <c r="A242" s="0">
-        <v>49155092</v>
+        <v>49155095</v>
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
-          <t>爱情海</t>
+          <t>平安保险~王家宝</t>
         </is>
       </c>
       <c r="C242" s="0" t="inlineStr">
@@ -15794,7 +15789,7 @@
       </c>
       <c r="G242" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:23</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H242" s="0" t="inlineStr">
@@ -15824,17 +15819,17 @@
       </c>
       <c r="M242" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125918396999</t>
+          <t>4500000321202608129139460754</t>
         </is>
       </c>
     </row>
     <row r="243" spans="1:14">
       <c r="A243" s="0">
-        <v>49155090</v>
+        <v>49155092</v>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>三月桃花</t>
+          <t>爱情海</t>
         </is>
       </c>
       <c r="C243" s="0" t="inlineStr">
@@ -15859,7 +15854,7 @@
       </c>
       <c r="G243" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:26</t>
+          <t>2026-08-12 21:32:23</t>
         </is>
       </c>
       <c r="H243" s="0" t="inlineStr">
@@ -15889,70 +15884,135 @@
       </c>
       <c r="M243" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608128744277768</t>
+          <t>4500000357202608125918396999</t>
         </is>
       </c>
     </row>
     <row r="244" spans="1:14">
       <c r="A244" s="0">
+        <v>49155090</v>
+      </c>
+      <c r="B244" s="0" t="inlineStr">
+        <is>
+          <t>三月桃花</t>
+        </is>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D244" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E244" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F244" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G244" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:26</t>
+        </is>
+      </c>
+      <c r="H244" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J244" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K244" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L244" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M244" s="0" t="inlineStr">
+        <is>
+          <t>4500000382202608128744277768</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" spans="1:14">
+      <c r="A245" s="0">
         <v>49155088</v>
       </c>
-      <c r="B244" s="0" t="inlineStr">
+      <c r="B245" s="0" t="inlineStr">
         <is>
           <t>绘兰艺术李老师</t>
         </is>
       </c>
-      <c r="C244" s="0" t="inlineStr">
-        <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
-        </is>
-      </c>
-      <c r="D244" s="0" t="inlineStr">
-        <is>
-          <t>训练营</t>
-        </is>
-      </c>
-      <c r="E244" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="F244" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="G244" s="0" t="inlineStr">
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D245" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E245" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F245" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G245" s="0" t="inlineStr">
         <is>
           <t>2026-08-12 21:32:20</t>
         </is>
       </c>
-      <c r="H244" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I244" s="0" t="inlineStr">
-        <is>
-          <t>彩虹-抖音1元瑜伽</t>
-        </is>
-      </c>
-      <c r="J244" s="0" t="inlineStr">
-        <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
-        </is>
-      </c>
-      <c r="K244" s="0" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="L244" s="0" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M244" s="0" t="inlineStr">
+      <c r="H245" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J245" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K245" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L245" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M245" s="0" t="inlineStr">
         <is>
           <t>4500000358202608128940402527</t>
         </is>

--- a/data/exports/王颖瑜伽/dist_order_2026-10-30.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-10-30.xlsx
@@ -125,11 +125,11 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="0">
-        <v>52336900</v>
+        <v>52340887</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>瀚海</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -154,7 +154,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-10-30 14:09:56</t>
+          <t>2026-10-30 16:34:25</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -164,7 +164,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>Leon老师-抖音0元</t>
+          <t>获客助手自动生成订单-Leon老师-抖音-2832</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -174,7 +174,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L2" s="0" t="inlineStr">
@@ -185,16 +185,16 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="0">
-        <v>51489339</v>
+        <v>52340471</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>春天来了</t>
+          <t>Amy_婷大小姐</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
+          <t>5天 新中老年生活英语营</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -204,17 +204,17 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:18</t>
+          <t>2026-10-30 16:15:33</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -224,17 +224,17 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>彩虹-抖音1元瑜伽</t>
+          <t>获客助手自动生成订单-Leon老师-抖音-2832</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+          <t>WY-0元英语-微信内外落地页添加</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L3" s="0" t="inlineStr">
@@ -242,24 +242,24 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M3" s="0" t="inlineStr">
-        <is>
-          <t>4500000483202610107774759911</t>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="0">
-        <v>51489338</v>
+        <v>52336900</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>兰梅布艺</t>
+          <t>瀚海</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
+          <t>5天 新中老年生活英语营</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -269,17 +269,17 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:16</t>
+          <t>2026-10-30 14:09:56</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>彩虹-抖音1元瑜伽</t>
+          <t>Leon老师-抖音0元</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+          <t>WY-0元英语-微信内外落地页添加</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
@@ -305,21 +305,16 @@
       <c r="L4" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="M4" s="0" t="inlineStr">
-        <is>
-          <t>4500000481202610106676039209</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="0">
-        <v>51489335</v>
+        <v>51489339</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>严伏秀</t>
+          <t>春天来了</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -344,7 +339,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:19</t>
+          <t>2026-10-10 19:47:18</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -374,17 +369,17 @@
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
-          <t>4500000441202610104072684488</t>
+          <t>4500000483202610107774759911</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="0">
-        <v>51489332</v>
+        <v>51489338</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>圣美（罗）</t>
+          <t>兰梅布艺</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -409,7 +404,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:13</t>
+          <t>2026-10-10 19:47:16</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -439,17 +434,17 @@
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
-          <t>4500000439202610103437371955</t>
+          <t>4500000481202610106676039209</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="0">
-        <v>51333559</v>
+        <v>51489335</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>锦瑟流年</t>
+          <t>严伏秀</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -474,7 +469,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:13:07</t>
+          <t>2026-10-10 19:47:19</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -504,17 +499,17 @@
       </c>
       <c r="M7" s="0" t="inlineStr">
         <is>
-          <t>4500000485202610069745624716</t>
+          <t>4500000441202610104072684488</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="0">
-        <v>51333506</v>
+        <v>51489332</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>桐泽</t>
+          <t>圣美（罗）</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -539,7 +534,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:11:49</t>
+          <t>2026-10-10 19:47:13</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -569,17 +564,17 @@
       </c>
       <c r="M8" s="0" t="inlineStr">
         <is>
-          <t>4500000492202610066600573090</t>
+          <t>4500000439202610103437371955</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="0">
-        <v>51333309</v>
+        <v>51333559</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>家乡的美</t>
+          <t>锦瑟流年</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -604,7 +599,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:02:55</t>
+          <t>2026-10-06 20:13:07</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -634,17 +629,17 @@
       </c>
       <c r="M9" s="0" t="inlineStr">
         <is>
-          <t>4500000447202610065339769930</t>
+          <t>4500000485202610069745624716</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="0">
-        <v>51333299</v>
+        <v>51333506</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>老张</t>
+          <t>桐泽</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -669,7 +664,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:02:41</t>
+          <t>2026-10-06 20:11:49</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -699,17 +694,17 @@
       </c>
       <c r="M10" s="0" t="inlineStr">
         <is>
-          <t>4500000477202610062734500506</t>
+          <t>4500000492202610066600573090</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="0">
-        <v>51333244</v>
+        <v>51333309</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>🥀এ᭄半颗糖ꦿ甜💔到伤ོ࿐ᩚ</t>
+          <t>家乡的美</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -734,7 +729,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:00:22</t>
+          <t>2026-10-06 20:02:55</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -764,17 +759,17 @@
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
-          <t>4500000457202610067152483447</t>
+          <t>4500000447202610065339769930</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="0">
-        <v>51333104</v>
+        <v>51333299</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>退休刘大哥</t>
+          <t>老张</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -799,7 +794,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:55:33</t>
+          <t>2026-10-06 20:02:41</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -829,17 +824,17 @@
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>4500000454202610064881956893</t>
+          <t>4500000477202610062734500506</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="0">
-        <v>51333035</v>
+        <v>51333244</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>楊秀淑</t>
+          <t>🥀এ᭄半颗糖ꦿ甜💔到伤ོ࿐ᩚ</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -864,7 +859,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:55:34</t>
+          <t>2026-10-06 20:00:22</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -894,17 +889,17 @@
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
-          <t>4500000487202610062154380210</t>
+          <t>4500000457202610067152483447</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="0">
-        <v>51333012</v>
+        <v>51333104</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>爱美家家纺13478223890</t>
+          <t>退休刘大哥</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -929,7 +924,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:53:01</t>
+          <t>2026-10-06 19:55:33</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -959,17 +954,17 @@
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>
-          <t>4500000494202610066145995028</t>
+          <t>4500000454202610064881956893</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="0">
-        <v>51222028</v>
+        <v>51333035</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>小红</t>
+          <t>楊秀淑</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 20:08:14</t>
+          <t>2026-10-06 19:55:34</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -1024,17 +1019,17 @@
       </c>
       <c r="M15" s="0" t="inlineStr">
         <is>
-          <t>4500000467202610027273134898</t>
+          <t>4500000487202610062154380210</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="0">
-        <v>51221659</v>
+        <v>51333012</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>我只在乎你</t>
+          <t>爱美家家纺13478223890</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -1059,7 +1054,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:54:01</t>
+          <t>2026-10-06 19:53:01</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1089,17 +1084,17 @@
       </c>
       <c r="M16" s="0" t="inlineStr">
         <is>
-          <t>4500000426202610025434647362</t>
+          <t>4500000494202610066145995028</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="0">
-        <v>51221634</v>
+        <v>51222028</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>米奶（葛）</t>
+          <t>小红</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1124,7 +1119,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:19</t>
+          <t>2026-10-02 20:08:14</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -1154,17 +1149,17 @@
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
-          <t>4500000429202610023247688151</t>
+          <t>4500000467202610027273134898</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="0">
-        <v>51221626</v>
+        <v>51221659</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>健康是福</t>
+          <t>我只在乎你</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -1189,7 +1184,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:07</t>
+          <t>2026-10-02 19:54:01</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -1219,17 +1214,17 @@
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
-          <t>4500000478202610025848412155</t>
+          <t>4500000426202610025434647362</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="0">
-        <v>51221623</v>
+        <v>51221634</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>风中雨荷</t>
+          <t>米奶（葛）</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -1254,7 +1249,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:49</t>
+          <t>2026-10-02 19:52:19</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -1284,17 +1279,17 @@
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>
-          <t>4500000485202610022211801630</t>
+          <t>4500000429202610023247688151</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="0">
-        <v>51221622</v>
+        <v>51221626</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>小双子</t>
+          <t>健康是福</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -1319,7 +1314,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:53:38</t>
+          <t>2026-10-02 19:52:07</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1349,17 +1344,17 @@
       </c>
       <c r="M20" s="0" t="inlineStr">
         <is>
-          <t>4500000430202610026316335585</t>
+          <t>4500000478202610025848412155</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="0">
-        <v>51221617</v>
+        <v>51221623</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>A英子</t>
+          <t>风中雨荷</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -1384,7 +1379,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:03</t>
+          <t>2026-10-02 19:51:49</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1414,17 +1409,17 @@
       </c>
       <c r="M21" s="0" t="inlineStr">
         <is>
-          <t>4500000455202610022662444307</t>
+          <t>4500000485202610022211801630</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="0">
-        <v>51221616</v>
+        <v>51221622</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>阿庆</t>
+          <t>小双子</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -1449,7 +1444,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:43</t>
+          <t>2026-10-02 19:53:38</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1479,17 +1474,17 @@
       </c>
       <c r="M22" s="0" t="inlineStr">
         <is>
-          <t>4500000479202610025538878979</t>
+          <t>4500000430202610026316335585</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="0">
-        <v>51221615</v>
+        <v>51221617</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>然然</t>
+          <t>A英子</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:16</t>
+          <t>2026-10-02 19:52:03</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1544,17 +1539,17 @@
       </c>
       <c r="M23" s="0" t="inlineStr">
         <is>
-          <t>4500000458202610029251790963</t>
+          <t>4500000455202610022662444307</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="0">
-        <v>51221614</v>
+        <v>51221616</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>睦然</t>
+          <t>阿庆</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1579,7 +1574,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:55</t>
+          <t>2026-10-02 19:51:43</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1609,17 +1604,17 @@
       </c>
       <c r="M24" s="0" t="inlineStr">
         <is>
-          <t>4500000481202610022649420793</t>
+          <t>4500000479202610025538878979</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="0">
-        <v>51221605</v>
+        <v>51221615</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>程方英13475802198</t>
+          <t>然然</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1644,7 +1639,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:29</t>
+          <t>2026-10-02 19:52:16</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1674,22 +1669,17 @@
       </c>
       <c r="M25" s="0" t="inlineStr">
         <is>
-          <t>4500000427202610028110811278</t>
-        </is>
-      </c>
-      <c r="N25" s="0" t="inlineStr">
-        <is>
-          <t>青岛</t>
+          <t>4500000458202610029251790963</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="0">
-        <v>49457201</v>
+        <v>51221614</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>紫烨</t>
+          <t>睦然</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1714,7 +1704,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:24:21</t>
+          <t>2026-10-02 19:51:55</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1744,17 +1734,17 @@
       </c>
       <c r="M26" s="0" t="inlineStr">
         <is>
-          <t>4500000366202608212918307979</t>
+          <t>4500000481202610022649420793</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="0">
-        <v>49456963</v>
+        <v>51221605</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>月光宝盒🌺</t>
+          <t>程方英13475802198</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1779,7 +1769,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:04:11</t>
+          <t>2026-10-02 19:51:29</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1809,17 +1799,22 @@
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>4500000370202608212773595140</t>
+          <t>4500000427202610028110811278</t>
+        </is>
+      </c>
+      <c r="N27" s="0" t="inlineStr">
+        <is>
+          <t>青岛</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="0">
-        <v>49456951</v>
+        <v>49457201</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>浅浅浅蓝</t>
+          <t>紫烨</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1844,7 +1839,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:03:09</t>
+          <t>2026-08-21 00:24:21</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1874,17 +1869,17 @@
       </c>
       <c r="M28" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608218688440287</t>
+          <t>4500000366202608212918307979</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="0">
-        <v>49451062</v>
+        <v>49456963</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>美丽天使</t>
+          <t>月光宝盒🌺</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -1909,7 +1904,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:04:54</t>
+          <t>2026-08-21 00:04:11</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1939,17 +1934,17 @@
       </c>
       <c r="M29" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608206032862385</t>
+          <t>4500000370202608212773595140</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="0">
-        <v>49451061</v>
+        <v>49456951</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>尹璐-专业设计各类风水画</t>
+          <t>浅浅浅蓝</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -1974,7 +1969,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:04:51</t>
+          <t>2026-08-21 00:03:09</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -2004,17 +1999,17 @@
       </c>
       <c r="M30" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608202974919363</t>
+          <t>4500000333202608218688440287</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="0">
-        <v>49451049</v>
+        <v>49451062</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>曾姐</t>
+          <t>美丽天使</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -2039,7 +2034,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:05:13</t>
+          <t>2026-08-20 21:04:54</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -2069,17 +2064,17 @@
       </c>
       <c r="M31" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608208073638505</t>
+          <t>4500000383202608206032862385</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="0">
-        <v>49380753</v>
+        <v>49451061</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>月亮</t>
+          <t>尹璐-专业设计各类风水画</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -2104,7 +2099,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:10</t>
+          <t>2026-08-20 21:04:51</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -2134,17 +2129,17 @@
       </c>
       <c r="M32" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608199548973720</t>
+          <t>4500000321202608202974919363</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="0">
-        <v>49380751</v>
+        <v>49451049</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>荣兰</t>
+          <t>曾姐</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -2169,7 +2164,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:34</t>
+          <t>2026-08-20 21:05:13</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2199,17 +2194,17 @@
       </c>
       <c r="M33" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608192770223988</t>
+          <t>4500000353202608208073638505</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="0">
-        <v>49380749</v>
+        <v>49380753</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>琴</t>
+          <t>月亮</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -2234,7 +2229,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:06</t>
+          <t>2026-08-19 00:04:10</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2264,17 +2259,17 @@
       </c>
       <c r="M34" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608197088116223</t>
+          <t>4500000340202608199548973720</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="0">
-        <v>49380733</v>
+        <v>49380751</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>风水道士何金权先生18885336852</t>
+          <t>荣兰</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -2299,7 +2294,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:03:55</t>
+          <t>2026-08-19 00:04:34</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2329,17 +2324,17 @@
       </c>
       <c r="M35" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608197323803505</t>
+          <t>4500000376202608192770223988</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="0">
-        <v>49378805</v>
+        <v>49380749</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>心想事成</t>
+          <t>琴</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -2364,7 +2359,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:36:11</t>
+          <t>2026-08-19 00:04:06</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2394,17 +2389,17 @@
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608187136696859</t>
+          <t>4500000365202608197088116223</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="0">
-        <v>49378780</v>
+        <v>49380733</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>ZCL</t>
+          <t>风水道士何金权先生18885336852</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -2429,7 +2424,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:59</t>
+          <t>2026-08-19 00:03:55</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2459,17 +2454,17 @@
       </c>
       <c r="M37" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608185058515299</t>
+          <t>4500000361202608197323803505</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="0">
-        <v>49378769</v>
+        <v>49378805</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>岁月如流水</t>
+          <t>心想事成</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -2494,7 +2489,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:45</t>
+          <t>2026-08-18 22:36:11</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2524,17 +2519,17 @@
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608182677022834</t>
+          <t>4500000316202608187136696859</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="0">
-        <v>49378768</v>
+        <v>49378780</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>天天好心情</t>
+          <t>ZCL</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -2559,7 +2554,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:39</t>
+          <t>2026-08-18 22:34:59</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2589,17 +2584,17 @@
       </c>
       <c r="M39" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608185835240274</t>
+          <t>4500000316202608185058515299</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="0">
-        <v>49375111</v>
+        <v>49378769</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>万事大吉</t>
+          <t>岁月如流水</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -2624,7 +2619,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:05:57</t>
+          <t>2026-08-18 22:34:45</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -2654,17 +2649,17 @@
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608187074952472</t>
+          <t>4500000363202608182677022834</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="0">
-        <v>49375081</v>
+        <v>49378768</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>如鱼得水</t>
+          <t>天天好心情</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -2689,7 +2684,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:04:47</t>
+          <t>2026-08-18 22:34:39</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -2719,17 +2714,17 @@
       </c>
       <c r="M41" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608189110994857</t>
+          <t>4500000345202608185835240274</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="0">
-        <v>49375015</v>
+        <v>49375111</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>母爱</t>
+          <t>万事大吉</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -2754,7 +2749,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:52</t>
+          <t>2026-08-18 21:05:57</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2784,17 +2779,17 @@
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608186111867199</t>
+          <t>4500000344202608187074952472</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="0">
-        <v>49375001</v>
+        <v>49375081</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>郭正平</t>
+          <t>如鱼得水</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -2819,7 +2814,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:41</t>
+          <t>2026-08-18 21:04:47</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2849,17 +2844,17 @@
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608187695923792</t>
+          <t>4500000369202608189110994857</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="0">
-        <v>49375000</v>
+        <v>49375015</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>云    朵</t>
+          <t>母爱</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -2884,7 +2879,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:36</t>
+          <t>2026-08-18 21:03:52</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2914,17 +2909,17 @@
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608184692846233</t>
+          <t>4500000365202608186111867199</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="0">
-        <v>49371969</v>
+        <v>49375001</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>豆棋奶奶</t>
+          <t>郭正平</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -2949,7 +2944,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:53:16</t>
+          <t>2026-08-18 21:03:41</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2979,17 +2974,17 @@
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
-          <t>4500000381202608187462400910</t>
+          <t>4500000358202608187695923792</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="0">
-        <v>49370049</v>
+        <v>49375000</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>熊金娥</t>
+          <t>云    朵</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -3014,7 +3009,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:34:52</t>
+          <t>2026-08-18 21:03:36</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -3044,17 +3039,17 @@
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608186456472403</t>
+          <t>4500000361202608184692846233</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="0">
-        <v>49370024</v>
+        <v>49371969</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>宏娇18906639773</t>
+          <t>豆棋奶奶</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -3079,7 +3074,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:34:43</t>
+          <t>2026-08-18 19:53:16</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -3109,17 +3104,17 @@
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608181915925686</t>
+          <t>4500000381202608187462400910</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="0">
-        <v>49369533</v>
+        <v>49370049</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>周周有钱</t>
+          <t>熊金娥</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -3144,7 +3139,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:32</t>
+          <t>2026-08-18 19:34:52</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -3174,17 +3169,17 @@
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608183864211631</t>
+          <t>4500000343202608186456472403</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="0">
-        <v>49369376</v>
+        <v>49370024</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>王兰允</t>
+          <t>宏娇18906639773</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -3209,7 +3204,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:40</t>
+          <t>2026-08-18 19:34:43</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -3239,17 +3234,17 @@
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
-          <t>4500000372202608185572793801</t>
+          <t>4500000356202608181915925686</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="0">
-        <v>49369344</v>
+        <v>49369533</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>陈</t>
+          <t>周周有钱</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3274,7 +3269,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:15</t>
+          <t>2026-08-18 19:33:32</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -3304,17 +3299,17 @@
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608183479278224</t>
+          <t>4500000324202608183864211631</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="0">
-        <v>49369203</v>
+        <v>49369376</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>静心</t>
+          <t>王兰允</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -3339,7 +3334,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:32:32</t>
+          <t>2026-08-18 19:33:40</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -3369,17 +3364,17 @@
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608182953367773</t>
+          <t>4500000372202608185572793801</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="0">
-        <v>49340095</v>
+        <v>49369344</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>小小</t>
+          <t>陈</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -3404,7 +3399,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:24:20</t>
+          <t>2026-08-18 19:33:15</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -3434,17 +3429,17 @@
       </c>
       <c r="M52" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608185905136033</t>
+          <t>4500000361202608183479278224</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="0">
-        <v>49340080</v>
+        <v>49369203</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>封艳丽</t>
+          <t>静心</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -3469,7 +3464,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:22:59</t>
+          <t>2026-08-18 19:32:32</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3499,17 +3494,17 @@
       </c>
       <c r="M53" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608183466806505</t>
+          <t>4500000377202608182953367773</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="0">
-        <v>49339950</v>
+        <v>49340095</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>家和万事兴</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -3534,7 +3529,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:07</t>
+          <t>2026-08-18 00:24:20</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -3564,22 +3559,17 @@
       </c>
       <c r="M54" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608183266732544</t>
-        </is>
-      </c>
-      <c r="N54" s="0" t="inlineStr">
-        <is>
-          <t>亳州</t>
+          <t>4500000339202608185905136033</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="0">
-        <v>49339947</v>
+        <v>49340080</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>温玉明</t>
+          <t>封艳丽</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -3604,7 +3594,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:58</t>
+          <t>2026-08-18 00:22:59</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -3634,17 +3624,17 @@
       </c>
       <c r="M55" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608181657535231</t>
+          <t>4500000320202608183466806505</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="0">
-        <v>49339943</v>
+        <v>49339950</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>春梅</t>
+          <t>家和万事兴</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -3669,7 +3659,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:49</t>
+          <t>2026-08-18 00:04:07</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -3699,17 +3689,22 @@
       </c>
       <c r="M56" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608182239214659</t>
+          <t>4500000344202608183266732544</t>
+        </is>
+      </c>
+      <c r="N56" s="0" t="inlineStr">
+        <is>
+          <t>亳州</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="0">
-        <v>49339939</v>
+        <v>49339947</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>青青</t>
+          <t>温玉明</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -3734,7 +3729,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:44</t>
+          <t>2026-08-18 00:04:58</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -3764,17 +3759,17 @@
       </c>
       <c r="M57" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608185247886970</t>
+          <t>4500000357202608181657535231</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="0">
-        <v>49339937</v>
+        <v>49339943</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>开心向日葵🌻</t>
+          <t>春梅</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -3799,7 +3794,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:40</t>
+          <t>2026-08-18 00:03:49</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3829,17 +3824,17 @@
       </c>
       <c r="M58" s="0" t="inlineStr">
         <is>
-          <t>4500000319202608184846762524</t>
+          <t>4500000342202608182239214659</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="0">
-        <v>49339936</v>
+        <v>49339939</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>彩之缘</t>
+          <t>青青</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -3864,7 +3859,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:39</t>
+          <t>2026-08-18 00:03:44</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -3894,17 +3889,17 @@
       </c>
       <c r="M59" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608186999829929</t>
+          <t>4500000355202608185247886970</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="0">
-        <v>49339931</v>
+        <v>49339937</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>开心向日葵🌻</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -3929,7 +3924,7 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:24</t>
+          <t>2026-08-18 00:03:40</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -3959,17 +3954,17 @@
       </c>
       <c r="M60" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608186968757749</t>
+          <t>4500000319202608184846762524</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="0">
-        <v>49339929</v>
+        <v>49339936</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>段桂富</t>
+          <t>彩之缘</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -3994,7 +3989,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:06</t>
+          <t>2026-08-18 00:03:39</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -4024,17 +4019,17 @@
       </c>
       <c r="M61" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608189428147476</t>
+          <t>4500000342202608186999829929</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="0">
-        <v>49339923</v>
+        <v>49339931</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>蓝天</t>
+          <t>my</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -4059,7 +4054,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:07</t>
+          <t>2026-08-18 00:03:24</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -4089,17 +4084,17 @@
       </c>
       <c r="M62" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608189060114184</t>
+          <t>4500000383202608186968757749</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="0">
-        <v>49339921</v>
+        <v>49339929</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>陌上花开</t>
+          <t>段桂富</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -4124,7 +4119,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:59</t>
+          <t>2026-08-18 00:04:06</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -4154,17 +4149,17 @@
       </c>
       <c r="M63" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608185881858135</t>
+          <t>4500000349202608189428147476</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="0">
-        <v>49339920</v>
+        <v>49339923</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>A红雨伞玲雪养发馆</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -4189,7 +4184,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:03</t>
+          <t>2026-08-18 00:03:07</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -4219,17 +4214,17 @@
       </c>
       <c r="M64" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608181810150616</t>
+          <t>4500000346202608189060114184</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="0">
-        <v>49339918</v>
+        <v>49339921</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>胡璎桉</t>
+          <t>陌上花开</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -4254,7 +4249,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:05:04</t>
+          <t>2026-08-18 00:03:59</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -4284,17 +4279,17 @@
       </c>
       <c r="M65" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608188854566939</t>
+          <t>4500000353202608185881858135</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="0">
-        <v>49337893</v>
+        <v>49339920</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>郑洁玲</t>
+          <t>A红雨伞玲雪养发馆</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -4319,7 +4314,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:36:14</t>
+          <t>2026-08-18 00:03:03</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4349,17 +4344,17 @@
       </c>
       <c r="M66" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608171736033078</t>
+          <t>4500000344202608181810150616</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="0">
-        <v>49337886</v>
+        <v>49339918</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>浪漫樱花</t>
+          <t>胡璎桉</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -4384,7 +4379,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:44</t>
+          <t>2026-08-18 00:05:04</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4414,17 +4409,17 @@
       </c>
       <c r="M67" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176588884719</t>
+          <t>4500000354202608188854566939</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="0">
-        <v>49337882</v>
+        <v>49337893</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>王仲槐</t>
+          <t>郑洁玲</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -4449,7 +4444,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:25</t>
+          <t>2026-08-17 22:36:14</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -4479,17 +4474,17 @@
       </c>
       <c r="M68" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608171381637652</t>
+          <t>4500000340202608171736033078</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="0">
-        <v>49337868</v>
+        <v>49337886</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>黄建17373719413</t>
+          <t>浪漫樱花</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -4514,7 +4509,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:03</t>
+          <t>2026-08-17 22:35:44</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -4544,17 +4539,17 @@
       </c>
       <c r="M69" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608175713808624</t>
+          <t>4500000362202608176588884719</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="0">
-        <v>49337865</v>
+        <v>49337882</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>晓燕</t>
+          <t>王仲槐</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -4579,7 +4574,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:01</t>
+          <t>2026-08-17 22:35:25</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -4609,17 +4604,17 @@
       </c>
       <c r="M70" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608175538967169</t>
+          <t>4500000339202608171381637652</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="0">
-        <v>49337857</v>
+        <v>49337868</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>真心真意</t>
+          <t>黄建17373719413</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -4644,7 +4639,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:34:43</t>
+          <t>2026-08-17 22:35:03</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -4674,17 +4669,17 @@
       </c>
       <c r="M71" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176387457203</t>
+          <t>4500000357202608175713808624</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="0">
-        <v>49334810</v>
+        <v>49337865</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>candy🧬甘💕</t>
+          <t>晓燕</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -4709,7 +4704,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:25:31</t>
+          <t>2026-08-17 22:35:01</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -4739,17 +4734,17 @@
       </c>
       <c r="M72" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608173665178011</t>
+          <t>4500000380202608175538967169</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="0">
-        <v>49334746</v>
+        <v>49337857</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>雨落弦音</t>
+          <t>真心真意</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -4774,7 +4769,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:24:18</t>
+          <t>2026-08-17 22:34:43</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -4804,17 +4799,17 @@
       </c>
       <c r="M73" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608175925050310</t>
+          <t>4500000362202608176387457203</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="0">
-        <v>49334683</v>
+        <v>49334810</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>🌹六福A413🌹</t>
+          <t>candy🧬甘💕</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -4839,7 +4834,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:23:16</t>
+          <t>2026-08-17 21:25:31</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -4869,17 +4864,17 @@
       </c>
       <c r="M74" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608175320562123</t>
+          <t>4500000379202608173665178011</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="0">
-        <v>49333672</v>
+        <v>49334746</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>☀️知足常乐😊</t>
+          <t>雨落弦音</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -4904,7 +4899,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:44</t>
+          <t>2026-08-17 21:24:18</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -4934,17 +4929,17 @@
       </c>
       <c r="M75" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608178190501918</t>
+          <t>4500000324202608175925050310</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="0">
-        <v>49333665</v>
+        <v>49334683</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>在水一方</t>
+          <t>🌹六福A413🌹</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -4969,7 +4964,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:41</t>
+          <t>2026-08-17 21:23:16</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -4999,17 +4994,17 @@
       </c>
       <c r="M76" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608175675285016</t>
+          <t>4500000337202608175320562123</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="0">
-        <v>49333658</v>
+        <v>49333672</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>牛牛</t>
+          <t>☀️知足常乐😊</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -5034,7 +5029,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:31</t>
+          <t>2026-08-17 21:01:44</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -5064,17 +5059,17 @@
       </c>
       <c r="M77" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608171889470116</t>
+          <t>4500000380202608178190501918</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="0">
-        <v>49333657</v>
+        <v>49333665</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>鲍镇定</t>
+          <t>在水一方</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -5099,7 +5094,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:38</t>
+          <t>2026-08-17 21:01:41</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -5129,17 +5124,17 @@
       </c>
       <c r="M78" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608179201028350</t>
+          <t>4500000333202608175675285016</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="0">
-        <v>49333649</v>
+        <v>49333658</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>:-D开心果O:-)</t>
+          <t>牛牛</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -5164,7 +5159,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:27</t>
+          <t>2026-08-17 21:01:31</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -5194,17 +5189,17 @@
       </c>
       <c r="M79" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608172428227717</t>
+          <t>4500000380202608171889470116</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="0">
-        <v>49333640</v>
+        <v>49333657</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>黛黛</t>
+          <t>鲍镇定</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -5229,7 +5224,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:30</t>
+          <t>2026-08-17 21:01:38</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -5259,17 +5254,17 @@
       </c>
       <c r="M80" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608177275411312</t>
+          <t>4500000321202608179201028350</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="0">
-        <v>49330491</v>
+        <v>49333649</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>兰花草</t>
+          <t>:-D开心果O:-)</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -5294,7 +5289,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:31</t>
+          <t>2026-08-17 21:01:27</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -5324,17 +5319,17 @@
       </c>
       <c r="M81" s="0" t="inlineStr">
         <is>
-          <t>4500000341202608178144232010</t>
+          <t>4500000344202608172428227717</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="0">
-        <v>49330472</v>
+        <v>49333640</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>郝杏月</t>
+          <t>黛黛</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -5359,7 +5354,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:27</t>
+          <t>2026-08-17 21:01:30</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -5389,17 +5384,17 @@
       </c>
       <c r="M82" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608176551746821</t>
+          <t>4500000316202608177275411312</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="0">
-        <v>49330471</v>
+        <v>49330491</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>金泽湖水</t>
+          <t>兰花草</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -5424,7 +5419,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:46</t>
+          <t>2026-08-17 19:53:31</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5454,17 +5449,17 @@
       </c>
       <c r="M83" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608175707490842</t>
+          <t>4500000341202608178144232010</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="0">
-        <v>49330470</v>
+        <v>49330472</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>乐惠</t>
+          <t>郝杏月</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -5489,7 +5484,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:54</t>
+          <t>2026-08-17 19:53:27</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -5519,17 +5514,17 @@
       </c>
       <c r="M84" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608179365238894</t>
+          <t>4500000337202608176551746821</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="0">
-        <v>49302015</v>
+        <v>49330471</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>辰悦</t>
+          <t>金泽湖水</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -5554,7 +5549,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:22:50</t>
+          <t>2026-08-17 19:52:46</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -5584,17 +5579,17 @@
       </c>
       <c r="M85" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608175953744348</t>
+          <t>4500000374202608175707490842</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="0">
-        <v>49301896</v>
+        <v>49330470</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>简简单单</t>
+          <t>乐惠</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -5619,7 +5614,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:05:28</t>
+          <t>2026-08-17 19:52:54</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -5649,17 +5644,17 @@
       </c>
       <c r="M86" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608175217008588</t>
+          <t>4500000347202608179365238894</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="0">
-        <v>49301861</v>
+        <v>49302015</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>小优不忘初心</t>
+          <t>辰悦</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -5684,7 +5679,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:03</t>
+          <t>2026-08-17 00:22:50</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -5714,17 +5709,17 @@
       </c>
       <c r="M87" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608176836637946</t>
+          <t>4500000368202608175953744348</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="0">
-        <v>49301860</v>
+        <v>49301896</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>半夏轻浅</t>
+          <t>简简单单</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -5749,7 +5744,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:08</t>
+          <t>2026-08-17 00:05:28</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -5779,17 +5774,17 @@
       </c>
       <c r="M88" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608175019525500</t>
+          <t>4500000353202608175217008588</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="0">
-        <v>49301859</v>
+        <v>49301861</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>小璇一（龙树门业</t>
+          <t>小优不忘初心</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -5814,7 +5809,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:52</t>
+          <t>2026-08-17 00:04:03</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -5844,17 +5839,17 @@
       </c>
       <c r="M89" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608177884628709</t>
+          <t>4500000330202608176836637946</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="0">
-        <v>49301854</v>
+        <v>49301860</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
+          <t>半夏轻浅</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -5879,7 +5874,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:00</t>
+          <t>2026-08-17 00:04:08</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -5909,17 +5904,17 @@
       </c>
       <c r="M90" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608177813577730</t>
+          <t>4500000338202608175019525500</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="0">
-        <v>49301853</v>
+        <v>49301859</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>祥云母婴春姐</t>
+          <t>小璇一（龙树门业</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -5944,7 +5939,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:49</t>
+          <t>2026-08-17 00:03:52</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -5974,17 +5969,17 @@
       </c>
       <c r="M91" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608178418886316</t>
+          <t>4500000347202608177884628709</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="0">
-        <v>49301852</v>
+        <v>49301854</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>白迎春</t>
+          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -6009,7 +6004,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:46</t>
+          <t>2026-08-17 00:04:00</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -6039,17 +6034,17 @@
       </c>
       <c r="M92" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608174681213879</t>
+          <t>4500000352202608177813577730</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="0">
-        <v>49301850</v>
+        <v>49301853</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>人心易冷</t>
+          <t>祥云母婴春姐</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -6074,7 +6069,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:04</t>
+          <t>2026-08-17 00:03:49</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -6104,17 +6099,17 @@
       </c>
       <c r="M93" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608172769831285</t>
+          <t>4500000337202608178418886316</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="0">
-        <v>49301846</v>
+        <v>49301852</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>心静自然凉</t>
+          <t>白迎春</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -6139,7 +6134,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:51</t>
+          <t>2026-08-17 00:03:46</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -6169,17 +6164,17 @@
       </c>
       <c r="M94" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608177412373514</t>
+          <t>4500000377202608174681213879</t>
         </is>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="0">
-        <v>49301843</v>
+        <v>49301850</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
+          <t>人心易冷</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -6204,7 +6199,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:40</t>
+          <t>2026-08-17 00:04:04</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -6234,17 +6229,17 @@
       </c>
       <c r="M95" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608176220568550</t>
+          <t>4500000349202608172769831285</t>
         </is>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="0">
-        <v>49300670</v>
+        <v>49301846</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>看透人心，</t>
+          <t>心静自然凉</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -6269,7 +6264,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:07</t>
+          <t>2026-08-17 00:03:51</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -6299,17 +6294,17 @@
       </c>
       <c r="M96" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608165434325764</t>
+          <t>4500000354202608177412373514</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="0">
-        <v>49300667</v>
+        <v>49301843</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>童心依旧</t>
+          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -6334,7 +6329,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:03</t>
+          <t>2026-08-17 00:03:40</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -6364,17 +6359,17 @@
       </c>
       <c r="M97" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608161482824495</t>
+          <t>4500000320202608176220568550</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="0">
-        <v>49300135</v>
+        <v>49300670</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>秋韵</t>
+          <t>看透人心，</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -6399,7 +6394,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:34</t>
+          <t>2026-08-16 22:56:07</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -6429,17 +6424,17 @@
       </c>
       <c r="M98" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608167344457159</t>
+          <t>4500000365202608165434325764</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="0">
-        <v>49300112</v>
+        <v>49300667</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>平安福贵</t>
+          <t>童心依旧</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -6464,7 +6459,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:27</t>
+          <t>2026-08-16 22:56:03</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -6494,17 +6489,17 @@
       </c>
       <c r="M99" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608162072183782</t>
+          <t>4500000369202608161482824495</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="0">
-        <v>49300100</v>
+        <v>49300135</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>萱奶奶</t>
+          <t>秋韵</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -6529,7 +6524,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:45</t>
+          <t>2026-08-16 22:36:34</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -6559,17 +6554,17 @@
       </c>
       <c r="M100" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608164279026924</t>
+          <t>4500000322202608167344457159</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="0">
-        <v>49300096</v>
+        <v>49300112</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>泓涧（红健）</t>
+          <t>平安福贵</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -6594,7 +6589,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:31</t>
+          <t>2026-08-16 22:36:27</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -6624,17 +6619,17 @@
       </c>
       <c r="M101" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608161591115326</t>
+          <t>4500000329202608162072183782</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="0">
-        <v>49300095</v>
+        <v>49300100</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>风行云🏇</t>
+          <t>萱奶奶</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -6659,7 +6654,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:13</t>
+          <t>2026-08-16 22:35:45</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -6689,17 +6684,17 @@
       </c>
       <c r="M102" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608165318502823</t>
+          <t>4500000345202608164279026924</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="0">
-        <v>49300083</v>
+        <v>49300096</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>才秀</t>
+          <t>泓涧（红健）</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -6724,7 +6719,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:11</t>
+          <t>2026-08-16 22:35:31</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -6754,22 +6749,17 @@
       </c>
       <c r="M103" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608161669406907</t>
-        </is>
-      </c>
-      <c r="N103" s="0" t="inlineStr">
-        <is>
-          <t>奉贤</t>
+          <t>4500000324202608161591115326</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="0">
-        <v>49300055</v>
+        <v>49300095</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>冰心</t>
+          <t>风行云🏇</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -6794,7 +6784,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:49</t>
+          <t>2026-08-16 22:36:13</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -6824,17 +6814,17 @@
       </c>
       <c r="M104" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608167949730522</t>
+          <t>4500000358202608165318502823</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="0">
-        <v>49300045</v>
+        <v>49300083</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>才秀</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -6859,7 +6849,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:20</t>
+          <t>2026-08-16 22:35:11</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -6889,22 +6879,22 @@
       </c>
       <c r="M105" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608162476754389</t>
+          <t>4500000330202608161669406907</t>
         </is>
       </c>
       <c r="N105" s="0" t="inlineStr">
         <is>
-          <t>荆州</t>
+          <t>奉贤</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="0">
-        <v>49300042</v>
+        <v>49300055</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>赵萍</t>
+          <t>冰心</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -6929,7 +6919,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:13</t>
+          <t>2026-08-16 22:34:49</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -6959,17 +6949,17 @@
       </c>
       <c r="M106" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608168494549151</t>
+          <t>4500000317202608167949730522</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="0">
-        <v>49300034</v>
+        <v>49300045</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>刘华</t>
+          <t>平</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -6994,7 +6984,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:07</t>
+          <t>2026-08-16 22:34:20</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -7024,17 +7014,22 @@
       </c>
       <c r="M107" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608165458621611</t>
+          <t>4500000353202608162476754389</t>
+        </is>
+      </c>
+      <c r="N107" s="0" t="inlineStr">
+        <is>
+          <t>荆州</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="0">
-        <v>49297749</v>
+        <v>49300042</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>沈雨凤</t>
+          <t>赵萍</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -7059,7 +7054,7 @@
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:24</t>
+          <t>2026-08-16 22:34:13</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -7089,17 +7084,17 @@
       </c>
       <c r="M108" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608164415130639</t>
+          <t>4500000346202608168494549151</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="0">
-        <v>49297736</v>
+        <v>49300034</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>莉莉</t>
+          <t>刘华</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -7124,7 +7119,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:09</t>
+          <t>2026-08-16 22:35:07</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -7154,17 +7149,17 @@
       </c>
       <c r="M109" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163428098661</t>
+          <t>4500000333202608165458621611</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="0">
-        <v>49297681</v>
+        <v>49297749</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>一生平安</t>
+          <t>沈雨凤</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -7189,7 +7184,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:46</t>
+          <t>2026-08-16 21:27:24</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -7219,17 +7214,17 @@
       </c>
       <c r="M110" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608163491096965</t>
+          <t>4500000375202608164415130639</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="0">
-        <v>49297679</v>
+        <v>49297736</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>孔平</t>
+          <t>莉莉</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -7254,7 +7249,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:57</t>
+          <t>2026-08-16 21:27:09</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -7284,17 +7279,17 @@
       </c>
       <c r="M111" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608165709204884</t>
+          <t>4500000369202608163428098661</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="0">
-        <v>49296893</v>
+        <v>49297681</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>逍遥仙子</t>
+          <t>一生平安</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -7319,7 +7314,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:30</t>
+          <t>2026-08-16 21:25:46</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -7349,17 +7344,17 @@
       </c>
       <c r="M112" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608167690459739</t>
+          <t>4500000368202608163491096965</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="0">
-        <v>49296884</v>
+        <v>49297679</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>丽红</t>
+          <t>孔平</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -7384,7 +7379,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:16</t>
+          <t>2026-08-16 21:25:57</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -7414,17 +7409,17 @@
       </c>
       <c r="M113" s="0" t="inlineStr">
         <is>
-          <t>4500000332202608162032983613</t>
+          <t>4500000367202608165709204884</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="0">
-        <v>49296874</v>
+        <v>49296893</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>海  角</t>
+          <t>逍遥仙子</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -7449,7 +7444,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:57</t>
+          <t>2026-08-16 21:04:30</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -7479,17 +7474,17 @@
       </c>
       <c r="M114" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163623487097</t>
+          <t>4500000316202608167690459739</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="0">
-        <v>49296864</v>
+        <v>49296884</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>曹景玉</t>
+          <t>丽红</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -7514,7 +7509,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:45</t>
+          <t>2026-08-16 21:04:16</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -7544,17 +7539,17 @@
       </c>
       <c r="M115" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608163779658463</t>
+          <t>4500000332202608162032983613</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="0">
-        <v>49296863</v>
+        <v>49296874</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>石陆萍</t>
+          <t>海  角</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -7579,7 +7574,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:13</t>
+          <t>2026-08-16 21:03:57</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -7609,17 +7604,17 @@
       </c>
       <c r="M116" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608161473678444</t>
+          <t>4500000369202608163623487097</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="0">
-        <v>49296849</v>
+        <v>49296864</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>阿荣</t>
+          <t>曹景玉</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -7644,7 +7639,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:43</t>
+          <t>2026-08-16 21:03:45</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -7674,17 +7669,17 @@
       </c>
       <c r="M117" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608169868333535</t>
+          <t>4500000331202608163779658463</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="0">
-        <v>49296823</v>
+        <v>49296863</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>周少丽</t>
+          <t>石陆萍</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -7709,7 +7704,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:17</t>
+          <t>2026-08-16 21:04:13</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -7739,17 +7734,17 @@
       </c>
       <c r="M118" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608169179019788</t>
+          <t>4500000351202608161473678444</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="0">
-        <v>49296822</v>
+        <v>49296849</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>雨花石</t>
+          <t>阿荣</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -7774,7 +7769,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:16</t>
+          <t>2026-08-16 21:03:43</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -7804,17 +7799,17 @@
       </c>
       <c r="M119" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608166345332381</t>
+          <t>4500000318202608169868333535</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="0">
-        <v>49293860</v>
+        <v>49296823</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>树玲</t>
+          <t>周少丽</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -7839,7 +7834,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:26</t>
+          <t>2026-08-16 21:03:17</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -7869,17 +7864,17 @@
       </c>
       <c r="M120" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608168589310428</t>
+          <t>4500000315202608169179019788</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="0">
-        <v>49293858</v>
+        <v>49296822</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>芬芳</t>
+          <t>雨花石</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -7904,7 +7899,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:42</t>
+          <t>2026-08-16 21:03:16</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -7934,17 +7929,17 @@
       </c>
       <c r="M121" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608162910375128</t>
+          <t>4500000367202608166345332381</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="0">
-        <v>49197594</v>
+        <v>49293860</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>李秀燕健康顾问</t>
+          <t>树玲</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -7969,7 +7964,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:55</t>
+          <t>2026-08-16 19:55:26</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -7999,17 +7994,17 @@
       </c>
       <c r="M122" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608135550322726</t>
+          <t>4500000342202608168589310428</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="0">
-        <v>49197555</v>
+        <v>49293858</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>FXH*</t>
+          <t>芬芳</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -8034,7 +8029,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:10</t>
+          <t>2026-08-16 19:55:42</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
@@ -8064,17 +8059,17 @@
       </c>
       <c r="M123" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608139667116905</t>
+          <t>4500000358202608162910375128</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="0">
-        <v>49197551</v>
+        <v>49197594</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>书英</t>
+          <t>李秀燕健康顾问</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
@@ -8099,7 +8094,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:09</t>
+          <t>2026-08-13 21:55:55</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -8129,17 +8124,17 @@
       </c>
       <c r="M124" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608135183726220</t>
+          <t>4500000383202608135550322726</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="0">
-        <v>49197500</v>
+        <v>49197555</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>求智慧</t>
+          <t>FXH*</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -8164,7 +8159,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:54:20</t>
+          <t>2026-08-13 21:55:10</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -8194,17 +8189,17 @@
       </c>
       <c r="M125" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608136477567012</t>
+          <t>4500000376202608139667116905</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="0">
-        <v>49196660</v>
+        <v>49197551</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>陈书先</t>
+          <t>书英</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -8229,7 +8224,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:55</t>
+          <t>2026-08-13 21:55:09</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -8259,17 +8254,17 @@
       </c>
       <c r="M126" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608137513582005</t>
+          <t>4500000363202608135183726220</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="0">
-        <v>49196649</v>
+        <v>49197500</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>chenchen</t>
+          <t>求智慧</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
@@ -8294,7 +8289,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:37</t>
+          <t>2026-08-13 21:54:20</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -8324,17 +8319,17 @@
       </c>
       <c r="M127" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608131193472561</t>
+          <t>4500000356202608136477567012</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="0">
-        <v>49196616</v>
+        <v>49196660</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>因子</t>
+          <t>陈书先</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -8359,7 +8354,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:34</t>
+          <t>2026-08-13 21:35:55</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -8389,17 +8384,17 @@
       </c>
       <c r="M128" s="0" t="inlineStr">
         <is>
-          <t>4500000381202608131084069069</t>
+          <t>4500000362202608137513582005</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="0">
-        <v>49196580</v>
+        <v>49196649</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>包容</t>
+          <t>chenchen</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -8424,7 +8419,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:49</t>
+          <t>2026-08-13 21:35:37</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -8454,17 +8449,17 @@
       </c>
       <c r="M129" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608134515206220</t>
+          <t>4500000360202608131193472561</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="0">
-        <v>49196556</v>
+        <v>49196616</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>小芳</t>
+          <t>因子</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -8489,7 +8484,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:00</t>
+          <t>2026-08-13 21:35:34</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -8519,17 +8514,17 @@
       </c>
       <c r="M130" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608131586040016</t>
+          <t>4500000381202608131084069069</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="0">
-        <v>49196547</v>
+        <v>49196580</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>雷宁</t>
+          <t>包容</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -8554,7 +8549,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:30</t>
+          <t>2026-08-13 21:34:49</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -8584,17 +8579,17 @@
       </c>
       <c r="M131" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608133116145497</t>
+          <t>4500000329202608134515206220</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="0">
-        <v>49196546</v>
+        <v>49196556</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>兰莓</t>
+          <t>小芳</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -8619,7 +8614,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:56:17</t>
+          <t>2026-08-13 21:34:00</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -8649,17 +8644,17 @@
       </c>
       <c r="M132" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608136989637138</t>
+          <t>4500000380202608131586040016</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="0">
-        <v>49196528</v>
+        <v>49196547</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>赵子睿奶奶</t>
+          <t>雷宁</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
@@ -8684,7 +8679,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:22</t>
+          <t>2026-08-13 21:34:30</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -8714,17 +8709,17 @@
       </c>
       <c r="M133" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608137236789446</t>
+          <t>4500000368202608133116145497</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="0">
-        <v>49196510</v>
+        <v>49196546</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>山岭巨人</t>
+          <t>兰莓</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -8749,7 +8744,7 @@
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:22</t>
+          <t>2026-08-13 21:56:17</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -8779,17 +8774,17 @@
       </c>
       <c r="M134" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608138809307553</t>
+          <t>4500000352202608136989637138</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="0">
-        <v>49196507</v>
+        <v>49196528</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>香字钟培芷</t>
+          <t>赵子睿奶奶</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -8814,7 +8809,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:53</t>
+          <t>2026-08-13 21:33:22</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -8844,17 +8839,17 @@
       </c>
       <c r="M135" s="0" t="inlineStr">
         <is>
-          <t>4500000370202608133660294135</t>
+          <t>4500000345202608137236789446</t>
         </is>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="0">
-        <v>49196498</v>
+        <v>49196510</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>孟光宗</t>
+          <t>山岭巨人</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -8879,7 +8874,7 @@
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:37:14</t>
+          <t>2026-08-13 21:35:22</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -8909,17 +8904,17 @@
       </c>
       <c r="M136" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608138859211736</t>
+          <t>4500000324202608138809307553</t>
         </is>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="0">
-        <v>49196495</v>
+        <v>49196507</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>夏雨晴的妈妈（天发水芹</t>
+          <t>香字钟培芷</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
@@ -8944,7 +8939,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:32:53</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -8974,22 +8969,17 @@
       </c>
       <c r="M137" s="0" t="inlineStr">
         <is>
-          <t>4500000371202608138873102820</t>
-        </is>
-      </c>
-      <c r="N137" s="0" t="inlineStr">
-        <is>
-          <t>湾仔区</t>
+          <t>4500000370202608133660294135</t>
         </is>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="0">
-        <v>49196485</v>
+        <v>49196498</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>法苑文印广告</t>
+          <t>孟光宗</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
@@ -9014,7 +9004,7 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:06</t>
+          <t>2026-08-13 21:37:14</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -9044,17 +9034,17 @@
       </c>
       <c r="M138" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608139506557676</t>
+          <t>4500000363202608138859211736</t>
         </is>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="0">
-        <v>49196481</v>
+        <v>49196495</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>四季果</t>
+          <t>夏雨晴的妈妈（天发水芹</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
@@ -9079,7 +9069,7 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:08</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -9109,17 +9099,22 @@
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608134787426208</t>
+          <t>4500000371202608138873102820</t>
+        </is>
+      </c>
+      <c r="N139" s="0" t="inlineStr">
+        <is>
+          <t>湾仔区</t>
         </is>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="0">
-        <v>49196479</v>
+        <v>49196485</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>仇尚妹</t>
+          <t>法苑文印广告</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -9144,7 +9139,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:43</t>
+          <t>2026-08-13 21:33:06</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -9174,17 +9169,17 @@
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608136810799236</t>
+          <t>4500000379202608139506557676</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="0">
-        <v>49196478</v>
+        <v>49196481</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>A古庄店大新手机卖场库琳琳</t>
+          <t>四季果</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -9209,7 +9204,7 @@
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:42</t>
+          <t>2026-08-13 21:33:08</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -9239,17 +9234,17 @@
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608137311399529</t>
+          <t>4500000335202608134787426208</t>
         </is>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="0">
-        <v>49196473</v>
+        <v>49196479</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>刘玉云机械租赁服务部15905691602</t>
+          <t>仇尚妹</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
@@ -9274,7 +9269,7 @@
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:30</t>
+          <t>2026-08-13 21:32:43</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -9304,17 +9299,17 @@
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608134297741797</t>
+          <t>4500000374202608136810799236</t>
         </is>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="0">
-        <v>49196470</v>
+        <v>49196478</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>众舍康安二手房丽姐</t>
+          <t>A古庄店大新手机卖场库琳琳</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -9339,7 +9334,7 @@
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:28</t>
+          <t>2026-08-13 21:32:42</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -9369,17 +9364,17 @@
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608137489426707</t>
+          <t>4500000373202608137311399529</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="0">
-        <v>49196462</v>
+        <v>49196473</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>欢欢</t>
+          <t>刘玉云机械租赁服务部15905691602</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -9404,7 +9399,7 @@
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:31</t>
+          <t>2026-08-13 21:32:30</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -9434,17 +9429,17 @@
       </c>
       <c r="M144" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608136078541008</t>
+          <t>4500000315202608134297741797</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="0">
-        <v>49196456</v>
+        <v>49196470</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>润花</t>
+          <t>众舍康安二手房丽姐</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -9469,7 +9464,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:32:28</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -9499,17 +9494,17 @@
       </c>
       <c r="M145" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608139285322594</t>
+          <t>4500000325202608137489426707</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="0">
-        <v>49196455</v>
+        <v>49196462</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>风之韵</t>
+          <t>欢欢</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -9534,7 +9529,7 @@
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:34</t>
+          <t>2026-08-13 21:32:31</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -9564,17 +9559,17 @@
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608137054529020</t>
+          <t>4500000382202608136078541008</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="0">
-        <v>49196452</v>
+        <v>49196456</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>开心每一天</t>
+          <t>润花</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -9599,7 +9594,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:40</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -9629,22 +9624,17 @@
       </c>
       <c r="M147" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608131603927208</t>
-        </is>
-      </c>
-      <c r="N147" s="0" t="inlineStr">
-        <is>
-          <t>连云港</t>
+          <t>4500000365202608139285322594</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="0">
-        <v>49196449</v>
+        <v>49196455</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>吉乐常伴</t>
+          <t>风之韵</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -9669,7 +9659,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:32:34</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -9699,17 +9689,17 @@
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608139313739490</t>
+          <t>4500000339202608137054529020</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="0">
-        <v>49196445</v>
+        <v>49196452</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>快乐宝贝</t>
+          <t>开心每一天</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -9734,7 +9724,7 @@
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:15</t>
+          <t>2026-08-13 21:32:40</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -9764,17 +9754,22 @@
       </c>
       <c r="M149" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133056225424</t>
+          <t>4500000327202608131603927208</t>
+        </is>
+      </c>
+      <c r="N149" s="0" t="inlineStr">
+        <is>
+          <t>连云港</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="0">
-        <v>49196441</v>
+        <v>49196449</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>感恩快乐每一天</t>
+          <t>吉乐常伴</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -9799,7 +9794,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:13</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -9829,17 +9824,17 @@
       </c>
       <c r="M150" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608132236113522</t>
+          <t>4500000340202608139313739490</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="0">
-        <v>49196439</v>
+        <v>49196445</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>翰林世家京墨18240001035</t>
+          <t>快乐宝贝</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -9864,7 +9859,7 @@
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:18</t>
+          <t>2026-08-13 21:32:15</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -9894,17 +9889,17 @@
       </c>
       <c r="M151" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608131410776307</t>
+          <t>4500000326202608133056225424</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="0">
-        <v>49196437</v>
+        <v>49196441</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>悦朵宝贝</t>
+          <t>感恩快乐每一天</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
@@ -9929,7 +9924,7 @@
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:06</t>
+          <t>2026-08-13 21:32:13</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -9959,17 +9954,17 @@
       </c>
       <c r="M152" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608135681746747</t>
+          <t>4500000383202608132236113522</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="0">
-        <v>49196435</v>
+        <v>49196439</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>我的幸福</t>
+          <t>翰林世家京墨18240001035</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -9994,7 +9989,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:32:18</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -10024,17 +10019,17 @@
       </c>
       <c r="M153" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608138821842807</t>
+          <t>4500000315202608131410776307</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="0">
-        <v>49196433</v>
+        <v>49196437</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>程胜英</t>
+          <t>悦朵宝贝</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -10059,7 +10054,7 @@
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:33</t>
+          <t>2026-08-13 21:32:06</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -10089,17 +10084,17 @@
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608136558136840</t>
+          <t>4500000343202608135681746747</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="0">
-        <v>49196424</v>
+        <v>49196435</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>甘峰源奶奶</t>
+          <t>我的幸福</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -10124,7 +10119,7 @@
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:16</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -10154,17 +10149,17 @@
       </c>
       <c r="M155" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608139681236972</t>
+          <t>4500000331202608138821842807</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="0">
-        <v>49196412</v>
+        <v>49196433</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>贝贝老妈</t>
+          <t>程胜英</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -10189,7 +10184,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:49</t>
+          <t>2026-08-13 21:32:33</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -10219,17 +10214,17 @@
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608138627203805</t>
+          <t>4500000338202608136558136840</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="0">
-        <v>49196406</v>
+        <v>49196424</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>过好每一天</t>
+          <t>甘峰源奶奶</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -10254,7 +10249,7 @@
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:55</t>
+          <t>2026-08-13 21:32:16</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -10284,17 +10279,17 @@
       </c>
       <c r="M157" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608139484061741</t>
+          <t>4500000374202608139681236972</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="0">
-        <v>49196403</v>
+        <v>49196412</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>迪迪</t>
+          <t>贝贝老妈</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -10319,7 +10314,7 @@
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:58</t>
+          <t>2026-08-13 21:31:49</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -10349,17 +10344,17 @@
       </c>
       <c r="M158" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608138209731181</t>
+          <t>4500000360202608138627203805</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="0">
-        <v>49196399</v>
+        <v>49196406</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>境随心转</t>
+          <t>过好每一天</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -10384,7 +10379,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:47</t>
+          <t>2026-08-13 21:31:55</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -10414,17 +10409,17 @@
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608138946210876</t>
+          <t>4500000384202608139484061741</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="0">
-        <v>49196391</v>
+        <v>49196403</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>💖越来越好💖</t>
+          <t>迪迪</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -10449,7 +10444,7 @@
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:01</t>
+          <t>2026-08-13 21:31:58</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -10479,17 +10474,17 @@
       </c>
       <c r="M160" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133672869122</t>
+          <t>4500000326202608138209731181</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="0">
-        <v>49196390</v>
+        <v>49196399</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>翠翠</t>
+          <t>境随心转</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -10514,7 +10509,7 @@
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:38</t>
+          <t>2026-08-13 21:31:47</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -10544,22 +10539,17 @@
       </c>
       <c r="M161" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608139683947334</t>
-        </is>
-      </c>
-      <c r="N161" s="0" t="inlineStr">
-        <is>
-          <t>广州</t>
+          <t>4500000380202608138946210876</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="0">
-        <v>49196389</v>
+        <v>49196391</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>漫步繁华街</t>
+          <t>💖越来越好💖</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -10584,7 +10574,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:39</t>
+          <t>2026-08-13 21:32:01</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -10614,17 +10604,17 @@
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608135974835236</t>
+          <t>4500000326202608133672869122</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="0">
-        <v>49196385</v>
+        <v>49196390</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>平淡人生🌲</t>
+          <t>翠翠</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -10649,7 +10639,7 @@
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:35</t>
+          <t>2026-08-13 21:31:38</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -10679,17 +10669,22 @@
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608136587117638</t>
+          <t>4500000351202608139683947334</t>
+        </is>
+      </c>
+      <c r="N163" s="0" t="inlineStr">
+        <is>
+          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="0">
-        <v>49196384</v>
+        <v>49196389</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>眼镜灯饰城3楼76号15923959748</t>
+          <t>漫步繁华街</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -10714,7 +10709,7 @@
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:34</t>
+          <t>2026-08-13 21:32:39</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -10744,17 +10739,17 @@
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608139966140440</t>
+          <t>4500000375202608135974835236</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="0">
-        <v>49196383</v>
+        <v>49196385</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>喜枝</t>
+          <t>平淡人生🌲</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -10779,7 +10774,7 @@
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:45</t>
+          <t>2026-08-13 21:31:35</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -10809,17 +10804,17 @@
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608138694510811</t>
+          <t>4500000359202608136587117638</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="0">
-        <v>49155446</v>
+        <v>49196384</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>笑口常开</t>
+          <t>眼镜灯饰城3楼76号15923959748</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
@@ -10844,7 +10839,7 @@
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:36:06</t>
+          <t>2026-08-13 21:31:34</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -10874,17 +10869,17 @@
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608121856487760</t>
+          <t>4500000333202608139966140440</t>
         </is>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="0">
-        <v>49155389</v>
+        <v>49196383</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>奥普郭彦丽13937990394</t>
+          <t>喜枝</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
@@ -10909,7 +10904,7 @@
       </c>
       <c r="G167" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:44</t>
+          <t>2026-08-13 21:31:45</t>
         </is>
       </c>
       <c r="H167" s="0" t="inlineStr">
@@ -10939,17 +10934,17 @@
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608124582542642</t>
+          <t>4500000333202608138694510811</t>
         </is>
       </c>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="0">
-        <v>49155374</v>
+        <v>49155446</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>流星雨文华</t>
+          <t>笑口常开</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
@@ -10974,7 +10969,7 @@
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:26</t>
+          <t>2026-08-12 21:36:06</t>
         </is>
       </c>
       <c r="H168" s="0" t="inlineStr">
@@ -11004,17 +10999,17 @@
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608121430434820</t>
+          <t>4500000376202608121856487760</t>
         </is>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="0">
-        <v>49155368</v>
+        <v>49155389</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>笑对人生</t>
+          <t>奥普郭彦丽13937990394</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
@@ -11039,7 +11034,7 @@
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:56</t>
+          <t>2026-08-12 21:35:44</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -11069,17 +11064,17 @@
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608126193240482</t>
+          <t>4500000324202608124582542642</t>
         </is>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="0">
-        <v>49155365</v>
+        <v>49155374</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>秀</t>
+          <t>流星雨文华</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
@@ -11104,7 +11099,7 @@
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:41</t>
+          <t>2026-08-12 21:35:26</t>
         </is>
       </c>
       <c r="H170" s="0" t="inlineStr">
@@ -11134,17 +11129,17 @@
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608121090433848</t>
+          <t>4500000377202608121430434820</t>
         </is>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="0">
-        <v>49155364</v>
+        <v>49155368</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>冯衣制版18966913385</t>
+          <t>笑对人生</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -11169,7 +11164,7 @@
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:09</t>
+          <t>2026-08-12 21:34:56</t>
         </is>
       </c>
       <c r="H171" s="0" t="inlineStr">
@@ -11199,17 +11194,17 @@
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608122728123344</t>
+          <t>4500000316202608126193240482</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="0">
-        <v>49155363</v>
+        <v>49155365</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>秀</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -11234,7 +11229,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:54</t>
+          <t>2026-08-12 21:34:41</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -11264,17 +11259,17 @@
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608128317430099</t>
+          <t>4500000363202608121090433848</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="0">
-        <v>49155361</v>
+        <v>49155364</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>春华秋实</t>
+          <t>冯衣制版18966913385</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -11299,7 +11294,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:48</t>
+          <t>2026-08-12 21:35:09</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -11329,17 +11324,17 @@
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608121174096033</t>
+          <t>4500000348202608122728123344</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="0">
-        <v>49155359</v>
+        <v>49155363</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>春梅。</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -11364,7 +11359,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:36</t>
+          <t>2026-08-12 21:34:54</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -11394,17 +11389,17 @@
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608123637081551</t>
+          <t>4500000320202608128317430099</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="0">
-        <v>49155344</v>
+        <v>49155361</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>自由人生</t>
+          <t>春华秋实</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -11429,7 +11424,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:25</t>
+          <t>2026-08-12 21:34:48</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -11459,17 +11454,17 @@
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608129865186226</t>
+          <t>4500000346202608121174096033</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="0">
-        <v>49155337</v>
+        <v>49155359</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>红红</t>
+          <t>春梅。</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -11494,7 +11489,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:50</t>
+          <t>2026-08-12 21:34:36</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -11524,17 +11519,17 @@
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608125530964720</t>
+          <t>4500000374202608123637081551</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="0">
-        <v>49155330</v>
+        <v>49155344</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>徐淑香</t>
+          <t>自由人生</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -11559,7 +11554,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:20</t>
+          <t>2026-08-12 21:34:25</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -11589,17 +11584,17 @@
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608124983971576</t>
+          <t>4500000317202608129865186226</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="0">
-        <v>49155314</v>
+        <v>49155337</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>H叶</t>
+          <t>红红</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -11624,7 +11619,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:57</t>
+          <t>2026-08-12 21:34:50</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -11654,17 +11649,17 @@
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608128162955185</t>
+          <t>4500000327202608125530964720</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="0">
-        <v>49155309</v>
+        <v>49155330</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>A0000刘氏修脚红姐</t>
+          <t>徐淑香</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -11689,7 +11684,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:47</t>
+          <t>2026-08-12 21:34:20</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -11719,17 +11714,17 @@
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127176361921</t>
+          <t>4500000359202608124983971576</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="0">
-        <v>49155304</v>
+        <v>49155314</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>万树红</t>
+          <t>H叶</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -11754,7 +11749,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:52</t>
+          <t>2026-08-12 21:33:57</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -11784,17 +11779,17 @@
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608123430987084</t>
+          <t>4500000322202608128162955185</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="0">
-        <v>49155293</v>
+        <v>49155309</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>往事如烟</t>
+          <t>A0000刘氏修脚红姐</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
@@ -11819,7 +11814,7 @@
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:33</t>
+          <t>2026-08-12 21:33:47</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -11849,17 +11844,17 @@
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608121388094535</t>
+          <t>4500000333202608127176361921</t>
         </is>
       </c>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="0">
-        <v>49155283</v>
+        <v>49155304</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>雪洁</t>
+          <t>万树红</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
@@ -11884,7 +11879,7 @@
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:27</t>
+          <t>2026-08-12 21:33:52</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -11914,17 +11909,17 @@
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608125072492429</t>
+          <t>4500000379202608123430987084</t>
         </is>
       </c>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="0">
-        <v>49155274</v>
+        <v>49155293</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>文英</t>
+          <t>往事如烟</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
@@ -11949,7 +11944,7 @@
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:24</t>
+          <t>2026-08-12 21:33:33</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -11979,17 +11974,17 @@
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608127495955817</t>
+          <t>4500000360202608121388094535</t>
         </is>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="0">
-        <v>49155273</v>
+        <v>49155283</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>宫本江</t>
+          <t>雪洁</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
@@ -12014,7 +12009,7 @@
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:27</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -12044,17 +12039,17 @@
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608122111396208</t>
+          <t>4500000369202608125072492429</t>
         </is>
       </c>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="0">
-        <v>49155272</v>
+        <v>49155274</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>悠闲的人</t>
+          <t>文英</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
@@ -12079,7 +12074,7 @@
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:13</t>
+          <t>2026-08-12 21:33:24</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
@@ -12109,17 +12104,17 @@
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608122303219210</t>
+          <t>4500000373202608127495955817</t>
         </is>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="0">
-        <v>49155271</v>
+        <v>49155273</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>幸福人生</t>
+          <t>宫本江</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
@@ -12144,7 +12139,7 @@
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:08</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
@@ -12174,17 +12169,17 @@
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608124799146350</t>
+          <t>4500000346202608122111396208</t>
         </is>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="0">
-        <v>49155270</v>
+        <v>49155272</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>雾里看花</t>
+          <t>悠闲的人</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
@@ -12209,7 +12204,7 @@
       </c>
       <c r="G187" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:15</t>
+          <t>2026-08-12 21:33:13</t>
         </is>
       </c>
       <c r="H187" s="0" t="inlineStr">
@@ -12239,17 +12234,17 @@
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608123995555310</t>
+          <t>4500000331202608122303219210</t>
         </is>
       </c>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="0">
-        <v>49155266</v>
+        <v>49155271</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>清风绕指柔</t>
+          <t>幸福人生</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
@@ -12274,7 +12269,7 @@
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:31</t>
+          <t>2026-08-12 21:34:08</t>
         </is>
       </c>
       <c r="H188" s="0" t="inlineStr">
@@ -12304,17 +12299,17 @@
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127946689166</t>
+          <t>4500000333202608124799146350</t>
         </is>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="0">
-        <v>49155265</v>
+        <v>49155270</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>心想事成南无阿弥陀佛</t>
+          <t>雾里看花</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
@@ -12339,7 +12334,7 @@
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:42</t>
+          <t>2026-08-12 21:33:15</t>
         </is>
       </c>
       <c r="H189" s="0" t="inlineStr">
@@ -12369,17 +12364,17 @@
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608126996164764</t>
+          <t>4500000331202608123995555310</t>
         </is>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="0">
-        <v>49155264</v>
+        <v>49155266</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>刘凤辉</t>
+          <t>清风绕指柔</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
@@ -12404,7 +12399,7 @@
       </c>
       <c r="G190" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:31</t>
         </is>
       </c>
       <c r="H190" s="0" t="inlineStr">
@@ -12434,17 +12429,17 @@
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608124680304775</t>
+          <t>4500000333202608127946689166</t>
         </is>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="0">
-        <v>49155263</v>
+        <v>49155265</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>朱叶</t>
+          <t>心想事成南无阿弥陀佛</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
@@ -12469,7 +12464,7 @@
       </c>
       <c r="G191" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:18</t>
+          <t>2026-08-12 21:33:42</t>
         </is>
       </c>
       <c r="H191" s="0" t="inlineStr">
@@ -12499,17 +12494,17 @@
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608124445297817</t>
+          <t>4500000330202608126996164764</t>
         </is>
       </c>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="0">
-        <v>49155253</v>
+        <v>49155264</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>一顺百顺。好运来</t>
+          <t>刘凤辉</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
@@ -12534,7 +12529,7 @@
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:51</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H192" s="0" t="inlineStr">
@@ -12564,17 +12559,17 @@
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608122909608257</t>
+          <t>4500000330202608124680304775</t>
         </is>
       </c>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="0">
-        <v>49155246</v>
+        <v>49155263</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>陈桂芳</t>
+          <t>朱叶</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
@@ -12599,7 +12594,7 @@
       </c>
       <c r="G193" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:33:18</t>
         </is>
       </c>
       <c r="H193" s="0" t="inlineStr">
@@ -12629,17 +12624,17 @@
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608126828589764</t>
+          <t>4500000345202608124445297817</t>
         </is>
       </c>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="0">
-        <v>49155234</v>
+        <v>49155253</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>黄仲芬15683592716</t>
+          <t>一顺百顺。好运来</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
@@ -12664,7 +12659,7 @@
       </c>
       <c r="G194" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:51</t>
         </is>
       </c>
       <c r="H194" s="0" t="inlineStr">
@@ -12694,17 +12689,17 @@
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608129237945248</t>
+          <t>4500000326202608122909608257</t>
         </is>
       </c>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="0">
-        <v>49155233</v>
+        <v>49155246</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>幸福姐赵会玲</t>
+          <t>陈桂芳</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
@@ -12729,7 +12724,7 @@
       </c>
       <c r="G195" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:04</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H195" s="0" t="inlineStr">
@@ -12759,17 +12754,17 @@
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608128379976752</t>
+          <t>4500000378202608126828589764</t>
         </is>
       </c>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="0">
-        <v>49155230</v>
+        <v>49155234</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>锦鲤果果</t>
+          <t>黄仲芬15683592716</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
@@ -12794,7 +12789,7 @@
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:20</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H196" s="0" t="inlineStr">
@@ -12824,17 +12819,17 @@
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608129199323858</t>
+          <t>4500000325202608129237945248</t>
         </is>
       </c>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="0">
-        <v>49155226</v>
+        <v>49155233</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>戎戎</t>
+          <t>幸福姐赵会玲</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
@@ -12859,7 +12854,7 @@
       </c>
       <c r="G197" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:05</t>
+          <t>2026-08-12 21:34:04</t>
         </is>
       </c>
       <c r="H197" s="0" t="inlineStr">
@@ -12889,17 +12884,17 @@
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608125827170254</t>
+          <t>4500000317202608128379976752</t>
         </is>
       </c>
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="0">
-        <v>49155220</v>
+        <v>49155230</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>阿玉</t>
+          <t>锦鲤果果</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
@@ -12924,7 +12919,7 @@
       </c>
       <c r="G198" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:20</t>
         </is>
       </c>
       <c r="H198" s="0" t="inlineStr">
@@ -12954,17 +12949,17 @@
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608129272259118</t>
+          <t>4500000322202608129199323858</t>
         </is>
       </c>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="0">
-        <v>49155219</v>
+        <v>49155226</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>沉淀、</t>
+          <t>戎戎</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
@@ -12989,7 +12984,7 @@
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:05</t>
         </is>
       </c>
       <c r="H199" s="0" t="inlineStr">
@@ -13019,17 +13014,17 @@
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
-          <t>4500000372202608124305947387</t>
+          <t>4500000331202608125827170254</t>
         </is>
       </c>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="0">
-        <v>49155216</v>
+        <v>49155220</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>晴天</t>
+          <t>阿玉</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
@@ -13054,7 +13049,7 @@
       </c>
       <c r="G200" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H200" s="0" t="inlineStr">
@@ -13084,17 +13079,17 @@
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608122833385690</t>
+          <t>4500000345202608129272259118</t>
         </is>
       </c>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="0">
-        <v>49155210</v>
+        <v>49155219</v>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>开正商行</t>
+          <t>沉淀、</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
@@ -13119,7 +13114,7 @@
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H201" s="0" t="inlineStr">
@@ -13149,17 +13144,17 @@
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608127466098812</t>
+          <t>4500000372202608124305947387</t>
         </is>
       </c>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="0">
-        <v>49155208</v>
+        <v>49155216</v>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>傻傻的幸福</t>
+          <t>晴天</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
@@ -13184,7 +13179,7 @@
       </c>
       <c r="G202" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H202" s="0" t="inlineStr">
@@ -13214,17 +13209,17 @@
       </c>
       <c r="M202" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608122593720010</t>
+          <t>4500000334202608122833385690</t>
         </is>
       </c>
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="0">
-        <v>49155205</v>
+        <v>49155210</v>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>你好</t>
+          <t>开正商行</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
@@ -13249,7 +13244,7 @@
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H203" s="0" t="inlineStr">
@@ -13279,17 +13274,17 @@
       </c>
       <c r="M203" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608122478222937</t>
+          <t>4500000348202608127466098812</t>
         </is>
       </c>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="0">
-        <v>49155203</v>
+        <v>49155208</v>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>一生有你</t>
+          <t>傻傻的幸福</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
@@ -13314,7 +13309,7 @@
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H204" s="0" t="inlineStr">
@@ -13344,17 +13339,17 @@
       </c>
       <c r="M204" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608129324316511</t>
+          <t>4500000378202608122593720010</t>
         </is>
       </c>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="0">
-        <v>49155200</v>
+        <v>49155205</v>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>你好</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
@@ -13379,7 +13374,7 @@
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:09</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H205" s="0" t="inlineStr">
@@ -13409,17 +13404,17 @@
       </c>
       <c r="M205" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608125850014769</t>
+          <t>4500000335202608122478222937</t>
         </is>
       </c>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="0">
-        <v>49155197</v>
+        <v>49155203</v>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>桂芝改名叫张淑玮</t>
+          <t>一生有你</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
@@ -13444,7 +13439,7 @@
       </c>
       <c r="G206" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H206" s="0" t="inlineStr">
@@ -13474,17 +13469,17 @@
       </c>
       <c r="M206" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608121228274851</t>
+          <t>4500000369202608129324316511</t>
         </is>
       </c>
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="0">
-        <v>49155194</v>
+        <v>49155200</v>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>自强不息</t>
+          <t>618</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
@@ -13509,7 +13504,7 @@
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:33:09</t>
         </is>
       </c>
       <c r="H207" s="0" t="inlineStr">
@@ -13539,17 +13534,17 @@
       </c>
       <c r="M207" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608124140031616</t>
+          <t>4500000384202608125850014769</t>
         </is>
       </c>
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="0">
-        <v>49155192</v>
+        <v>49155197</v>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>时光如水</t>
+          <t>桂芝改名叫张淑玮</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
@@ -13574,7 +13569,7 @@
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:03</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H208" s="0" t="inlineStr">
@@ -13604,17 +13599,17 @@
       </c>
       <c r="M208" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608128865933230</t>
+          <t>4500000351202608121228274851</t>
         </is>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="A209" s="0">
-        <v>49155187</v>
+        <v>49155194</v>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>自强不息</t>
         </is>
       </c>
       <c r="C209" s="0" t="inlineStr">
@@ -13639,7 +13634,7 @@
       </c>
       <c r="G209" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H209" s="0" t="inlineStr">
@@ -13669,17 +13664,17 @@
       </c>
       <c r="M209" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608125275144248</t>
+          <t>4500000356202608124140031616</t>
         </is>
       </c>
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="0">
-        <v>49155186</v>
+        <v>49155192</v>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>星辰</t>
+          <t>时光如水</t>
         </is>
       </c>
       <c r="C210" s="0" t="inlineStr">
@@ -13704,7 +13699,7 @@
       </c>
       <c r="G210" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:33:03</t>
         </is>
       </c>
       <c r="H210" s="0" t="inlineStr">
@@ -13734,17 +13729,17 @@
       </c>
       <c r="M210" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608121378976306</t>
+          <t>4500000364202608128865933230</t>
         </is>
       </c>
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="0">
-        <v>49155185</v>
+        <v>49155187</v>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>天津温室大棚光伏厂家18920981728</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="C211" s="0" t="inlineStr">
@@ -13769,7 +13764,7 @@
       </c>
       <c r="G211" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:32</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H211" s="0" t="inlineStr">
@@ -13799,17 +13794,17 @@
       </c>
       <c r="M211" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608125631581660</t>
+          <t>4500000334202608125275144248</t>
         </is>
       </c>
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="0">
-        <v>49155184</v>
+        <v>49155186</v>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>惠民</t>
+          <t>星辰</t>
         </is>
       </c>
       <c r="C212" s="0" t="inlineStr">
@@ -13834,7 +13829,7 @@
       </c>
       <c r="G212" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:08</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H212" s="0" t="inlineStr">
@@ -13864,17 +13859,17 @@
       </c>
       <c r="M212" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608121279528970</t>
+          <t>4500000373202608121378976306</t>
         </is>
       </c>
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="0">
-        <v>49155180</v>
+        <v>49155185</v>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>常青树</t>
+          <t>天津温室大棚光伏厂家18920981728</t>
         </is>
       </c>
       <c r="C213" s="0" t="inlineStr">
@@ -13899,7 +13894,7 @@
       </c>
       <c r="G213" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:06</t>
+          <t>2026-08-12 21:33:32</t>
         </is>
       </c>
       <c r="H213" s="0" t="inlineStr">
@@ -13929,17 +13924,17 @@
       </c>
       <c r="M213" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125426925788</t>
+          <t>4500000318202608125631581660</t>
         </is>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="0">
-        <v>49155178</v>
+        <v>49155184</v>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>玉伟</t>
+          <t>惠民</t>
         </is>
       </c>
       <c r="C214" s="0" t="inlineStr">
@@ -13964,7 +13959,7 @@
       </c>
       <c r="G214" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:33:08</t>
         </is>
       </c>
       <c r="H214" s="0" t="inlineStr">
@@ -13994,17 +13989,17 @@
       </c>
       <c r="M214" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608125205677586</t>
+          <t>4500000355202608121279528970</t>
         </is>
       </c>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="0">
-        <v>49155171</v>
+        <v>49155180</v>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>秦晓娟～中医五官排毒</t>
+          <t>常青树</t>
         </is>
       </c>
       <c r="C215" s="0" t="inlineStr">
@@ -14029,7 +14024,7 @@
       </c>
       <c r="G215" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:06</t>
         </is>
       </c>
       <c r="H215" s="0" t="inlineStr">
@@ -14059,17 +14054,17 @@
       </c>
       <c r="M215" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608129265074581</t>
+          <t>4500000357202608125426925788</t>
         </is>
       </c>
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="0">
-        <v>49155167</v>
+        <v>49155178</v>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>水琴</t>
+          <t>玉伟</t>
         </is>
       </c>
       <c r="C216" s="0" t="inlineStr">
@@ -14094,7 +14089,7 @@
       </c>
       <c r="G216" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H216" s="0" t="inlineStr">
@@ -14124,17 +14119,17 @@
       </c>
       <c r="M216" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608128554791016</t>
+          <t>4500000364202608125205677586</t>
         </is>
       </c>
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="0">
-        <v>49155163</v>
+        <v>49155171</v>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>祥云ಠ_ಠ</t>
+          <t>秦晓娟～中医五官排毒</t>
         </is>
       </c>
       <c r="C217" s="0" t="inlineStr">
@@ -14159,7 +14154,7 @@
       </c>
       <c r="G217" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H217" s="0" t="inlineStr">
@@ -14189,17 +14184,17 @@
       </c>
       <c r="M217" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608126804876906</t>
+          <t>4500000365202608129265074581</t>
         </is>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="A218" s="0">
-        <v>49155162</v>
+        <v>49155167</v>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>雪绒花</t>
+          <t>水琴</t>
         </is>
       </c>
       <c r="C218" s="0" t="inlineStr">
@@ -14224,7 +14219,7 @@
       </c>
       <c r="G218" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H218" s="0" t="inlineStr">
@@ -14254,17 +14249,17 @@
       </c>
       <c r="M218" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608122943306781</t>
+          <t>4500000315202608128554791016</t>
         </is>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="A219" s="0">
-        <v>49155161</v>
+        <v>49155163</v>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>        糖果</t>
+          <t>祥云ಠ_ಠ</t>
         </is>
       </c>
       <c r="C219" s="0" t="inlineStr">
@@ -14289,7 +14284,7 @@
       </c>
       <c r="G219" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H219" s="0" t="inlineStr">
@@ -14319,17 +14314,17 @@
       </c>
       <c r="M219" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608121712400624</t>
+          <t>4500000344202608126804876906</t>
         </is>
       </c>
     </row>
     <row r="220" spans="1:14">
       <c r="A220" s="0">
-        <v>49155157</v>
+        <v>49155162</v>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>流失的岁月</t>
+          <t>雪绒花</t>
         </is>
       </c>
       <c r="C220" s="0" t="inlineStr">
@@ -14354,7 +14349,7 @@
       </c>
       <c r="G220" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:11</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H220" s="0" t="inlineStr">
@@ -14384,17 +14379,17 @@
       </c>
       <c r="M220" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608126379751055</t>
+          <t>4500000343202608122943306781</t>
         </is>
       </c>
     </row>
     <row r="221" spans="1:14">
       <c r="A221" s="0">
-        <v>49155152</v>
+        <v>49155161</v>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>夏末幽荷</t>
+          <t>        糖果</t>
         </is>
       </c>
       <c r="C221" s="0" t="inlineStr">
@@ -14419,7 +14414,7 @@
       </c>
       <c r="G221" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H221" s="0" t="inlineStr">
@@ -14449,17 +14444,17 @@
       </c>
       <c r="M221" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608128669470764</t>
+          <t>4500000384202608121712400624</t>
         </is>
       </c>
     </row>
     <row r="222" spans="1:14">
       <c r="A222" s="0">
-        <v>49155150</v>
+        <v>49155157</v>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>药曼</t>
+          <t>流失的岁月</t>
         </is>
       </c>
       <c r="C222" s="0" t="inlineStr">
@@ -14484,7 +14479,7 @@
       </c>
       <c r="G222" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:33:11</t>
         </is>
       </c>
       <c r="H222" s="0" t="inlineStr">
@@ -14514,17 +14509,17 @@
       </c>
       <c r="M222" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608127294126669</t>
+          <t>4500000379202608126379751055</t>
         </is>
       </c>
     </row>
     <row r="223" spans="1:14">
       <c r="A223" s="0">
-        <v>49155149</v>
+        <v>49155152</v>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>🌺 谭谭🌺</t>
+          <t>夏末幽荷</t>
         </is>
       </c>
       <c r="C223" s="0" t="inlineStr">
@@ -14549,7 +14544,7 @@
       </c>
       <c r="G223" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:58</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H223" s="0" t="inlineStr">
@@ -14579,17 +14574,17 @@
       </c>
       <c r="M223" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608121029117778</t>
+          <t>4500000337202608128669470764</t>
         </is>
       </c>
     </row>
     <row r="224" spans="1:14">
       <c r="A224" s="0">
-        <v>49155148</v>
+        <v>49155150</v>
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
-          <t>王玉(邮局对面卖手机)</t>
+          <t>药曼</t>
         </is>
       </c>
       <c r="C224" s="0" t="inlineStr">
@@ -14614,7 +14609,7 @@
       </c>
       <c r="G224" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H224" s="0" t="inlineStr">
@@ -14644,17 +14639,17 @@
       </c>
       <c r="M224" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608126218721690</t>
+          <t>4500000345202608127294126669</t>
         </is>
       </c>
     </row>
     <row r="225" spans="1:14">
       <c r="A225" s="0">
-        <v>49155147</v>
+        <v>49155149</v>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>美好夕阳</t>
+          <t>🌺 谭谭🌺</t>
         </is>
       </c>
       <c r="C225" s="0" t="inlineStr">
@@ -14679,7 +14674,7 @@
       </c>
       <c r="G225" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:32:58</t>
         </is>
       </c>
       <c r="H225" s="0" t="inlineStr">
@@ -14709,17 +14704,17 @@
       </c>
       <c r="M225" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608128224202725</t>
+          <t>4500000350202608121029117778</t>
         </is>
       </c>
     </row>
     <row r="226" spans="1:14">
       <c r="A226" s="0">
-        <v>49155145</v>
+        <v>49155148</v>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>平凡</t>
+          <t>王玉(邮局对面卖手机)</t>
         </is>
       </c>
       <c r="C226" s="0" t="inlineStr">
@@ -14744,7 +14739,7 @@
       </c>
       <c r="G226" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H226" s="0" t="inlineStr">
@@ -14774,17 +14769,17 @@
       </c>
       <c r="M226" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608122476247171</t>
+          <t>4500000342202608126218721690</t>
         </is>
       </c>
     </row>
     <row r="227" spans="1:14">
       <c r="A227" s="0">
-        <v>49155143</v>
+        <v>49155147</v>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>唐洪</t>
+          <t>美好夕阳</t>
         </is>
       </c>
       <c r="C227" s="0" t="inlineStr">
@@ -14809,7 +14804,7 @@
       </c>
       <c r="G227" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:45</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H227" s="0" t="inlineStr">
@@ -14839,17 +14834,17 @@
       </c>
       <c r="M227" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608125309483592</t>
+          <t>4500000343202608128224202725</t>
         </is>
       </c>
     </row>
     <row r="228" spans="1:14">
       <c r="A228" s="0">
-        <v>49155140</v>
+        <v>49155145</v>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>浅笑</t>
+          <t>平凡</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
@@ -14904,17 +14899,17 @@
       </c>
       <c r="M228" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608123442658613</t>
+          <t>4500000359202608122476247171</t>
         </is>
       </c>
     </row>
     <row r="229" spans="1:14">
       <c r="A229" s="0">
-        <v>49155137</v>
+        <v>49155143</v>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>梅放芳香</t>
+          <t>唐洪</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
@@ -14939,7 +14934,7 @@
       </c>
       <c r="G229" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:32:45</t>
         </is>
       </c>
       <c r="H229" s="0" t="inlineStr">
@@ -14969,17 +14964,17 @@
       </c>
       <c r="M229" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608127843962862</t>
+          <t>4500000350202608125309483592</t>
         </is>
       </c>
     </row>
     <row r="230" spans="1:14">
       <c r="A230" s="0">
-        <v>49155135</v>
+        <v>49155140</v>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>吴素华</t>
+          <t>浅笑</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
@@ -15004,7 +14999,7 @@
       </c>
       <c r="G230" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H230" s="0" t="inlineStr">
@@ -15034,17 +15029,17 @@
       </c>
       <c r="M230" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608124292727044</t>
+          <t>4500000360202608123442658613</t>
         </is>
       </c>
     </row>
     <row r="231" spans="1:14">
       <c r="A231" s="0">
-        <v>49155132</v>
+        <v>49155137</v>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
+          <t>梅放芳香</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
@@ -15069,7 +15064,7 @@
       </c>
       <c r="G231" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H231" s="0" t="inlineStr">
@@ -15099,17 +15094,17 @@
       </c>
       <c r="M231" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608123141162109</t>
+          <t>4500000356202608127843962862</t>
         </is>
       </c>
     </row>
     <row r="232" spans="1:14">
       <c r="A232" s="0">
-        <v>49155131</v>
+        <v>49155135</v>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>瓷星.</t>
+          <t>吴素华</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
@@ -15134,7 +15129,7 @@
       </c>
       <c r="G232" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H232" s="0" t="inlineStr">
@@ -15164,17 +15159,17 @@
       </c>
       <c r="M232" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608121548709297</t>
+          <t>4500000339202608124292727044</t>
         </is>
       </c>
     </row>
     <row r="233" spans="1:14">
       <c r="A233" s="0">
-        <v>49155129</v>
+        <v>49155132</v>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>妈咪宝贝</t>
+          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
         </is>
       </c>
       <c r="C233" s="0" t="inlineStr">
@@ -15199,7 +15194,7 @@
       </c>
       <c r="G233" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:42</t>
+          <t>2026-08-12 21:32:46</t>
         </is>
       </c>
       <c r="H233" s="0" t="inlineStr">
@@ -15229,17 +15224,17 @@
       </c>
       <c r="M233" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608127726342481</t>
+          <t>4500000322202608123141162109</t>
         </is>
       </c>
     </row>
     <row r="234" spans="1:14">
       <c r="A234" s="0">
-        <v>49155128</v>
+        <v>49155131</v>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>愿结天下有缘人</t>
+          <t>瓷星.</t>
         </is>
       </c>
       <c r="C234" s="0" t="inlineStr">
@@ -15264,7 +15259,7 @@
       </c>
       <c r="G234" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H234" s="0" t="inlineStr">
@@ -15294,17 +15289,17 @@
       </c>
       <c r="M234" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608128699617090</t>
+          <t>4500000383202608121548709297</t>
         </is>
       </c>
     </row>
     <row r="235" spans="1:14">
       <c r="A235" s="0">
-        <v>49155124</v>
+        <v>49155129</v>
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
-          <t>勿忘初心</t>
+          <t>妈咪宝贝</t>
         </is>
       </c>
       <c r="C235" s="0" t="inlineStr">
@@ -15329,7 +15324,7 @@
       </c>
       <c r="G235" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:42</t>
         </is>
       </c>
       <c r="H235" s="0" t="inlineStr">
@@ -15359,17 +15354,17 @@
       </c>
       <c r="M235" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608128217629837</t>
+          <t>4500000347202608127726342481</t>
         </is>
       </c>
     </row>
     <row r="236" spans="1:14">
       <c r="A236" s="0">
-        <v>49155123</v>
+        <v>49155128</v>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>芳草天涯</t>
+          <t>愿结天下有缘人</t>
         </is>
       </c>
       <c r="C236" s="0" t="inlineStr">
@@ -15394,7 +15389,7 @@
       </c>
       <c r="G236" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:46</t>
         </is>
       </c>
       <c r="H236" s="0" t="inlineStr">
@@ -15424,22 +15419,17 @@
       </c>
       <c r="M236" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608123653997556</t>
-        </is>
-      </c>
-      <c r="N236" s="0" t="inlineStr">
-        <is>
-          <t>合肥</t>
+          <t>4500000321202608128699617090</t>
         </is>
       </c>
     </row>
     <row r="237" spans="1:14">
       <c r="A237" s="0">
-        <v>49155120</v>
+        <v>49155124</v>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>记忆中的你</t>
+          <t>勿忘初心</t>
         </is>
       </c>
       <c r="C237" s="0" t="inlineStr">
@@ -15464,7 +15454,7 @@
       </c>
       <c r="G237" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:53</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H237" s="0" t="inlineStr">
@@ -15494,17 +15484,17 @@
       </c>
       <c r="M237" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608124401684219</t>
+          <t>4500000373202608128217629837</t>
         </is>
       </c>
     </row>
     <row r="238" spans="1:14">
       <c r="A238" s="0">
-        <v>49155114</v>
+        <v>49155123</v>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>微笑取暖</t>
+          <t>芳草天涯</t>
         </is>
       </c>
       <c r="C238" s="0" t="inlineStr">
@@ -15529,7 +15519,7 @@
       </c>
       <c r="G238" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:38</t>
+          <t>2026-08-12 21:32:32</t>
         </is>
       </c>
       <c r="H238" s="0" t="inlineStr">
@@ -15559,17 +15549,22 @@
       </c>
       <c r="M238" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608121874803628</t>
+          <t>4500000321202608123653997556</t>
+        </is>
+      </c>
+      <c r="N238" s="0" t="inlineStr">
+        <is>
+          <t>合肥</t>
         </is>
       </c>
     </row>
     <row r="239" spans="1:14">
       <c r="A239" s="0">
-        <v>49155112</v>
+        <v>49155120</v>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>净心李芸</t>
+          <t>记忆中的你</t>
         </is>
       </c>
       <c r="C239" s="0" t="inlineStr">
@@ -15594,7 +15589,7 @@
       </c>
       <c r="G239" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:33</t>
+          <t>2026-08-12 21:32:53</t>
         </is>
       </c>
       <c r="H239" s="0" t="inlineStr">
@@ -15624,17 +15619,17 @@
       </c>
       <c r="M239" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608126115898528</t>
+          <t>4500000326202608124401684219</t>
         </is>
       </c>
     </row>
     <row r="240" spans="1:14">
       <c r="A240" s="0">
-        <v>49155108</v>
+        <v>49155114</v>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>衡澜</t>
+          <t>微笑取暖</t>
         </is>
       </c>
       <c r="C240" s="0" t="inlineStr">
@@ -15659,7 +15654,7 @@
       </c>
       <c r="G240" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:33:38</t>
         </is>
       </c>
       <c r="H240" s="0" t="inlineStr">
@@ -15689,17 +15684,17 @@
       </c>
       <c r="M240" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608128833814214</t>
+          <t>4500000325202608121874803628</t>
         </is>
       </c>
     </row>
     <row r="241" spans="1:14">
       <c r="A241" s="0">
-        <v>49155098</v>
+        <v>49155112</v>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>珂</t>
+          <t>净心李芸</t>
         </is>
       </c>
       <c r="C241" s="0" t="inlineStr">
@@ -15724,7 +15719,7 @@
       </c>
       <c r="G241" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:39</t>
+          <t>2026-08-12 21:32:33</t>
         </is>
       </c>
       <c r="H241" s="0" t="inlineStr">
@@ -15754,17 +15749,17 @@
       </c>
       <c r="M241" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608128766183266</t>
+          <t>4500000351202608126115898528</t>
         </is>
       </c>
     </row>
     <row r="242" spans="1:14">
       <c r="A242" s="0">
-        <v>49155095</v>
+        <v>49155108</v>
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
-          <t>平安保险~王家宝</t>
+          <t>衡澜</t>
         </is>
       </c>
       <c r="C242" s="0" t="inlineStr">
@@ -15789,7 +15784,7 @@
       </c>
       <c r="G242" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:32:32</t>
         </is>
       </c>
       <c r="H242" s="0" t="inlineStr">
@@ -15819,17 +15814,17 @@
       </c>
       <c r="M242" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608129139460754</t>
+          <t>4500000360202608128833814214</t>
         </is>
       </c>
     </row>
     <row r="243" spans="1:14">
       <c r="A243" s="0">
-        <v>49155092</v>
+        <v>49155098</v>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>爱情海</t>
+          <t>珂</t>
         </is>
       </c>
       <c r="C243" s="0" t="inlineStr">
@@ -15854,7 +15849,7 @@
       </c>
       <c r="G243" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:23</t>
+          <t>2026-08-12 21:32:39</t>
         </is>
       </c>
       <c r="H243" s="0" t="inlineStr">
@@ -15884,17 +15879,17 @@
       </c>
       <c r="M243" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125918396999</t>
+          <t>4500000344202608128766183266</t>
         </is>
       </c>
     </row>
     <row r="244" spans="1:14">
       <c r="A244" s="0">
-        <v>49155090</v>
+        <v>49155095</v>
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
-          <t>三月桃花</t>
+          <t>平安保险~王家宝</t>
         </is>
       </c>
       <c r="C244" s="0" t="inlineStr">
@@ -15919,7 +15914,7 @@
       </c>
       <c r="G244" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:26</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H244" s="0" t="inlineStr">
@@ -15949,70 +15944,200 @@
       </c>
       <c r="M244" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608128744277768</t>
+          <t>4500000321202608129139460754</t>
         </is>
       </c>
     </row>
     <row r="245" spans="1:14">
       <c r="A245" s="0">
+        <v>49155092</v>
+      </c>
+      <c r="B245" s="0" t="inlineStr">
+        <is>
+          <t>爱情海</t>
+        </is>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D245" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E245" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F245" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G245" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:23</t>
+        </is>
+      </c>
+      <c r="H245" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J245" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K245" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L245" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M245" s="0" t="inlineStr">
+        <is>
+          <t>4500000357202608125918396999</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" spans="1:14">
+      <c r="A246" s="0">
+        <v>49155090</v>
+      </c>
+      <c r="B246" s="0" t="inlineStr">
+        <is>
+          <t>三月桃花</t>
+        </is>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D246" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E246" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F246" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G246" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:26</t>
+        </is>
+      </c>
+      <c r="H246" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J246" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K246" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L246" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M246" s="0" t="inlineStr">
+        <is>
+          <t>4500000382202608128744277768</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" spans="1:14">
+      <c r="A247" s="0">
         <v>49155088</v>
       </c>
-      <c r="B245" s="0" t="inlineStr">
+      <c r="B247" s="0" t="inlineStr">
         <is>
           <t>绘兰艺术李老师</t>
         </is>
       </c>
-      <c r="C245" s="0" t="inlineStr">
-        <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
-        </is>
-      </c>
-      <c r="D245" s="0" t="inlineStr">
-        <is>
-          <t>训练营</t>
-        </is>
-      </c>
-      <c r="E245" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="F245" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="G245" s="0" t="inlineStr">
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F247" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G247" s="0" t="inlineStr">
         <is>
           <t>2026-08-12 21:32:20</t>
         </is>
       </c>
-      <c r="H245" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I245" s="0" t="inlineStr">
-        <is>
-          <t>彩虹-抖音1元瑜伽</t>
-        </is>
-      </c>
-      <c r="J245" s="0" t="inlineStr">
-        <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
-        </is>
-      </c>
-      <c r="K245" s="0" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="L245" s="0" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M245" s="0" t="inlineStr">
+      <c r="H247" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J247" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K247" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L247" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M247" s="0" t="inlineStr">
         <is>
           <t>4500000358202608128940402527</t>
         </is>

--- a/data/exports/王颖瑜伽/dist_order_2026-10-30.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-10-30.xlsx
@@ -125,11 +125,11 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="0">
-        <v>52340887</v>
+        <v>52352597</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>谭浩</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -154,7 +154,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-10-30 16:34:25</t>
+          <t>2026-10-30 21:45:54</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -164,7 +164,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>获客助手自动生成订单-Leon老师-抖音-2832</t>
+          <t>Leon老师-抖音</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -174,7 +174,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>获客助手加好友</t>
+          <t>微信支付</t>
         </is>
       </c>
       <c r="L2" s="0" t="inlineStr">
@@ -185,11 +185,11 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="0">
-        <v>52340471</v>
+        <v>52351867</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Amy_婷大小姐</t>
+          <t>Hc</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -214,7 +214,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2026-10-30 16:15:33</t>
+          <t>2026-10-30 21:32:19</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -240,21 +240,16 @@
       <c r="L3" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N3" s="0" t="inlineStr">
-        <is>
-          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="0">
-        <v>52336900</v>
+        <v>52345022</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>瀚海</t>
+          <t>月亮之吻</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -279,7 +274,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-10-30 14:09:56</t>
+          <t>2026-10-30 19:06:03</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -289,7 +284,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>Leon老师-抖音0元</t>
+          <t>获客助手自动生成订单-Leon老师-抖音-2832</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -299,7 +294,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
@@ -310,16 +305,16 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="0">
-        <v>51489339</v>
+        <v>52340887</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>春天来了</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
+          <t>5天 新中老年生活英语营</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -329,17 +324,17 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:18</t>
+          <t>2026-10-30 16:34:25</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -349,42 +344,37 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>彩虹-抖音1元瑜伽</t>
+          <t>获客助手自动生成订单-Leon老师-抖音-2832</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+          <t>WY-0元英语-微信内外落地页添加</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="M5" s="0" t="inlineStr">
-        <is>
-          <t>4500000483202610107774759911</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="0">
-        <v>51489338</v>
+        <v>52340471</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>兰梅布艺</t>
+          <t>Amy_婷大小姐</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
+          <t>5天 新中老年生活英语营</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -394,17 +384,17 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:16</t>
+          <t>2026-10-30 16:15:33</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -414,17 +404,17 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t>彩虹-抖音1元瑜伽</t>
+          <t>获客助手自动生成订单-Leon老师-抖音-2832</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+          <t>WY-0元英语-微信内外落地页添加</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
@@ -432,24 +422,24 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M6" s="0" t="inlineStr">
-        <is>
-          <t>4500000481202610106676039209</t>
+      <c r="N6" s="0" t="inlineStr">
+        <is>
+          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="0">
-        <v>51489335</v>
+        <v>52336900</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>严伏秀</t>
+          <t>瀚海</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
+          <t>5天 新中老年生活英语营</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -459,17 +449,17 @@
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>￥1</t>
+          <t>￥0</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:19</t>
+          <t>2026-10-30 14:09:56</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -479,12 +469,12 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>彩虹-抖音1元瑜伽</t>
+          <t>Leon老师-抖音0元</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+          <t>WY-0元英语-微信内外落地页添加</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
@@ -495,21 +485,16 @@
       <c r="L7" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="M7" s="0" t="inlineStr">
-        <is>
-          <t>4500000441202610104072684488</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="0">
-        <v>51489332</v>
+        <v>51489339</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>圣美（罗）</t>
+          <t>春天来了</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -534,7 +519,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-10-10 19:47:13</t>
+          <t>2026-10-10 19:47:18</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -564,17 +549,17 @@
       </c>
       <c r="M8" s="0" t="inlineStr">
         <is>
-          <t>4500000439202610103437371955</t>
+          <t>4500000483202610107774759911</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="0">
-        <v>51333559</v>
+        <v>51489338</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>锦瑟流年</t>
+          <t>兰梅布艺</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -599,7 +584,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:13:07</t>
+          <t>2026-10-10 19:47:16</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -629,17 +614,17 @@
       </c>
       <c r="M9" s="0" t="inlineStr">
         <is>
-          <t>4500000485202610069745624716</t>
+          <t>4500000481202610106676039209</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="0">
-        <v>51333506</v>
+        <v>51489335</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>桐泽</t>
+          <t>严伏秀</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -664,7 +649,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:11:49</t>
+          <t>2026-10-10 19:47:19</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -694,17 +679,17 @@
       </c>
       <c r="M10" s="0" t="inlineStr">
         <is>
-          <t>4500000492202610066600573090</t>
+          <t>4500000441202610104072684488</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="0">
-        <v>51333309</v>
+        <v>51489332</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>家乡的美</t>
+          <t>圣美（罗）</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -729,7 +714,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:02:55</t>
+          <t>2026-10-10 19:47:13</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -759,17 +744,17 @@
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
-          <t>4500000447202610065339769930</t>
+          <t>4500000439202610103437371955</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="0">
-        <v>51333299</v>
+        <v>51333559</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>老张</t>
+          <t>锦瑟流年</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -794,7 +779,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:02:41</t>
+          <t>2026-10-06 20:13:07</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -824,17 +809,17 @@
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>4500000477202610062734500506</t>
+          <t>4500000485202610069745624716</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="0">
-        <v>51333244</v>
+        <v>51333506</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>🥀এ᭄半颗糖ꦿ甜💔到伤ོ࿐ᩚ</t>
+          <t>桐泽</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -859,7 +844,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 20:00:22</t>
+          <t>2026-10-06 20:11:49</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -889,17 +874,17 @@
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
-          <t>4500000457202610067152483447</t>
+          <t>4500000492202610066600573090</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="0">
-        <v>51333104</v>
+        <v>51333309</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>退休刘大哥</t>
+          <t>家乡的美</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -924,7 +909,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:55:33</t>
+          <t>2026-10-06 20:02:55</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -954,17 +939,17 @@
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>
-          <t>4500000454202610064881956893</t>
+          <t>4500000447202610065339769930</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="0">
-        <v>51333035</v>
+        <v>51333299</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>楊秀淑</t>
+          <t>老张</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -989,7 +974,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:55:34</t>
+          <t>2026-10-06 20:02:41</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -1019,17 +1004,17 @@
       </c>
       <c r="M15" s="0" t="inlineStr">
         <is>
-          <t>4500000487202610062154380210</t>
+          <t>4500000477202610062734500506</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="0">
-        <v>51333012</v>
+        <v>51333244</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>爱美家家纺13478223890</t>
+          <t>🥀এ᭄半颗糖ꦿ甜💔到伤ོ࿐ᩚ</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -1054,7 +1039,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>2026-10-06 19:53:01</t>
+          <t>2026-10-06 20:00:22</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1084,17 +1069,17 @@
       </c>
       <c r="M16" s="0" t="inlineStr">
         <is>
-          <t>4500000494202610066145995028</t>
+          <t>4500000457202610067152483447</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="0">
-        <v>51222028</v>
+        <v>51333104</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>小红</t>
+          <t>退休刘大哥</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1119,7 +1104,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 20:08:14</t>
+          <t>2026-10-06 19:55:33</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -1149,17 +1134,17 @@
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
-          <t>4500000467202610027273134898</t>
+          <t>4500000454202610064881956893</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="0">
-        <v>51221659</v>
+        <v>51333035</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>我只在乎你</t>
+          <t>楊秀淑</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -1184,7 +1169,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:54:01</t>
+          <t>2026-10-06 19:55:34</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -1214,17 +1199,17 @@
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
-          <t>4500000426202610025434647362</t>
+          <t>4500000487202610062154380210</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="0">
-        <v>51221634</v>
+        <v>51333012</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>米奶（葛）</t>
+          <t>爱美家家纺13478223890</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -1249,7 +1234,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:19</t>
+          <t>2026-10-06 19:53:01</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -1279,17 +1264,17 @@
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>
-          <t>4500000429202610023247688151</t>
+          <t>4500000494202610066145995028</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="0">
-        <v>51221626</v>
+        <v>51222028</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>健康是福</t>
+          <t>小红</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -1314,7 +1299,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:07</t>
+          <t>2026-10-02 20:08:14</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1344,17 +1329,17 @@
       </c>
       <c r="M20" s="0" t="inlineStr">
         <is>
-          <t>4500000478202610025848412155</t>
+          <t>4500000467202610027273134898</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="0">
-        <v>51221623</v>
+        <v>51221659</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>风中雨荷</t>
+          <t>我只在乎你</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -1379,7 +1364,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:49</t>
+          <t>2026-10-02 19:54:01</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1409,17 +1394,17 @@
       </c>
       <c r="M21" s="0" t="inlineStr">
         <is>
-          <t>4500000485202610022211801630</t>
+          <t>4500000426202610025434647362</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="0">
-        <v>51221622</v>
+        <v>51221634</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>小双子</t>
+          <t>米奶（葛）</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -1444,7 +1429,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:53:38</t>
+          <t>2026-10-02 19:52:19</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1474,17 +1459,17 @@
       </c>
       <c r="M22" s="0" t="inlineStr">
         <is>
-          <t>4500000430202610026316335585</t>
+          <t>4500000429202610023247688151</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="0">
-        <v>51221617</v>
+        <v>51221626</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>A英子</t>
+          <t>健康是福</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -1509,7 +1494,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:03</t>
+          <t>2026-10-02 19:52:07</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1539,17 +1524,17 @@
       </c>
       <c r="M23" s="0" t="inlineStr">
         <is>
-          <t>4500000455202610022662444307</t>
+          <t>4500000478202610025848412155</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="0">
-        <v>51221616</v>
+        <v>51221623</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>阿庆</t>
+          <t>风中雨荷</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1574,7 +1559,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:43</t>
+          <t>2026-10-02 19:51:49</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1604,17 +1589,17 @@
       </c>
       <c r="M24" s="0" t="inlineStr">
         <is>
-          <t>4500000479202610025538878979</t>
+          <t>4500000485202610022211801630</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="0">
-        <v>51221615</v>
+        <v>51221622</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>然然</t>
+          <t>小双子</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1639,7 +1624,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:52:16</t>
+          <t>2026-10-02 19:53:38</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1669,17 +1654,17 @@
       </c>
       <c r="M25" s="0" t="inlineStr">
         <is>
-          <t>4500000458202610029251790963</t>
+          <t>4500000430202610026316335585</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="0">
-        <v>51221614</v>
+        <v>51221617</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>睦然</t>
+          <t>A英子</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1704,7 +1689,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:55</t>
+          <t>2026-10-02 19:52:03</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1734,17 +1719,17 @@
       </c>
       <c r="M26" s="0" t="inlineStr">
         <is>
-          <t>4500000481202610022649420793</t>
+          <t>4500000455202610022662444307</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="0">
-        <v>51221605</v>
+        <v>51221616</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>程方英13475802198</t>
+          <t>阿庆</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1769,7 +1754,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>2026-10-02 19:51:29</t>
+          <t>2026-10-02 19:51:43</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1799,22 +1784,17 @@
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>4500000427202610028110811278</t>
-        </is>
-      </c>
-      <c r="N27" s="0" t="inlineStr">
-        <is>
-          <t>青岛</t>
+          <t>4500000479202610025538878979</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="0">
-        <v>49457201</v>
+        <v>51221615</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>紫烨</t>
+          <t>然然</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1839,7 +1819,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:24:21</t>
+          <t>2026-10-02 19:52:16</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1869,17 +1849,17 @@
       </c>
       <c r="M28" s="0" t="inlineStr">
         <is>
-          <t>4500000366202608212918307979</t>
+          <t>4500000458202610029251790963</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="0">
-        <v>49456963</v>
+        <v>51221614</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>月光宝盒🌺</t>
+          <t>睦然</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -1904,7 +1884,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:04:11</t>
+          <t>2026-10-02 19:51:55</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1934,17 +1914,17 @@
       </c>
       <c r="M29" s="0" t="inlineStr">
         <is>
-          <t>4500000370202608212773595140</t>
+          <t>4500000481202610022649420793</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="0">
-        <v>49456951</v>
+        <v>51221605</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>浅浅浅蓝</t>
+          <t>程方英13475802198</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -1969,7 +1949,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 00:03:09</t>
+          <t>2026-10-02 19:51:29</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -1999,17 +1979,22 @@
       </c>
       <c r="M30" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608218688440287</t>
+          <t>4500000427202610028110811278</t>
+        </is>
+      </c>
+      <c r="N30" s="0" t="inlineStr">
+        <is>
+          <t>青岛</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="0">
-        <v>49451062</v>
+        <v>49457201</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>美丽天使</t>
+          <t>紫烨</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -2034,7 +2019,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:04:54</t>
+          <t>2026-08-21 00:24:21</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -2064,17 +2049,17 @@
       </c>
       <c r="M31" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608206032862385</t>
+          <t>4500000366202608212918307979</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="0">
-        <v>49451061</v>
+        <v>49456963</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>尹璐-专业设计各类风水画</t>
+          <t>月光宝盒🌺</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -2099,7 +2084,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:04:51</t>
+          <t>2026-08-21 00:04:11</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -2129,17 +2114,17 @@
       </c>
       <c r="M32" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608202974919363</t>
+          <t>4500000370202608212773595140</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="0">
-        <v>49451049</v>
+        <v>49456951</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>曾姐</t>
+          <t>浅浅浅蓝</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -2164,7 +2149,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 21:05:13</t>
+          <t>2026-08-21 00:03:09</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2194,17 +2179,17 @@
       </c>
       <c r="M33" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608208073638505</t>
+          <t>4500000333202608218688440287</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="0">
-        <v>49380753</v>
+        <v>49451062</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>月亮</t>
+          <t>美丽天使</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -2229,7 +2214,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:10</t>
+          <t>2026-08-20 21:04:54</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2259,17 +2244,17 @@
       </c>
       <c r="M34" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608199548973720</t>
+          <t>4500000383202608206032862385</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="0">
-        <v>49380751</v>
+        <v>49451061</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>荣兰</t>
+          <t>尹璐-专业设计各类风水画</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -2294,7 +2279,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:34</t>
+          <t>2026-08-20 21:04:51</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2324,17 +2309,17 @@
       </c>
       <c r="M35" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608192770223988</t>
+          <t>4500000321202608202974919363</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="0">
-        <v>49380749</v>
+        <v>49451049</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>琴</t>
+          <t>曾姐</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -2359,7 +2344,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:04:06</t>
+          <t>2026-08-20 21:05:13</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2389,17 +2374,17 @@
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608197088116223</t>
+          <t>4500000353202608208073638505</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="0">
-        <v>49380733</v>
+        <v>49380753</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>风水道士何金权先生18885336852</t>
+          <t>月亮</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -2424,7 +2409,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 00:03:55</t>
+          <t>2026-08-19 00:04:10</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2454,17 +2439,17 @@
       </c>
       <c r="M37" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608197323803505</t>
+          <t>4500000340202608199548973720</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="0">
-        <v>49378805</v>
+        <v>49380751</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>心想事成</t>
+          <t>荣兰</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -2489,7 +2474,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:36:11</t>
+          <t>2026-08-19 00:04:34</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2519,17 +2504,17 @@
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608187136696859</t>
+          <t>4500000376202608192770223988</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="0">
-        <v>49378780</v>
+        <v>49380749</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>ZCL</t>
+          <t>琴</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -2554,7 +2539,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:59</t>
+          <t>2026-08-19 00:04:06</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2584,17 +2569,17 @@
       </c>
       <c r="M39" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608185058515299</t>
+          <t>4500000365202608197088116223</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="0">
-        <v>49378769</v>
+        <v>49380733</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>岁月如流水</t>
+          <t>风水道士何金权先生18885336852</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -2619,7 +2604,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:45</t>
+          <t>2026-08-19 00:03:55</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -2649,17 +2634,17 @@
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608182677022834</t>
+          <t>4500000361202608197323803505</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="0">
-        <v>49378768</v>
+        <v>49378805</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>天天好心情</t>
+          <t>心想事成</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -2684,7 +2669,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 22:34:39</t>
+          <t>2026-08-18 22:36:11</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -2714,17 +2699,17 @@
       </c>
       <c r="M41" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608185835240274</t>
+          <t>4500000316202608187136696859</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="0">
-        <v>49375111</v>
+        <v>49378780</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>万事大吉</t>
+          <t>ZCL</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -2749,7 +2734,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:05:57</t>
+          <t>2026-08-18 22:34:59</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2779,17 +2764,17 @@
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608187074952472</t>
+          <t>4500000316202608185058515299</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="0">
-        <v>49375081</v>
+        <v>49378769</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>如鱼得水</t>
+          <t>岁月如流水</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -2814,7 +2799,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:04:47</t>
+          <t>2026-08-18 22:34:45</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2844,17 +2829,17 @@
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608189110994857</t>
+          <t>4500000363202608182677022834</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="0">
-        <v>49375015</v>
+        <v>49378768</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>母爱</t>
+          <t>天天好心情</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -2879,7 +2864,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:52</t>
+          <t>2026-08-18 22:34:39</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2909,17 +2894,17 @@
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608186111867199</t>
+          <t>4500000345202608185835240274</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="0">
-        <v>49375001</v>
+        <v>49375111</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>郭正平</t>
+          <t>万事大吉</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -2944,7 +2929,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:41</t>
+          <t>2026-08-18 21:05:57</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2974,17 +2959,17 @@
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608187695923792</t>
+          <t>4500000344202608187074952472</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="0">
-        <v>49375000</v>
+        <v>49375081</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>云    朵</t>
+          <t>如鱼得水</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -3009,7 +2994,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:36</t>
+          <t>2026-08-18 21:04:47</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -3039,17 +3024,17 @@
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608184692846233</t>
+          <t>4500000369202608189110994857</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="0">
-        <v>49371969</v>
+        <v>49375015</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>豆棋奶奶</t>
+          <t>母爱</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -3074,7 +3059,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:53:16</t>
+          <t>2026-08-18 21:03:52</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -3104,17 +3089,17 @@
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
-          <t>4500000381202608187462400910</t>
+          <t>4500000365202608186111867199</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="0">
-        <v>49370049</v>
+        <v>49375001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>熊金娥</t>
+          <t>郭正平</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -3139,7 +3124,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:34:52</t>
+          <t>2026-08-18 21:03:41</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -3169,17 +3154,17 @@
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608186456472403</t>
+          <t>4500000358202608187695923792</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="0">
-        <v>49370024</v>
+        <v>49375000</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>宏娇18906639773</t>
+          <t>云    朵</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -3204,7 +3189,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:34:43</t>
+          <t>2026-08-18 21:03:36</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -3234,17 +3219,17 @@
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608181915925686</t>
+          <t>4500000361202608184692846233</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="0">
-        <v>49369533</v>
+        <v>49371969</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>周周有钱</t>
+          <t>豆棋奶奶</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3269,7 +3254,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:32</t>
+          <t>2026-08-18 19:53:16</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -3299,17 +3284,17 @@
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608183864211631</t>
+          <t>4500000381202608187462400910</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="0">
-        <v>49369376</v>
+        <v>49370049</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>王兰允</t>
+          <t>熊金娥</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -3334,7 +3319,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:40</t>
+          <t>2026-08-18 19:34:52</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -3364,17 +3349,17 @@
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>
-          <t>4500000372202608185572793801</t>
+          <t>4500000343202608186456472403</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="0">
-        <v>49369344</v>
+        <v>49370024</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>陈</t>
+          <t>宏娇18906639773</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -3399,7 +3384,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:33:15</t>
+          <t>2026-08-18 19:34:43</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -3429,17 +3414,17 @@
       </c>
       <c r="M52" s="0" t="inlineStr">
         <is>
-          <t>4500000361202608183479278224</t>
+          <t>4500000356202608181915925686</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="0">
-        <v>49369203</v>
+        <v>49369533</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>静心</t>
+          <t>周周有钱</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -3464,7 +3449,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 19:32:32</t>
+          <t>2026-08-18 19:33:32</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3494,17 +3479,17 @@
       </c>
       <c r="M53" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608182953367773</t>
+          <t>4500000324202608183864211631</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="0">
-        <v>49340095</v>
+        <v>49369376</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>小小</t>
+          <t>王兰允</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -3529,7 +3514,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:24:20</t>
+          <t>2026-08-18 19:33:40</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -3559,17 +3544,17 @@
       </c>
       <c r="M54" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608185905136033</t>
+          <t>4500000372202608185572793801</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="0">
-        <v>49340080</v>
+        <v>49369344</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>封艳丽</t>
+          <t>陈</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -3594,7 +3579,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:22:59</t>
+          <t>2026-08-18 19:33:15</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -3624,17 +3609,17 @@
       </c>
       <c r="M55" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608183466806505</t>
+          <t>4500000361202608183479278224</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="0">
-        <v>49339950</v>
+        <v>49369203</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>家和万事兴</t>
+          <t>静心</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -3659,7 +3644,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:07</t>
+          <t>2026-08-18 19:32:32</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -3689,22 +3674,17 @@
       </c>
       <c r="M56" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608183266732544</t>
-        </is>
-      </c>
-      <c r="N56" s="0" t="inlineStr">
-        <is>
-          <t>亳州</t>
+          <t>4500000377202608182953367773</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="0">
-        <v>49339947</v>
+        <v>49340095</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>温玉明</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -3729,7 +3709,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:58</t>
+          <t>2026-08-18 00:24:20</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -3759,17 +3739,17 @@
       </c>
       <c r="M57" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608181657535231</t>
+          <t>4500000339202608185905136033</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="0">
-        <v>49339943</v>
+        <v>49340080</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>春梅</t>
+          <t>封艳丽</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -3794,7 +3774,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:49</t>
+          <t>2026-08-18 00:22:59</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3824,17 +3804,17 @@
       </c>
       <c r="M58" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608182239214659</t>
+          <t>4500000320202608183466806505</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="0">
-        <v>49339939</v>
+        <v>49339950</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>青青</t>
+          <t>家和万事兴</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -3859,7 +3839,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:44</t>
+          <t>2026-08-18 00:04:07</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -3889,17 +3869,22 @@
       </c>
       <c r="M59" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608185247886970</t>
+          <t>4500000344202608183266732544</t>
+        </is>
+      </c>
+      <c r="N59" s="0" t="inlineStr">
+        <is>
+          <t>亳州</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="0">
-        <v>49339937</v>
+        <v>49339947</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>开心向日葵🌻</t>
+          <t>温玉明</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -3924,7 +3909,7 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:40</t>
+          <t>2026-08-18 00:04:58</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -3954,17 +3939,17 @@
       </c>
       <c r="M60" s="0" t="inlineStr">
         <is>
-          <t>4500000319202608184846762524</t>
+          <t>4500000357202608181657535231</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="0">
-        <v>49339936</v>
+        <v>49339943</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>彩之缘</t>
+          <t>春梅</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -3989,7 +3974,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:39</t>
+          <t>2026-08-18 00:03:49</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -4019,17 +4004,17 @@
       </c>
       <c r="M61" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608186999829929</t>
+          <t>4500000342202608182239214659</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="0">
-        <v>49339931</v>
+        <v>49339939</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>青青</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -4054,7 +4039,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:24</t>
+          <t>2026-08-18 00:03:44</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -4084,17 +4069,17 @@
       </c>
       <c r="M62" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608186968757749</t>
+          <t>4500000355202608185247886970</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="0">
-        <v>49339929</v>
+        <v>49339937</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>段桂富</t>
+          <t>开心向日葵🌻</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -4119,7 +4104,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:06</t>
+          <t>2026-08-18 00:03:40</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -4149,17 +4134,17 @@
       </c>
       <c r="M63" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608189428147476</t>
+          <t>4500000319202608184846762524</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="0">
-        <v>49339923</v>
+        <v>49339936</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>蓝天</t>
+          <t>彩之缘</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -4184,7 +4169,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:07</t>
+          <t>2026-08-18 00:03:39</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -4214,17 +4199,17 @@
       </c>
       <c r="M64" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608189060114184</t>
+          <t>4500000342202608186999829929</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="0">
-        <v>49339921</v>
+        <v>49339931</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>陌上花开</t>
+          <t>my</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -4249,7 +4234,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:59</t>
+          <t>2026-08-18 00:03:24</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -4279,17 +4264,17 @@
       </c>
       <c r="M65" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608185881858135</t>
+          <t>4500000383202608186968757749</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="0">
-        <v>49339920</v>
+        <v>49339929</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>A红雨伞玲雪养发馆</t>
+          <t>段桂富</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -4314,7 +4299,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:03</t>
+          <t>2026-08-18 00:04:06</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4344,17 +4329,17 @@
       </c>
       <c r="M66" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608181810150616</t>
+          <t>4500000349202608189428147476</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="0">
-        <v>49339918</v>
+        <v>49339923</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>胡璎桉</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -4379,7 +4364,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:05:04</t>
+          <t>2026-08-18 00:03:07</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4409,17 +4394,17 @@
       </c>
       <c r="M67" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608188854566939</t>
+          <t>4500000346202608189060114184</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="0">
-        <v>49337893</v>
+        <v>49339921</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>郑洁玲</t>
+          <t>陌上花开</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -4444,7 +4429,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:36:14</t>
+          <t>2026-08-18 00:03:59</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -4474,17 +4459,17 @@
       </c>
       <c r="M68" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608171736033078</t>
+          <t>4500000353202608185881858135</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="0">
-        <v>49337886</v>
+        <v>49339920</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>浪漫樱花</t>
+          <t>A红雨伞玲雪养发馆</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -4509,7 +4494,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:44</t>
+          <t>2026-08-18 00:03:03</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -4539,17 +4524,17 @@
       </c>
       <c r="M69" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176588884719</t>
+          <t>4500000344202608181810150616</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="0">
-        <v>49337882</v>
+        <v>49339918</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>王仲槐</t>
+          <t>胡璎桉</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -4574,7 +4559,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:25</t>
+          <t>2026-08-18 00:05:04</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -4604,17 +4589,17 @@
       </c>
       <c r="M70" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608171381637652</t>
+          <t>4500000354202608188854566939</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="0">
-        <v>49337868</v>
+        <v>49337893</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>黄建17373719413</t>
+          <t>郑洁玲</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -4639,7 +4624,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:03</t>
+          <t>2026-08-17 22:36:14</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -4669,17 +4654,17 @@
       </c>
       <c r="M71" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608175713808624</t>
+          <t>4500000340202608171736033078</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="0">
-        <v>49337865</v>
+        <v>49337886</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>晓燕</t>
+          <t>浪漫樱花</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -4704,7 +4689,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:01</t>
+          <t>2026-08-17 22:35:44</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -4734,17 +4719,17 @@
       </c>
       <c r="M72" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608175538967169</t>
+          <t>4500000362202608176588884719</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="0">
-        <v>49337857</v>
+        <v>49337882</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>真心真意</t>
+          <t>王仲槐</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -4769,7 +4754,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:34:43</t>
+          <t>2026-08-17 22:35:25</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -4799,17 +4784,17 @@
       </c>
       <c r="M73" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176387457203</t>
+          <t>4500000339202608171381637652</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="0">
-        <v>49334810</v>
+        <v>49337868</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>candy🧬甘💕</t>
+          <t>黄建17373719413</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -4834,7 +4819,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:25:31</t>
+          <t>2026-08-17 22:35:03</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -4864,17 +4849,17 @@
       </c>
       <c r="M74" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608173665178011</t>
+          <t>4500000357202608175713808624</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="0">
-        <v>49334746</v>
+        <v>49337865</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>雨落弦音</t>
+          <t>晓燕</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -4899,7 +4884,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:24:18</t>
+          <t>2026-08-17 22:35:01</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -4929,17 +4914,17 @@
       </c>
       <c r="M75" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608175925050310</t>
+          <t>4500000380202608175538967169</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="0">
-        <v>49334683</v>
+        <v>49337857</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>🌹六福A413🌹</t>
+          <t>真心真意</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -4964,7 +4949,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:23:16</t>
+          <t>2026-08-17 22:34:43</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -4994,17 +4979,17 @@
       </c>
       <c r="M76" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608175320562123</t>
+          <t>4500000362202608176387457203</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="0">
-        <v>49333672</v>
+        <v>49334810</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>☀️知足常乐😊</t>
+          <t>candy🧬甘💕</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -5029,7 +5014,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:44</t>
+          <t>2026-08-17 21:25:31</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -5059,17 +5044,17 @@
       </c>
       <c r="M77" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608178190501918</t>
+          <t>4500000379202608173665178011</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="0">
-        <v>49333665</v>
+        <v>49334746</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>在水一方</t>
+          <t>雨落弦音</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -5094,7 +5079,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:41</t>
+          <t>2026-08-17 21:24:18</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -5124,17 +5109,17 @@
       </c>
       <c r="M78" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608175675285016</t>
+          <t>4500000324202608175925050310</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="0">
-        <v>49333658</v>
+        <v>49334683</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>牛牛</t>
+          <t>🌹六福A413🌹</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -5159,7 +5144,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:31</t>
+          <t>2026-08-17 21:23:16</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -5189,17 +5174,17 @@
       </c>
       <c r="M79" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608171889470116</t>
+          <t>4500000337202608175320562123</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="0">
-        <v>49333657</v>
+        <v>49333672</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>鲍镇定</t>
+          <t>☀️知足常乐😊</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -5224,7 +5209,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:38</t>
+          <t>2026-08-17 21:01:44</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -5254,17 +5239,17 @@
       </c>
       <c r="M80" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608179201028350</t>
+          <t>4500000380202608178190501918</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="0">
-        <v>49333649</v>
+        <v>49333665</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>:-D开心果O:-)</t>
+          <t>在水一方</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -5289,7 +5274,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:27</t>
+          <t>2026-08-17 21:01:41</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -5319,17 +5304,17 @@
       </c>
       <c r="M81" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608172428227717</t>
+          <t>4500000333202608175675285016</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="0">
-        <v>49333640</v>
+        <v>49333658</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>黛黛</t>
+          <t>牛牛</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -5354,7 +5339,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:30</t>
+          <t>2026-08-17 21:01:31</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -5384,17 +5369,17 @@
       </c>
       <c r="M82" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608177275411312</t>
+          <t>4500000380202608171889470116</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="0">
-        <v>49330491</v>
+        <v>49333657</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>兰花草</t>
+          <t>鲍镇定</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -5419,7 +5404,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:31</t>
+          <t>2026-08-17 21:01:38</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5449,17 +5434,17 @@
       </c>
       <c r="M83" s="0" t="inlineStr">
         <is>
-          <t>4500000341202608178144232010</t>
+          <t>4500000321202608179201028350</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="0">
-        <v>49330472</v>
+        <v>49333649</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>郝杏月</t>
+          <t>:-D开心果O:-)</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -5484,7 +5469,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:27</t>
+          <t>2026-08-17 21:01:27</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -5514,17 +5499,17 @@
       </c>
       <c r="M84" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608176551746821</t>
+          <t>4500000344202608172428227717</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="0">
-        <v>49330471</v>
+        <v>49333640</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>金泽湖水</t>
+          <t>黛黛</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -5549,7 +5534,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:46</t>
+          <t>2026-08-17 21:01:30</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -5579,17 +5564,17 @@
       </c>
       <c r="M85" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608175707490842</t>
+          <t>4500000316202608177275411312</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="0">
-        <v>49330470</v>
+        <v>49330491</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>乐惠</t>
+          <t>兰花草</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -5614,7 +5599,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:54</t>
+          <t>2026-08-17 19:53:31</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -5644,17 +5629,17 @@
       </c>
       <c r="M86" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608179365238894</t>
+          <t>4500000341202608178144232010</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="0">
-        <v>49302015</v>
+        <v>49330472</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>辰悦</t>
+          <t>郝杏月</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -5679,7 +5664,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:22:50</t>
+          <t>2026-08-17 19:53:27</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -5709,17 +5694,17 @@
       </c>
       <c r="M87" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608175953744348</t>
+          <t>4500000337202608176551746821</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="0">
-        <v>49301896</v>
+        <v>49330471</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>简简单单</t>
+          <t>金泽湖水</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -5744,7 +5729,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:05:28</t>
+          <t>2026-08-17 19:52:46</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -5774,17 +5759,17 @@
       </c>
       <c r="M88" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608175217008588</t>
+          <t>4500000374202608175707490842</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="0">
-        <v>49301861</v>
+        <v>49330470</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>小优不忘初心</t>
+          <t>乐惠</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -5809,7 +5794,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:03</t>
+          <t>2026-08-17 19:52:54</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -5839,17 +5824,17 @@
       </c>
       <c r="M89" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608176836637946</t>
+          <t>4500000347202608179365238894</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="0">
-        <v>49301860</v>
+        <v>49302015</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>半夏轻浅</t>
+          <t>辰悦</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -5874,7 +5859,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:08</t>
+          <t>2026-08-17 00:22:50</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -5904,17 +5889,17 @@
       </c>
       <c r="M90" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608175019525500</t>
+          <t>4500000368202608175953744348</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="0">
-        <v>49301859</v>
+        <v>49301896</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>小璇一（龙树门业</t>
+          <t>简简单单</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -5939,7 +5924,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:52</t>
+          <t>2026-08-17 00:05:28</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -5969,17 +5954,17 @@
       </c>
       <c r="M91" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608177884628709</t>
+          <t>4500000353202608175217008588</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="0">
-        <v>49301854</v>
+        <v>49301861</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
+          <t>小优不忘初心</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -6004,7 +5989,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:00</t>
+          <t>2026-08-17 00:04:03</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -6034,17 +6019,17 @@
       </c>
       <c r="M92" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608177813577730</t>
+          <t>4500000330202608176836637946</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="0">
-        <v>49301853</v>
+        <v>49301860</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>祥云母婴春姐</t>
+          <t>半夏轻浅</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -6069,7 +6054,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:49</t>
+          <t>2026-08-17 00:04:08</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -6099,17 +6084,17 @@
       </c>
       <c r="M93" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608178418886316</t>
+          <t>4500000338202608175019525500</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="0">
-        <v>49301852</v>
+        <v>49301859</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>白迎春</t>
+          <t>小璇一（龙树门业</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -6134,7 +6119,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:46</t>
+          <t>2026-08-17 00:03:52</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -6164,17 +6149,17 @@
       </c>
       <c r="M94" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608174681213879</t>
+          <t>4500000347202608177884628709</t>
         </is>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="0">
-        <v>49301850</v>
+        <v>49301854</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>人心易冷</t>
+          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -6199,7 +6184,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:04</t>
+          <t>2026-08-17 00:04:00</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -6229,17 +6214,17 @@
       </c>
       <c r="M95" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608172769831285</t>
+          <t>4500000352202608177813577730</t>
         </is>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="0">
-        <v>49301846</v>
+        <v>49301853</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>心静自然凉</t>
+          <t>祥云母婴春姐</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -6264,7 +6249,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:51</t>
+          <t>2026-08-17 00:03:49</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -6294,17 +6279,17 @@
       </c>
       <c r="M96" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608177412373514</t>
+          <t>4500000337202608178418886316</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="0">
-        <v>49301843</v>
+        <v>49301852</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
+          <t>白迎春</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -6329,7 +6314,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:40</t>
+          <t>2026-08-17 00:03:46</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -6359,17 +6344,17 @@
       </c>
       <c r="M97" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608176220568550</t>
+          <t>4500000377202608174681213879</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="0">
-        <v>49300670</v>
+        <v>49301850</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>看透人心，</t>
+          <t>人心易冷</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -6394,7 +6379,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:07</t>
+          <t>2026-08-17 00:04:04</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -6424,17 +6409,17 @@
       </c>
       <c r="M98" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608165434325764</t>
+          <t>4500000349202608172769831285</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="0">
-        <v>49300667</v>
+        <v>49301846</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>童心依旧</t>
+          <t>心静自然凉</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -6459,7 +6444,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:03</t>
+          <t>2026-08-17 00:03:51</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -6489,17 +6474,17 @@
       </c>
       <c r="M99" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608161482824495</t>
+          <t>4500000354202608177412373514</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="0">
-        <v>49300135</v>
+        <v>49301843</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>秋韵</t>
+          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -6524,7 +6509,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:34</t>
+          <t>2026-08-17 00:03:40</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -6554,17 +6539,17 @@
       </c>
       <c r="M100" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608167344457159</t>
+          <t>4500000320202608176220568550</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="0">
-        <v>49300112</v>
+        <v>49300670</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>平安福贵</t>
+          <t>看透人心，</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -6589,7 +6574,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:27</t>
+          <t>2026-08-16 22:56:07</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -6619,17 +6604,17 @@
       </c>
       <c r="M101" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608162072183782</t>
+          <t>4500000365202608165434325764</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="0">
-        <v>49300100</v>
+        <v>49300667</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>萱奶奶</t>
+          <t>童心依旧</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -6654,7 +6639,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:45</t>
+          <t>2026-08-16 22:56:03</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -6684,17 +6669,17 @@
       </c>
       <c r="M102" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608164279026924</t>
+          <t>4500000369202608161482824495</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="0">
-        <v>49300096</v>
+        <v>49300135</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>泓涧（红健）</t>
+          <t>秋韵</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -6719,7 +6704,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:31</t>
+          <t>2026-08-16 22:36:34</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -6749,17 +6734,17 @@
       </c>
       <c r="M103" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608161591115326</t>
+          <t>4500000322202608167344457159</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="0">
-        <v>49300095</v>
+        <v>49300112</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>风行云🏇</t>
+          <t>平安福贵</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -6784,7 +6769,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:13</t>
+          <t>2026-08-16 22:36:27</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -6814,17 +6799,17 @@
       </c>
       <c r="M104" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608165318502823</t>
+          <t>4500000329202608162072183782</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="0">
-        <v>49300083</v>
+        <v>49300100</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>才秀</t>
+          <t>萱奶奶</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -6849,7 +6834,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:11</t>
+          <t>2026-08-16 22:35:45</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -6879,22 +6864,17 @@
       </c>
       <c r="M105" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608161669406907</t>
-        </is>
-      </c>
-      <c r="N105" s="0" t="inlineStr">
-        <is>
-          <t>奉贤</t>
+          <t>4500000345202608164279026924</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="0">
-        <v>49300055</v>
+        <v>49300096</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>冰心</t>
+          <t>泓涧（红健）</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -6919,7 +6899,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:49</t>
+          <t>2026-08-16 22:35:31</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -6949,17 +6929,17 @@
       </c>
       <c r="M106" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608167949730522</t>
+          <t>4500000324202608161591115326</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="0">
-        <v>49300045</v>
+        <v>49300095</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>风行云🏇</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -6984,7 +6964,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:20</t>
+          <t>2026-08-16 22:36:13</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -7014,22 +6994,17 @@
       </c>
       <c r="M107" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608162476754389</t>
-        </is>
-      </c>
-      <c r="N107" s="0" t="inlineStr">
-        <is>
-          <t>荆州</t>
+          <t>4500000358202608165318502823</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="0">
-        <v>49300042</v>
+        <v>49300083</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>赵萍</t>
+          <t>才秀</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -7054,7 +7029,7 @@
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:13</t>
+          <t>2026-08-16 22:35:11</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -7084,17 +7059,22 @@
       </c>
       <c r="M108" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608168494549151</t>
+          <t>4500000330202608161669406907</t>
+        </is>
+      </c>
+      <c r="N108" s="0" t="inlineStr">
+        <is>
+          <t>奉贤</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="0">
-        <v>49300034</v>
+        <v>49300055</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>刘华</t>
+          <t>冰心</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -7119,7 +7099,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:07</t>
+          <t>2026-08-16 22:34:49</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -7149,17 +7129,17 @@
       </c>
       <c r="M109" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608165458621611</t>
+          <t>4500000317202608167949730522</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="0">
-        <v>49297749</v>
+        <v>49300045</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>沈雨凤</t>
+          <t>平</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -7184,7 +7164,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:24</t>
+          <t>2026-08-16 22:34:20</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -7214,17 +7194,22 @@
       </c>
       <c r="M110" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608164415130639</t>
+          <t>4500000353202608162476754389</t>
+        </is>
+      </c>
+      <c r="N110" s="0" t="inlineStr">
+        <is>
+          <t>荆州</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="0">
-        <v>49297736</v>
+        <v>49300042</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>莉莉</t>
+          <t>赵萍</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -7249,7 +7234,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:09</t>
+          <t>2026-08-16 22:34:13</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -7279,17 +7264,17 @@
       </c>
       <c r="M111" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163428098661</t>
+          <t>4500000346202608168494549151</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="0">
-        <v>49297681</v>
+        <v>49300034</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>一生平安</t>
+          <t>刘华</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -7314,7 +7299,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:46</t>
+          <t>2026-08-16 22:35:07</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -7344,17 +7329,17 @@
       </c>
       <c r="M112" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608163491096965</t>
+          <t>4500000333202608165458621611</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="0">
-        <v>49297679</v>
+        <v>49297749</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>孔平</t>
+          <t>沈雨凤</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -7379,7 +7364,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:57</t>
+          <t>2026-08-16 21:27:24</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -7409,17 +7394,17 @@
       </c>
       <c r="M113" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608165709204884</t>
+          <t>4500000375202608164415130639</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="0">
-        <v>49296893</v>
+        <v>49297736</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>逍遥仙子</t>
+          <t>莉莉</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -7444,7 +7429,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:30</t>
+          <t>2026-08-16 21:27:09</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -7474,17 +7459,17 @@
       </c>
       <c r="M114" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608167690459739</t>
+          <t>4500000369202608163428098661</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="0">
-        <v>49296884</v>
+        <v>49297681</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>丽红</t>
+          <t>一生平安</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -7509,7 +7494,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:16</t>
+          <t>2026-08-16 21:25:46</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -7539,17 +7524,17 @@
       </c>
       <c r="M115" s="0" t="inlineStr">
         <is>
-          <t>4500000332202608162032983613</t>
+          <t>4500000368202608163491096965</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="0">
-        <v>49296874</v>
+        <v>49297679</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>海  角</t>
+          <t>孔平</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -7574,7 +7559,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:57</t>
+          <t>2026-08-16 21:25:57</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -7604,17 +7589,17 @@
       </c>
       <c r="M116" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163623487097</t>
+          <t>4500000367202608165709204884</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="0">
-        <v>49296864</v>
+        <v>49296893</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>曹景玉</t>
+          <t>逍遥仙子</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -7639,7 +7624,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:45</t>
+          <t>2026-08-16 21:04:30</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -7669,17 +7654,17 @@
       </c>
       <c r="M117" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608163779658463</t>
+          <t>4500000316202608167690459739</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="0">
-        <v>49296863</v>
+        <v>49296884</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>石陆萍</t>
+          <t>丽红</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -7704,7 +7689,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:13</t>
+          <t>2026-08-16 21:04:16</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -7734,17 +7719,17 @@
       </c>
       <c r="M118" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608161473678444</t>
+          <t>4500000332202608162032983613</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="0">
-        <v>49296849</v>
+        <v>49296874</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>阿荣</t>
+          <t>海  角</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -7769,7 +7754,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:43</t>
+          <t>2026-08-16 21:03:57</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -7799,17 +7784,17 @@
       </c>
       <c r="M119" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608169868333535</t>
+          <t>4500000369202608163623487097</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="0">
-        <v>49296823</v>
+        <v>49296864</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>周少丽</t>
+          <t>曹景玉</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -7834,7 +7819,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:17</t>
+          <t>2026-08-16 21:03:45</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -7864,17 +7849,17 @@
       </c>
       <c r="M120" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608169179019788</t>
+          <t>4500000331202608163779658463</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="0">
-        <v>49296822</v>
+        <v>49296863</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>雨花石</t>
+          <t>石陆萍</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -7899,7 +7884,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:16</t>
+          <t>2026-08-16 21:04:13</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -7929,17 +7914,17 @@
       </c>
       <c r="M121" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608166345332381</t>
+          <t>4500000351202608161473678444</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="0">
-        <v>49293860</v>
+        <v>49296849</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>树玲</t>
+          <t>阿荣</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -7964,7 +7949,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:26</t>
+          <t>2026-08-16 21:03:43</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -7994,17 +7979,17 @@
       </c>
       <c r="M122" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608168589310428</t>
+          <t>4500000318202608169868333535</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="0">
-        <v>49293858</v>
+        <v>49296823</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>芬芳</t>
+          <t>周少丽</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -8029,7 +8014,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:42</t>
+          <t>2026-08-16 21:03:17</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
@@ -8059,17 +8044,17 @@
       </c>
       <c r="M123" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608162910375128</t>
+          <t>4500000315202608169179019788</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="0">
-        <v>49197594</v>
+        <v>49296822</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>李秀燕健康顾问</t>
+          <t>雨花石</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
@@ -8094,7 +8079,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:55</t>
+          <t>2026-08-16 21:03:16</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -8124,17 +8109,17 @@
       </c>
       <c r="M124" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608135550322726</t>
+          <t>4500000367202608166345332381</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="0">
-        <v>49197555</v>
+        <v>49293860</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>FXH*</t>
+          <t>树玲</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -8159,7 +8144,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:10</t>
+          <t>2026-08-16 19:55:26</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -8189,17 +8174,17 @@
       </c>
       <c r="M125" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608139667116905</t>
+          <t>4500000342202608168589310428</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="0">
-        <v>49197551</v>
+        <v>49293858</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>书英</t>
+          <t>芬芳</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -8224,7 +8209,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:09</t>
+          <t>2026-08-16 19:55:42</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -8254,17 +8239,17 @@
       </c>
       <c r="M126" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608135183726220</t>
+          <t>4500000358202608162910375128</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="0">
-        <v>49197500</v>
+        <v>49197594</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>求智慧</t>
+          <t>李秀燕健康顾问</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
@@ -8289,7 +8274,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:54:20</t>
+          <t>2026-08-13 21:55:55</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -8319,17 +8304,17 @@
       </c>
       <c r="M127" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608136477567012</t>
+          <t>4500000383202608135550322726</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="0">
-        <v>49196660</v>
+        <v>49197555</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>陈书先</t>
+          <t>FXH*</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -8354,7 +8339,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:55</t>
+          <t>2026-08-13 21:55:10</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -8384,17 +8369,17 @@
       </c>
       <c r="M128" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608137513582005</t>
+          <t>4500000376202608139667116905</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="0">
-        <v>49196649</v>
+        <v>49197551</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>chenchen</t>
+          <t>书英</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -8419,7 +8404,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:37</t>
+          <t>2026-08-13 21:55:09</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -8449,17 +8434,17 @@
       </c>
       <c r="M129" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608131193472561</t>
+          <t>4500000363202608135183726220</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="0">
-        <v>49196616</v>
+        <v>49197500</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>因子</t>
+          <t>求智慧</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -8484,7 +8469,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:34</t>
+          <t>2026-08-13 21:54:20</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -8514,17 +8499,17 @@
       </c>
       <c r="M130" s="0" t="inlineStr">
         <is>
-          <t>4500000381202608131084069069</t>
+          <t>4500000356202608136477567012</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="0">
-        <v>49196580</v>
+        <v>49196660</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>包容</t>
+          <t>陈书先</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -8549,7 +8534,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:49</t>
+          <t>2026-08-13 21:35:55</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -8579,17 +8564,17 @@
       </c>
       <c r="M131" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608134515206220</t>
+          <t>4500000362202608137513582005</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="0">
-        <v>49196556</v>
+        <v>49196649</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>小芳</t>
+          <t>chenchen</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -8614,7 +8599,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:00</t>
+          <t>2026-08-13 21:35:37</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -8644,17 +8629,17 @@
       </c>
       <c r="M132" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608131586040016</t>
+          <t>4500000360202608131193472561</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="0">
-        <v>49196547</v>
+        <v>49196616</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>雷宁</t>
+          <t>因子</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
@@ -8679,7 +8664,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:30</t>
+          <t>2026-08-13 21:35:34</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -8709,17 +8694,17 @@
       </c>
       <c r="M133" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608133116145497</t>
+          <t>4500000381202608131084069069</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="0">
-        <v>49196546</v>
+        <v>49196580</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>兰莓</t>
+          <t>包容</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -8744,7 +8729,7 @@
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:56:17</t>
+          <t>2026-08-13 21:34:49</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -8774,17 +8759,17 @@
       </c>
       <c r="M134" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608136989637138</t>
+          <t>4500000329202608134515206220</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="0">
-        <v>49196528</v>
+        <v>49196556</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>赵子睿奶奶</t>
+          <t>小芳</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -8809,7 +8794,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:22</t>
+          <t>2026-08-13 21:34:00</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -8839,17 +8824,17 @@
       </c>
       <c r="M135" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608137236789446</t>
+          <t>4500000380202608131586040016</t>
         </is>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="0">
-        <v>49196510</v>
+        <v>49196547</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>山岭巨人</t>
+          <t>雷宁</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -8874,7 +8859,7 @@
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:22</t>
+          <t>2026-08-13 21:34:30</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -8904,17 +8889,17 @@
       </c>
       <c r="M136" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608138809307553</t>
+          <t>4500000368202608133116145497</t>
         </is>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="0">
-        <v>49196507</v>
+        <v>49196546</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>香字钟培芷</t>
+          <t>兰莓</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
@@ -8939,7 +8924,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:53</t>
+          <t>2026-08-13 21:56:17</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -8969,17 +8954,17 @@
       </c>
       <c r="M137" s="0" t="inlineStr">
         <is>
-          <t>4500000370202608133660294135</t>
+          <t>4500000352202608136989637138</t>
         </is>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="0">
-        <v>49196498</v>
+        <v>49196528</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>孟光宗</t>
+          <t>赵子睿奶奶</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
@@ -9004,7 +8989,7 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:37:14</t>
+          <t>2026-08-13 21:33:22</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -9034,17 +9019,17 @@
       </c>
       <c r="M138" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608138859211736</t>
+          <t>4500000345202608137236789446</t>
         </is>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="0">
-        <v>49196495</v>
+        <v>49196510</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>夏雨晴的妈妈（天发水芹</t>
+          <t>山岭巨人</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
@@ -9069,7 +9054,7 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:35:22</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -9099,22 +9084,17 @@
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
-          <t>4500000371202608138873102820</t>
-        </is>
-      </c>
-      <c r="N139" s="0" t="inlineStr">
-        <is>
-          <t>湾仔区</t>
+          <t>4500000324202608138809307553</t>
         </is>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="0">
-        <v>49196485</v>
+        <v>49196507</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>法苑文印广告</t>
+          <t>香字钟培芷</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -9139,7 +9119,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:06</t>
+          <t>2026-08-13 21:32:53</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -9169,17 +9149,17 @@
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608139506557676</t>
+          <t>4500000370202608133660294135</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="0">
-        <v>49196481</v>
+        <v>49196498</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>四季果</t>
+          <t>孟光宗</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -9204,7 +9184,7 @@
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:08</t>
+          <t>2026-08-13 21:37:14</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -9234,17 +9214,17 @@
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608134787426208</t>
+          <t>4500000363202608138859211736</t>
         </is>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="0">
-        <v>49196479</v>
+        <v>49196495</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>仇尚妹</t>
+          <t>夏雨晴的妈妈（天发水芹</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
@@ -9269,7 +9249,7 @@
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:43</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -9299,17 +9279,22 @@
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608136810799236</t>
+          <t>4500000371202608138873102820</t>
+        </is>
+      </c>
+      <c r="N142" s="0" t="inlineStr">
+        <is>
+          <t>湾仔区</t>
         </is>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="0">
-        <v>49196478</v>
+        <v>49196485</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>A古庄店大新手机卖场库琳琳</t>
+          <t>法苑文印广告</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -9334,7 +9319,7 @@
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:42</t>
+          <t>2026-08-13 21:33:06</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -9364,17 +9349,17 @@
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608137311399529</t>
+          <t>4500000379202608139506557676</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="0">
-        <v>49196473</v>
+        <v>49196481</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>刘玉云机械租赁服务部15905691602</t>
+          <t>四季果</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -9399,7 +9384,7 @@
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:30</t>
+          <t>2026-08-13 21:33:08</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -9429,17 +9414,17 @@
       </c>
       <c r="M144" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608134297741797</t>
+          <t>4500000335202608134787426208</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="0">
-        <v>49196470</v>
+        <v>49196479</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>众舍康安二手房丽姐</t>
+          <t>仇尚妹</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -9464,7 +9449,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:28</t>
+          <t>2026-08-13 21:32:43</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -9494,17 +9479,17 @@
       </c>
       <c r="M145" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608137489426707</t>
+          <t>4500000374202608136810799236</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="0">
-        <v>49196462</v>
+        <v>49196478</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>欢欢</t>
+          <t>A古庄店大新手机卖场库琳琳</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -9529,7 +9514,7 @@
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:31</t>
+          <t>2026-08-13 21:32:42</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -9559,17 +9544,17 @@
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608136078541008</t>
+          <t>4500000373202608137311399529</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="0">
-        <v>49196456</v>
+        <v>49196473</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>润花</t>
+          <t>刘玉云机械租赁服务部15905691602</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -9594,7 +9579,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:32:30</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -9624,17 +9609,17 @@
       </c>
       <c r="M147" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608139285322594</t>
+          <t>4500000315202608134297741797</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="0">
-        <v>49196455</v>
+        <v>49196470</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>风之韵</t>
+          <t>众舍康安二手房丽姐</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -9659,7 +9644,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:34</t>
+          <t>2026-08-13 21:32:28</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -9689,17 +9674,17 @@
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608137054529020</t>
+          <t>4500000325202608137489426707</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="0">
-        <v>49196452</v>
+        <v>49196462</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>开心每一天</t>
+          <t>欢欢</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -9724,7 +9709,7 @@
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:40</t>
+          <t>2026-08-13 21:32:31</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -9754,22 +9739,17 @@
       </c>
       <c r="M149" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608131603927208</t>
-        </is>
-      </c>
-      <c r="N149" s="0" t="inlineStr">
-        <is>
-          <t>连云港</t>
+          <t>4500000382202608136078541008</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="0">
-        <v>49196449</v>
+        <v>49196456</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>吉乐常伴</t>
+          <t>润花</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -9794,7 +9774,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -9824,17 +9804,17 @@
       </c>
       <c r="M150" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608139313739490</t>
+          <t>4500000365202608139285322594</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="0">
-        <v>49196445</v>
+        <v>49196455</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>快乐宝贝</t>
+          <t>风之韵</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -9859,7 +9839,7 @@
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:15</t>
+          <t>2026-08-13 21:32:34</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -9889,17 +9869,17 @@
       </c>
       <c r="M151" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133056225424</t>
+          <t>4500000339202608137054529020</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="0">
-        <v>49196441</v>
+        <v>49196452</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>感恩快乐每一天</t>
+          <t>开心每一天</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
@@ -9924,7 +9904,7 @@
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:13</t>
+          <t>2026-08-13 21:32:40</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -9954,17 +9934,22 @@
       </c>
       <c r="M152" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608132236113522</t>
+          <t>4500000327202608131603927208</t>
+        </is>
+      </c>
+      <c r="N152" s="0" t="inlineStr">
+        <is>
+          <t>连云港</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="0">
-        <v>49196439</v>
+        <v>49196449</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>翰林世家京墨18240001035</t>
+          <t>吉乐常伴</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -9989,7 +9974,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:18</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -10019,17 +10004,17 @@
       </c>
       <c r="M153" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608131410776307</t>
+          <t>4500000340202608139313739490</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="0">
-        <v>49196437</v>
+        <v>49196445</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>悦朵宝贝</t>
+          <t>快乐宝贝</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -10054,7 +10039,7 @@
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:06</t>
+          <t>2026-08-13 21:32:15</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -10084,17 +10069,17 @@
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608135681746747</t>
+          <t>4500000326202608133056225424</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="0">
-        <v>49196435</v>
+        <v>49196441</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>我的幸福</t>
+          <t>感恩快乐每一天</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -10119,7 +10104,7 @@
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:32:13</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -10149,17 +10134,17 @@
       </c>
       <c r="M155" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608138821842807</t>
+          <t>4500000383202608132236113522</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="0">
-        <v>49196433</v>
+        <v>49196439</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>程胜英</t>
+          <t>翰林世家京墨18240001035</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -10184,7 +10169,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:33</t>
+          <t>2026-08-13 21:32:18</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -10214,17 +10199,17 @@
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608136558136840</t>
+          <t>4500000315202608131410776307</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="0">
-        <v>49196424</v>
+        <v>49196437</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>甘峰源奶奶</t>
+          <t>悦朵宝贝</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -10249,7 +10234,7 @@
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:16</t>
+          <t>2026-08-13 21:32:06</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -10279,17 +10264,17 @@
       </c>
       <c r="M157" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608139681236972</t>
+          <t>4500000343202608135681746747</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="0">
-        <v>49196412</v>
+        <v>49196435</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>贝贝老妈</t>
+          <t>我的幸福</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -10314,7 +10299,7 @@
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:49</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -10344,17 +10329,17 @@
       </c>
       <c r="M158" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608138627203805</t>
+          <t>4500000331202608138821842807</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="0">
-        <v>49196406</v>
+        <v>49196433</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>过好每一天</t>
+          <t>程胜英</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -10379,7 +10364,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:55</t>
+          <t>2026-08-13 21:32:33</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -10409,17 +10394,17 @@
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608139484061741</t>
+          <t>4500000338202608136558136840</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="0">
-        <v>49196403</v>
+        <v>49196424</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>迪迪</t>
+          <t>甘峰源奶奶</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -10444,7 +10429,7 @@
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:58</t>
+          <t>2026-08-13 21:32:16</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -10474,17 +10459,17 @@
       </c>
       <c r="M160" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608138209731181</t>
+          <t>4500000374202608139681236972</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="0">
-        <v>49196399</v>
+        <v>49196412</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>境随心转</t>
+          <t>贝贝老妈</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -10509,7 +10494,7 @@
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:47</t>
+          <t>2026-08-13 21:31:49</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -10539,17 +10524,17 @@
       </c>
       <c r="M161" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608138946210876</t>
+          <t>4500000360202608138627203805</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="0">
-        <v>49196391</v>
+        <v>49196406</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>💖越来越好💖</t>
+          <t>过好每一天</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -10574,7 +10559,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:01</t>
+          <t>2026-08-13 21:31:55</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -10604,17 +10589,17 @@
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133672869122</t>
+          <t>4500000384202608139484061741</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="0">
-        <v>49196390</v>
+        <v>49196403</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>翠翠</t>
+          <t>迪迪</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -10639,7 +10624,7 @@
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:38</t>
+          <t>2026-08-13 21:31:58</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -10669,22 +10654,17 @@
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608139683947334</t>
-        </is>
-      </c>
-      <c r="N163" s="0" t="inlineStr">
-        <is>
-          <t>广州</t>
+          <t>4500000326202608138209731181</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="0">
-        <v>49196389</v>
+        <v>49196399</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>漫步繁华街</t>
+          <t>境随心转</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -10709,7 +10689,7 @@
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:39</t>
+          <t>2026-08-13 21:31:47</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -10739,17 +10719,17 @@
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608135974835236</t>
+          <t>4500000380202608138946210876</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="0">
-        <v>49196385</v>
+        <v>49196391</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>平淡人生🌲</t>
+          <t>💖越来越好💖</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -10774,7 +10754,7 @@
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:35</t>
+          <t>2026-08-13 21:32:01</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -10804,17 +10784,17 @@
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608136587117638</t>
+          <t>4500000326202608133672869122</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="0">
-        <v>49196384</v>
+        <v>49196390</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>眼镜灯饰城3楼76号15923959748</t>
+          <t>翠翠</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
@@ -10839,7 +10819,7 @@
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:34</t>
+          <t>2026-08-13 21:31:38</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -10869,17 +10849,22 @@
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608139966140440</t>
+          <t>4500000351202608139683947334</t>
+        </is>
+      </c>
+      <c r="N166" s="0" t="inlineStr">
+        <is>
+          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="0">
-        <v>49196383</v>
+        <v>49196389</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>喜枝</t>
+          <t>漫步繁华街</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
@@ -10904,7 +10889,7 @@
       </c>
       <c r="G167" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:45</t>
+          <t>2026-08-13 21:32:39</t>
         </is>
       </c>
       <c r="H167" s="0" t="inlineStr">
@@ -10934,17 +10919,17 @@
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608138694510811</t>
+          <t>4500000375202608135974835236</t>
         </is>
       </c>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="0">
-        <v>49155446</v>
+        <v>49196385</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>笑口常开</t>
+          <t>平淡人生🌲</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
@@ -10969,7 +10954,7 @@
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:36:06</t>
+          <t>2026-08-13 21:31:35</t>
         </is>
       </c>
       <c r="H168" s="0" t="inlineStr">
@@ -10999,17 +10984,17 @@
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608121856487760</t>
+          <t>4500000359202608136587117638</t>
         </is>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="0">
-        <v>49155389</v>
+        <v>49196384</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>奥普郭彦丽13937990394</t>
+          <t>眼镜灯饰城3楼76号15923959748</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
@@ -11034,7 +11019,7 @@
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:44</t>
+          <t>2026-08-13 21:31:34</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -11064,17 +11049,17 @@
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608124582542642</t>
+          <t>4500000333202608139966140440</t>
         </is>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="0">
-        <v>49155374</v>
+        <v>49196383</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>流星雨文华</t>
+          <t>喜枝</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
@@ -11099,7 +11084,7 @@
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:26</t>
+          <t>2026-08-13 21:31:45</t>
         </is>
       </c>
       <c r="H170" s="0" t="inlineStr">
@@ -11129,17 +11114,17 @@
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608121430434820</t>
+          <t>4500000333202608138694510811</t>
         </is>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="0">
-        <v>49155368</v>
+        <v>49155446</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>笑对人生</t>
+          <t>笑口常开</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -11164,7 +11149,7 @@
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:56</t>
+          <t>2026-08-12 21:36:06</t>
         </is>
       </c>
       <c r="H171" s="0" t="inlineStr">
@@ -11194,17 +11179,17 @@
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608126193240482</t>
+          <t>4500000376202608121856487760</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="0">
-        <v>49155365</v>
+        <v>49155389</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>秀</t>
+          <t>奥普郭彦丽13937990394</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -11229,7 +11214,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:41</t>
+          <t>2026-08-12 21:35:44</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -11259,17 +11244,17 @@
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608121090433848</t>
+          <t>4500000324202608124582542642</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="0">
-        <v>49155364</v>
+        <v>49155374</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>冯衣制版18966913385</t>
+          <t>流星雨文华</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -11294,7 +11279,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:09</t>
+          <t>2026-08-12 21:35:26</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -11324,17 +11309,17 @@
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608122728123344</t>
+          <t>4500000377202608121430434820</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="0">
-        <v>49155363</v>
+        <v>49155368</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>笑对人生</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -11359,7 +11344,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:54</t>
+          <t>2026-08-12 21:34:56</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -11389,17 +11374,17 @@
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608128317430099</t>
+          <t>4500000316202608126193240482</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="0">
-        <v>49155361</v>
+        <v>49155365</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>春华秋实</t>
+          <t>秀</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -11424,7 +11409,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:48</t>
+          <t>2026-08-12 21:34:41</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -11454,17 +11439,17 @@
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608121174096033</t>
+          <t>4500000363202608121090433848</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="0">
-        <v>49155359</v>
+        <v>49155364</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>春梅。</t>
+          <t>冯衣制版18966913385</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -11489,7 +11474,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:36</t>
+          <t>2026-08-12 21:35:09</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -11519,17 +11504,17 @@
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608123637081551</t>
+          <t>4500000348202608122728123344</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="0">
-        <v>49155344</v>
+        <v>49155363</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>自由人生</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -11554,7 +11539,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:25</t>
+          <t>2026-08-12 21:34:54</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -11584,17 +11569,17 @@
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608129865186226</t>
+          <t>4500000320202608128317430099</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="0">
-        <v>49155337</v>
+        <v>49155361</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>红红</t>
+          <t>春华秋实</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -11619,7 +11604,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:50</t>
+          <t>2026-08-12 21:34:48</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -11649,17 +11634,17 @@
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608125530964720</t>
+          <t>4500000346202608121174096033</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="0">
-        <v>49155330</v>
+        <v>49155359</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>徐淑香</t>
+          <t>春梅。</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -11684,7 +11669,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:20</t>
+          <t>2026-08-12 21:34:36</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -11714,17 +11699,17 @@
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608124983971576</t>
+          <t>4500000374202608123637081551</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="0">
-        <v>49155314</v>
+        <v>49155344</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>H叶</t>
+          <t>自由人生</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -11749,7 +11734,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:57</t>
+          <t>2026-08-12 21:34:25</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -11779,17 +11764,17 @@
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608128162955185</t>
+          <t>4500000317202608129865186226</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="0">
-        <v>49155309</v>
+        <v>49155337</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>A0000刘氏修脚红姐</t>
+          <t>红红</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
@@ -11814,7 +11799,7 @@
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:47</t>
+          <t>2026-08-12 21:34:50</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -11844,17 +11829,17 @@
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127176361921</t>
+          <t>4500000327202608125530964720</t>
         </is>
       </c>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="0">
-        <v>49155304</v>
+        <v>49155330</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>万树红</t>
+          <t>徐淑香</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
@@ -11879,7 +11864,7 @@
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:52</t>
+          <t>2026-08-12 21:34:20</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -11909,17 +11894,17 @@
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608123430987084</t>
+          <t>4500000359202608124983971576</t>
         </is>
       </c>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="0">
-        <v>49155293</v>
+        <v>49155314</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>往事如烟</t>
+          <t>H叶</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
@@ -11944,7 +11929,7 @@
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:33</t>
+          <t>2026-08-12 21:33:57</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -11974,17 +11959,17 @@
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608121388094535</t>
+          <t>4500000322202608128162955185</t>
         </is>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="0">
-        <v>49155283</v>
+        <v>49155309</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>雪洁</t>
+          <t>A0000刘氏修脚红姐</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
@@ -12009,7 +11994,7 @@
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:27</t>
+          <t>2026-08-12 21:33:47</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -12039,17 +12024,17 @@
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608125072492429</t>
+          <t>4500000333202608127176361921</t>
         </is>
       </c>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="0">
-        <v>49155274</v>
+        <v>49155304</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>文英</t>
+          <t>万树红</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
@@ -12074,7 +12059,7 @@
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:24</t>
+          <t>2026-08-12 21:33:52</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
@@ -12104,17 +12089,17 @@
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608127495955817</t>
+          <t>4500000379202608123430987084</t>
         </is>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="0">
-        <v>49155273</v>
+        <v>49155293</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>宫本江</t>
+          <t>往事如烟</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
@@ -12139,7 +12124,7 @@
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:33</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
@@ -12169,17 +12154,17 @@
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608122111396208</t>
+          <t>4500000360202608121388094535</t>
         </is>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="0">
-        <v>49155272</v>
+        <v>49155283</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>悠闲的人</t>
+          <t>雪洁</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
@@ -12204,7 +12189,7 @@
       </c>
       <c r="G187" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:13</t>
+          <t>2026-08-12 21:33:27</t>
         </is>
       </c>
       <c r="H187" s="0" t="inlineStr">
@@ -12234,17 +12219,17 @@
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608122303219210</t>
+          <t>4500000369202608125072492429</t>
         </is>
       </c>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="0">
-        <v>49155271</v>
+        <v>49155274</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>幸福人生</t>
+          <t>文英</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
@@ -12269,7 +12254,7 @@
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:08</t>
+          <t>2026-08-12 21:33:24</t>
         </is>
       </c>
       <c r="H188" s="0" t="inlineStr">
@@ -12299,17 +12284,17 @@
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608124799146350</t>
+          <t>4500000373202608127495955817</t>
         </is>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="0">
-        <v>49155270</v>
+        <v>49155273</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>雾里看花</t>
+          <t>宫本江</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
@@ -12334,7 +12319,7 @@
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:15</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H189" s="0" t="inlineStr">
@@ -12364,17 +12349,17 @@
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608123995555310</t>
+          <t>4500000346202608122111396208</t>
         </is>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="0">
-        <v>49155266</v>
+        <v>49155272</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>清风绕指柔</t>
+          <t>悠闲的人</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
@@ -12399,7 +12384,7 @@
       </c>
       <c r="G190" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:31</t>
+          <t>2026-08-12 21:33:13</t>
         </is>
       </c>
       <c r="H190" s="0" t="inlineStr">
@@ -12429,17 +12414,17 @@
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127946689166</t>
+          <t>4500000331202608122303219210</t>
         </is>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="0">
-        <v>49155265</v>
+        <v>49155271</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>心想事成南无阿弥陀佛</t>
+          <t>幸福人生</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
@@ -12464,7 +12449,7 @@
       </c>
       <c r="G191" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:42</t>
+          <t>2026-08-12 21:34:08</t>
         </is>
       </c>
       <c r="H191" s="0" t="inlineStr">
@@ -12494,17 +12479,17 @@
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608126996164764</t>
+          <t>4500000333202608124799146350</t>
         </is>
       </c>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="0">
-        <v>49155264</v>
+        <v>49155270</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>刘凤辉</t>
+          <t>雾里看花</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
@@ -12529,7 +12514,7 @@
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:15</t>
         </is>
       </c>
       <c r="H192" s="0" t="inlineStr">
@@ -12559,17 +12544,17 @@
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608124680304775</t>
+          <t>4500000331202608123995555310</t>
         </is>
       </c>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="0">
-        <v>49155263</v>
+        <v>49155266</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>朱叶</t>
+          <t>清风绕指柔</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
@@ -12594,7 +12579,7 @@
       </c>
       <c r="G193" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:18</t>
+          <t>2026-08-12 21:33:31</t>
         </is>
       </c>
       <c r="H193" s="0" t="inlineStr">
@@ -12624,17 +12609,17 @@
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608124445297817</t>
+          <t>4500000333202608127946689166</t>
         </is>
       </c>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="0">
-        <v>49155253</v>
+        <v>49155265</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>一顺百顺。好运来</t>
+          <t>心想事成南无阿弥陀佛</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
@@ -12659,7 +12644,7 @@
       </c>
       <c r="G194" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:51</t>
+          <t>2026-08-12 21:33:42</t>
         </is>
       </c>
       <c r="H194" s="0" t="inlineStr">
@@ -12689,17 +12674,17 @@
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608122909608257</t>
+          <t>4500000330202608126996164764</t>
         </is>
       </c>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="0">
-        <v>49155246</v>
+        <v>49155264</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>陈桂芳</t>
+          <t>刘凤辉</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
@@ -12724,7 +12709,7 @@
       </c>
       <c r="G195" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H195" s="0" t="inlineStr">
@@ -12754,17 +12739,17 @@
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608126828589764</t>
+          <t>4500000330202608124680304775</t>
         </is>
       </c>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="0">
-        <v>49155234</v>
+        <v>49155263</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>黄仲芬15683592716</t>
+          <t>朱叶</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
@@ -12789,7 +12774,7 @@
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:18</t>
         </is>
       </c>
       <c r="H196" s="0" t="inlineStr">
@@ -12819,17 +12804,17 @@
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608129237945248</t>
+          <t>4500000345202608124445297817</t>
         </is>
       </c>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="0">
-        <v>49155233</v>
+        <v>49155253</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>幸福姐赵会玲</t>
+          <t>一顺百顺。好运来</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
@@ -12854,7 +12839,7 @@
       </c>
       <c r="G197" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:04</t>
+          <t>2026-08-12 21:33:51</t>
         </is>
       </c>
       <c r="H197" s="0" t="inlineStr">
@@ -12884,17 +12869,17 @@
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608128379976752</t>
+          <t>4500000326202608122909608257</t>
         </is>
       </c>
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="0">
-        <v>49155230</v>
+        <v>49155246</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>锦鲤果果</t>
+          <t>陈桂芳</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
@@ -12919,7 +12904,7 @@
       </c>
       <c r="G198" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:20</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H198" s="0" t="inlineStr">
@@ -12949,17 +12934,17 @@
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608129199323858</t>
+          <t>4500000378202608126828589764</t>
         </is>
       </c>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="0">
-        <v>49155226</v>
+        <v>49155234</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>戎戎</t>
+          <t>黄仲芬15683592716</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
@@ -12984,7 +12969,7 @@
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:05</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H199" s="0" t="inlineStr">
@@ -13014,17 +12999,17 @@
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608125827170254</t>
+          <t>4500000325202608129237945248</t>
         </is>
       </c>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="0">
-        <v>49155220</v>
+        <v>49155233</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>阿玉</t>
+          <t>幸福姐赵会玲</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
@@ -13049,7 +13034,7 @@
       </c>
       <c r="G200" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:34:04</t>
         </is>
       </c>
       <c r="H200" s="0" t="inlineStr">
@@ -13079,17 +13064,17 @@
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608129272259118</t>
+          <t>4500000317202608128379976752</t>
         </is>
       </c>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="0">
-        <v>49155219</v>
+        <v>49155230</v>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>沉淀、</t>
+          <t>锦鲤果果</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
@@ -13114,7 +13099,7 @@
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:20</t>
         </is>
       </c>
       <c r="H201" s="0" t="inlineStr">
@@ -13144,17 +13129,17 @@
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>
-          <t>4500000372202608124305947387</t>
+          <t>4500000322202608129199323858</t>
         </is>
       </c>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="0">
-        <v>49155216</v>
+        <v>49155226</v>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>晴天</t>
+          <t>戎戎</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
@@ -13179,7 +13164,7 @@
       </c>
       <c r="G202" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:33:05</t>
         </is>
       </c>
       <c r="H202" s="0" t="inlineStr">
@@ -13209,17 +13194,17 @@
       </c>
       <c r="M202" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608122833385690</t>
+          <t>4500000331202608125827170254</t>
         </is>
       </c>
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="0">
-        <v>49155210</v>
+        <v>49155220</v>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>开正商行</t>
+          <t>阿玉</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
@@ -13244,7 +13229,7 @@
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H203" s="0" t="inlineStr">
@@ -13274,17 +13259,17 @@
       </c>
       <c r="M203" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608127466098812</t>
+          <t>4500000345202608129272259118</t>
         </is>
       </c>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="0">
-        <v>49155208</v>
+        <v>49155219</v>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>傻傻的幸福</t>
+          <t>沉淀、</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
@@ -13309,7 +13294,7 @@
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H204" s="0" t="inlineStr">
@@ -13339,17 +13324,17 @@
       </c>
       <c r="M204" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608122593720010</t>
+          <t>4500000372202608124305947387</t>
         </is>
       </c>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="0">
-        <v>49155205</v>
+        <v>49155216</v>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>你好</t>
+          <t>晴天</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
@@ -13374,7 +13359,7 @@
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H205" s="0" t="inlineStr">
@@ -13404,17 +13389,17 @@
       </c>
       <c r="M205" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608122478222937</t>
+          <t>4500000334202608122833385690</t>
         </is>
       </c>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="0">
-        <v>49155203</v>
+        <v>49155210</v>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>一生有你</t>
+          <t>开正商行</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
@@ -13439,7 +13424,7 @@
       </c>
       <c r="G206" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H206" s="0" t="inlineStr">
@@ -13469,17 +13454,17 @@
       </c>
       <c r="M206" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608129324316511</t>
+          <t>4500000348202608127466098812</t>
         </is>
       </c>
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="0">
-        <v>49155200</v>
+        <v>49155208</v>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>傻傻的幸福</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
@@ -13504,7 +13489,7 @@
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:09</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H207" s="0" t="inlineStr">
@@ -13534,17 +13519,17 @@
       </c>
       <c r="M207" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608125850014769</t>
+          <t>4500000378202608122593720010</t>
         </is>
       </c>
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="0">
-        <v>49155197</v>
+        <v>49155205</v>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>桂芝改名叫张淑玮</t>
+          <t>你好</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
@@ -13569,7 +13554,7 @@
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H208" s="0" t="inlineStr">
@@ -13599,17 +13584,17 @@
       </c>
       <c r="M208" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608121228274851</t>
+          <t>4500000335202608122478222937</t>
         </is>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="A209" s="0">
-        <v>49155194</v>
+        <v>49155203</v>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>自强不息</t>
+          <t>一生有你</t>
         </is>
       </c>
       <c r="C209" s="0" t="inlineStr">
@@ -13634,7 +13619,7 @@
       </c>
       <c r="G209" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H209" s="0" t="inlineStr">
@@ -13664,17 +13649,17 @@
       </c>
       <c r="M209" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608124140031616</t>
+          <t>4500000369202608129324316511</t>
         </is>
       </c>
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="0">
-        <v>49155192</v>
+        <v>49155200</v>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>时光如水</t>
+          <t>618</t>
         </is>
       </c>
       <c r="C210" s="0" t="inlineStr">
@@ -13699,7 +13684,7 @@
       </c>
       <c r="G210" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:03</t>
+          <t>2026-08-12 21:33:09</t>
         </is>
       </c>
       <c r="H210" s="0" t="inlineStr">
@@ -13729,17 +13714,17 @@
       </c>
       <c r="M210" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608128865933230</t>
+          <t>4500000384202608125850014769</t>
         </is>
       </c>
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="0">
-        <v>49155187</v>
+        <v>49155197</v>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>桂芝改名叫张淑玮</t>
         </is>
       </c>
       <c r="C211" s="0" t="inlineStr">
@@ -13764,7 +13749,7 @@
       </c>
       <c r="G211" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H211" s="0" t="inlineStr">
@@ -13794,17 +13779,17 @@
       </c>
       <c r="M211" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608125275144248</t>
+          <t>4500000351202608121228274851</t>
         </is>
       </c>
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="0">
-        <v>49155186</v>
+        <v>49155194</v>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>星辰</t>
+          <t>自强不息</t>
         </is>
       </c>
       <c r="C212" s="0" t="inlineStr">
@@ -13829,7 +13814,7 @@
       </c>
       <c r="G212" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H212" s="0" t="inlineStr">
@@ -13859,17 +13844,17 @@
       </c>
       <c r="M212" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608121378976306</t>
+          <t>4500000356202608124140031616</t>
         </is>
       </c>
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="0">
-        <v>49155185</v>
+        <v>49155192</v>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>天津温室大棚光伏厂家18920981728</t>
+          <t>时光如水</t>
         </is>
       </c>
       <c r="C213" s="0" t="inlineStr">
@@ -13894,7 +13879,7 @@
       </c>
       <c r="G213" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:32</t>
+          <t>2026-08-12 21:33:03</t>
         </is>
       </c>
       <c r="H213" s="0" t="inlineStr">
@@ -13924,17 +13909,17 @@
       </c>
       <c r="M213" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608125631581660</t>
+          <t>4500000364202608128865933230</t>
         </is>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="0">
-        <v>49155184</v>
+        <v>49155187</v>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>惠民</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="C214" s="0" t="inlineStr">
@@ -13959,7 +13944,7 @@
       </c>
       <c r="G214" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:08</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H214" s="0" t="inlineStr">
@@ -13989,17 +13974,17 @@
       </c>
       <c r="M214" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608121279528970</t>
+          <t>4500000334202608125275144248</t>
         </is>
       </c>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="0">
-        <v>49155180</v>
+        <v>49155186</v>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>常青树</t>
+          <t>星辰</t>
         </is>
       </c>
       <c r="C215" s="0" t="inlineStr">
@@ -14024,7 +14009,7 @@
       </c>
       <c r="G215" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:06</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H215" s="0" t="inlineStr">
@@ -14054,17 +14039,17 @@
       </c>
       <c r="M215" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125426925788</t>
+          <t>4500000373202608121378976306</t>
         </is>
       </c>
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="0">
-        <v>49155178</v>
+        <v>49155185</v>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>玉伟</t>
+          <t>天津温室大棚光伏厂家18920981728</t>
         </is>
       </c>
       <c r="C216" s="0" t="inlineStr">
@@ -14089,7 +14074,7 @@
       </c>
       <c r="G216" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:33:32</t>
         </is>
       </c>
       <c r="H216" s="0" t="inlineStr">
@@ -14119,17 +14104,17 @@
       </c>
       <c r="M216" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608125205677586</t>
+          <t>4500000318202608125631581660</t>
         </is>
       </c>
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="0">
-        <v>49155171</v>
+        <v>49155184</v>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>秦晓娟～中医五官排毒</t>
+          <t>惠民</t>
         </is>
       </c>
       <c r="C217" s="0" t="inlineStr">
@@ -14154,7 +14139,7 @@
       </c>
       <c r="G217" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:08</t>
         </is>
       </c>
       <c r="H217" s="0" t="inlineStr">
@@ -14184,17 +14169,17 @@
       </c>
       <c r="M217" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608129265074581</t>
+          <t>4500000355202608121279528970</t>
         </is>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="A218" s="0">
-        <v>49155167</v>
+        <v>49155180</v>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>水琴</t>
+          <t>常青树</t>
         </is>
       </c>
       <c r="C218" s="0" t="inlineStr">
@@ -14219,7 +14204,7 @@
       </c>
       <c r="G218" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:06</t>
         </is>
       </c>
       <c r="H218" s="0" t="inlineStr">
@@ -14249,17 +14234,17 @@
       </c>
       <c r="M218" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608128554791016</t>
+          <t>4500000357202608125426925788</t>
         </is>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="A219" s="0">
-        <v>49155163</v>
+        <v>49155178</v>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>祥云ಠ_ಠ</t>
+          <t>玉伟</t>
         </is>
       </c>
       <c r="C219" s="0" t="inlineStr">
@@ -14284,7 +14269,7 @@
       </c>
       <c r="G219" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H219" s="0" t="inlineStr">
@@ -14314,17 +14299,17 @@
       </c>
       <c r="M219" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608126804876906</t>
+          <t>4500000364202608125205677586</t>
         </is>
       </c>
     </row>
     <row r="220" spans="1:14">
       <c r="A220" s="0">
-        <v>49155162</v>
+        <v>49155171</v>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>雪绒花</t>
+          <t>秦晓娟～中医五官排毒</t>
         </is>
       </c>
       <c r="C220" s="0" t="inlineStr">
@@ -14349,7 +14334,7 @@
       </c>
       <c r="G220" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H220" s="0" t="inlineStr">
@@ -14379,17 +14364,17 @@
       </c>
       <c r="M220" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608122943306781</t>
+          <t>4500000365202608129265074581</t>
         </is>
       </c>
     </row>
     <row r="221" spans="1:14">
       <c r="A221" s="0">
-        <v>49155161</v>
+        <v>49155167</v>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>        糖果</t>
+          <t>水琴</t>
         </is>
       </c>
       <c r="C221" s="0" t="inlineStr">
@@ -14414,7 +14399,7 @@
       </c>
       <c r="G221" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H221" s="0" t="inlineStr">
@@ -14444,17 +14429,17 @@
       </c>
       <c r="M221" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608121712400624</t>
+          <t>4500000315202608128554791016</t>
         </is>
       </c>
     </row>
     <row r="222" spans="1:14">
       <c r="A222" s="0">
-        <v>49155157</v>
+        <v>49155163</v>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>流失的岁月</t>
+          <t>祥云ಠ_ಠ</t>
         </is>
       </c>
       <c r="C222" s="0" t="inlineStr">
@@ -14479,7 +14464,7 @@
       </c>
       <c r="G222" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:11</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H222" s="0" t="inlineStr">
@@ -14509,17 +14494,17 @@
       </c>
       <c r="M222" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608126379751055</t>
+          <t>4500000344202608126804876906</t>
         </is>
       </c>
     </row>
     <row r="223" spans="1:14">
       <c r="A223" s="0">
-        <v>49155152</v>
+        <v>49155162</v>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>夏末幽荷</t>
+          <t>雪绒花</t>
         </is>
       </c>
       <c r="C223" s="0" t="inlineStr">
@@ -14544,7 +14529,7 @@
       </c>
       <c r="G223" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H223" s="0" t="inlineStr">
@@ -14574,17 +14559,17 @@
       </c>
       <c r="M223" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608128669470764</t>
+          <t>4500000343202608122943306781</t>
         </is>
       </c>
     </row>
     <row r="224" spans="1:14">
       <c r="A224" s="0">
-        <v>49155150</v>
+        <v>49155161</v>
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
-          <t>药曼</t>
+          <t>        糖果</t>
         </is>
       </c>
       <c r="C224" s="0" t="inlineStr">
@@ -14609,7 +14594,7 @@
       </c>
       <c r="G224" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H224" s="0" t="inlineStr">
@@ -14639,17 +14624,17 @@
       </c>
       <c r="M224" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608127294126669</t>
+          <t>4500000384202608121712400624</t>
         </is>
       </c>
     </row>
     <row r="225" spans="1:14">
       <c r="A225" s="0">
-        <v>49155149</v>
+        <v>49155157</v>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>🌺 谭谭🌺</t>
+          <t>流失的岁月</t>
         </is>
       </c>
       <c r="C225" s="0" t="inlineStr">
@@ -14674,7 +14659,7 @@
       </c>
       <c r="G225" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:58</t>
+          <t>2026-08-12 21:33:11</t>
         </is>
       </c>
       <c r="H225" s="0" t="inlineStr">
@@ -14704,17 +14689,17 @@
       </c>
       <c r="M225" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608121029117778</t>
+          <t>4500000379202608126379751055</t>
         </is>
       </c>
     </row>
     <row r="226" spans="1:14">
       <c r="A226" s="0">
-        <v>49155148</v>
+        <v>49155152</v>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>王玉(邮局对面卖手机)</t>
+          <t>夏末幽荷</t>
         </is>
       </c>
       <c r="C226" s="0" t="inlineStr">
@@ -14769,17 +14754,17 @@
       </c>
       <c r="M226" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608126218721690</t>
+          <t>4500000337202608128669470764</t>
         </is>
       </c>
     </row>
     <row r="227" spans="1:14">
       <c r="A227" s="0">
-        <v>49155147</v>
+        <v>49155150</v>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>美好夕阳</t>
+          <t>药曼</t>
         </is>
       </c>
       <c r="C227" s="0" t="inlineStr">
@@ -14834,17 +14819,17 @@
       </c>
       <c r="M227" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608128224202725</t>
+          <t>4500000345202608127294126669</t>
         </is>
       </c>
     </row>
     <row r="228" spans="1:14">
       <c r="A228" s="0">
-        <v>49155145</v>
+        <v>49155149</v>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>平凡</t>
+          <t>🌺 谭谭🌺</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
@@ -14869,7 +14854,7 @@
       </c>
       <c r="G228" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:32:58</t>
         </is>
       </c>
       <c r="H228" s="0" t="inlineStr">
@@ -14899,17 +14884,17 @@
       </c>
       <c r="M228" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608122476247171</t>
+          <t>4500000350202608121029117778</t>
         </is>
       </c>
     </row>
     <row r="229" spans="1:14">
       <c r="A229" s="0">
-        <v>49155143</v>
+        <v>49155148</v>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>唐洪</t>
+          <t>王玉(邮局对面卖手机)</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
@@ -14934,7 +14919,7 @@
       </c>
       <c r="G229" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:45</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H229" s="0" t="inlineStr">
@@ -14964,17 +14949,17 @@
       </c>
       <c r="M229" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608125309483592</t>
+          <t>4500000342202608126218721690</t>
         </is>
       </c>
     </row>
     <row r="230" spans="1:14">
       <c r="A230" s="0">
-        <v>49155140</v>
+        <v>49155147</v>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>浅笑</t>
+          <t>美好夕阳</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
@@ -14999,7 +14984,7 @@
       </c>
       <c r="G230" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H230" s="0" t="inlineStr">
@@ -15029,17 +15014,17 @@
       </c>
       <c r="M230" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608123442658613</t>
+          <t>4500000343202608128224202725</t>
         </is>
       </c>
     </row>
     <row r="231" spans="1:14">
       <c r="A231" s="0">
-        <v>49155137</v>
+        <v>49155145</v>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>梅放芳香</t>
+          <t>平凡</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
@@ -15064,7 +15049,7 @@
       </c>
       <c r="G231" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H231" s="0" t="inlineStr">
@@ -15094,17 +15079,17 @@
       </c>
       <c r="M231" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608127843962862</t>
+          <t>4500000359202608122476247171</t>
         </is>
       </c>
     </row>
     <row r="232" spans="1:14">
       <c r="A232" s="0">
-        <v>49155135</v>
+        <v>49155143</v>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>吴素华</t>
+          <t>唐洪</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
@@ -15129,7 +15114,7 @@
       </c>
       <c r="G232" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:45</t>
         </is>
       </c>
       <c r="H232" s="0" t="inlineStr">
@@ -15159,17 +15144,17 @@
       </c>
       <c r="M232" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608124292727044</t>
+          <t>4500000350202608125309483592</t>
         </is>
       </c>
     </row>
     <row r="233" spans="1:14">
       <c r="A233" s="0">
-        <v>49155132</v>
+        <v>49155140</v>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
+          <t>浅笑</t>
         </is>
       </c>
       <c r="C233" s="0" t="inlineStr">
@@ -15194,7 +15179,7 @@
       </c>
       <c r="G233" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H233" s="0" t="inlineStr">
@@ -15224,17 +15209,17 @@
       </c>
       <c r="M233" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608123141162109</t>
+          <t>4500000360202608123442658613</t>
         </is>
       </c>
     </row>
     <row r="234" spans="1:14">
       <c r="A234" s="0">
-        <v>49155131</v>
+        <v>49155137</v>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>瓷星.</t>
+          <t>梅放芳香</t>
         </is>
       </c>
       <c r="C234" s="0" t="inlineStr">
@@ -15259,7 +15244,7 @@
       </c>
       <c r="G234" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H234" s="0" t="inlineStr">
@@ -15289,17 +15274,17 @@
       </c>
       <c r="M234" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608121548709297</t>
+          <t>4500000356202608127843962862</t>
         </is>
       </c>
     </row>
     <row r="235" spans="1:14">
       <c r="A235" s="0">
-        <v>49155129</v>
+        <v>49155135</v>
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
-          <t>妈咪宝贝</t>
+          <t>吴素华</t>
         </is>
       </c>
       <c r="C235" s="0" t="inlineStr">
@@ -15324,7 +15309,7 @@
       </c>
       <c r="G235" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:42</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H235" s="0" t="inlineStr">
@@ -15354,17 +15339,17 @@
       </c>
       <c r="M235" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608127726342481</t>
+          <t>4500000339202608124292727044</t>
         </is>
       </c>
     </row>
     <row r="236" spans="1:14">
       <c r="A236" s="0">
-        <v>49155128</v>
+        <v>49155132</v>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>愿结天下有缘人</t>
+          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
         </is>
       </c>
       <c r="C236" s="0" t="inlineStr">
@@ -15419,17 +15404,17 @@
       </c>
       <c r="M236" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608128699617090</t>
+          <t>4500000322202608123141162109</t>
         </is>
       </c>
     </row>
     <row r="237" spans="1:14">
       <c r="A237" s="0">
-        <v>49155124</v>
+        <v>49155131</v>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>勿忘初心</t>
+          <t>瓷星.</t>
         </is>
       </c>
       <c r="C237" s="0" t="inlineStr">
@@ -15454,7 +15439,7 @@
       </c>
       <c r="G237" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H237" s="0" t="inlineStr">
@@ -15484,17 +15469,17 @@
       </c>
       <c r="M237" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608128217629837</t>
+          <t>4500000383202608121548709297</t>
         </is>
       </c>
     </row>
     <row r="238" spans="1:14">
       <c r="A238" s="0">
-        <v>49155123</v>
+        <v>49155129</v>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>芳草天涯</t>
+          <t>妈咪宝贝</t>
         </is>
       </c>
       <c r="C238" s="0" t="inlineStr">
@@ -15519,7 +15504,7 @@
       </c>
       <c r="G238" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:42</t>
         </is>
       </c>
       <c r="H238" s="0" t="inlineStr">
@@ -15549,22 +15534,17 @@
       </c>
       <c r="M238" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608123653997556</t>
-        </is>
-      </c>
-      <c r="N238" s="0" t="inlineStr">
-        <is>
-          <t>合肥</t>
+          <t>4500000347202608127726342481</t>
         </is>
       </c>
     </row>
     <row r="239" spans="1:14">
       <c r="A239" s="0">
-        <v>49155120</v>
+        <v>49155128</v>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>记忆中的你</t>
+          <t>愿结天下有缘人</t>
         </is>
       </c>
       <c r="C239" s="0" t="inlineStr">
@@ -15589,7 +15569,7 @@
       </c>
       <c r="G239" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:53</t>
+          <t>2026-08-12 21:32:46</t>
         </is>
       </c>
       <c r="H239" s="0" t="inlineStr">
@@ -15619,17 +15599,17 @@
       </c>
       <c r="M239" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608124401684219</t>
+          <t>4500000321202608128699617090</t>
         </is>
       </c>
     </row>
     <row r="240" spans="1:14">
       <c r="A240" s="0">
-        <v>49155114</v>
+        <v>49155124</v>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>微笑取暖</t>
+          <t>勿忘初心</t>
         </is>
       </c>
       <c r="C240" s="0" t="inlineStr">
@@ -15654,7 +15634,7 @@
       </c>
       <c r="G240" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:38</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H240" s="0" t="inlineStr">
@@ -15684,17 +15664,17 @@
       </c>
       <c r="M240" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608121874803628</t>
+          <t>4500000373202608128217629837</t>
         </is>
       </c>
     </row>
     <row r="241" spans="1:14">
       <c r="A241" s="0">
-        <v>49155112</v>
+        <v>49155123</v>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>净心李芸</t>
+          <t>芳草天涯</t>
         </is>
       </c>
       <c r="C241" s="0" t="inlineStr">
@@ -15719,7 +15699,7 @@
       </c>
       <c r="G241" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:33</t>
+          <t>2026-08-12 21:32:32</t>
         </is>
       </c>
       <c r="H241" s="0" t="inlineStr">
@@ -15749,17 +15729,22 @@
       </c>
       <c r="M241" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608126115898528</t>
+          <t>4500000321202608123653997556</t>
+        </is>
+      </c>
+      <c r="N241" s="0" t="inlineStr">
+        <is>
+          <t>合肥</t>
         </is>
       </c>
     </row>
     <row r="242" spans="1:14">
       <c r="A242" s="0">
-        <v>49155108</v>
+        <v>49155120</v>
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
-          <t>衡澜</t>
+          <t>记忆中的你</t>
         </is>
       </c>
       <c r="C242" s="0" t="inlineStr">
@@ -15784,7 +15769,7 @@
       </c>
       <c r="G242" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:53</t>
         </is>
       </c>
       <c r="H242" s="0" t="inlineStr">
@@ -15814,17 +15799,17 @@
       </c>
       <c r="M242" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608128833814214</t>
+          <t>4500000326202608124401684219</t>
         </is>
       </c>
     </row>
     <row r="243" spans="1:14">
       <c r="A243" s="0">
-        <v>49155098</v>
+        <v>49155114</v>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>珂</t>
+          <t>微笑取暖</t>
         </is>
       </c>
       <c r="C243" s="0" t="inlineStr">
@@ -15849,7 +15834,7 @@
       </c>
       <c r="G243" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:39</t>
+          <t>2026-08-12 21:33:38</t>
         </is>
       </c>
       <c r="H243" s="0" t="inlineStr">
@@ -15879,17 +15864,17 @@
       </c>
       <c r="M243" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608128766183266</t>
+          <t>4500000325202608121874803628</t>
         </is>
       </c>
     </row>
     <row r="244" spans="1:14">
       <c r="A244" s="0">
-        <v>49155095</v>
+        <v>49155112</v>
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
-          <t>平安保险~王家宝</t>
+          <t>净心李芸</t>
         </is>
       </c>
       <c r="C244" s="0" t="inlineStr">
@@ -15914,7 +15899,7 @@
       </c>
       <c r="G244" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:32:33</t>
         </is>
       </c>
       <c r="H244" s="0" t="inlineStr">
@@ -15944,17 +15929,17 @@
       </c>
       <c r="M244" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608129139460754</t>
+          <t>4500000351202608126115898528</t>
         </is>
       </c>
     </row>
     <row r="245" spans="1:14">
       <c r="A245" s="0">
-        <v>49155092</v>
+        <v>49155108</v>
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
-          <t>爱情海</t>
+          <t>衡澜</t>
         </is>
       </c>
       <c r="C245" s="0" t="inlineStr">
@@ -15979,7 +15964,7 @@
       </c>
       <c r="G245" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:23</t>
+          <t>2026-08-12 21:32:32</t>
         </is>
       </c>
       <c r="H245" s="0" t="inlineStr">
@@ -16009,17 +15994,17 @@
       </c>
       <c r="M245" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125918396999</t>
+          <t>4500000360202608128833814214</t>
         </is>
       </c>
     </row>
     <row r="246" spans="1:14">
       <c r="A246" s="0">
-        <v>49155090</v>
+        <v>49155098</v>
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
-          <t>三月桃花</t>
+          <t>珂</t>
         </is>
       </c>
       <c r="C246" s="0" t="inlineStr">
@@ -16044,7 +16029,7 @@
       </c>
       <c r="G246" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:26</t>
+          <t>2026-08-12 21:32:39</t>
         </is>
       </c>
       <c r="H246" s="0" t="inlineStr">
@@ -16074,70 +16059,265 @@
       </c>
       <c r="M246" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608128744277768</t>
+          <t>4500000344202608128766183266</t>
         </is>
       </c>
     </row>
     <row r="247" spans="1:14">
       <c r="A247" s="0">
+        <v>49155095</v>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t>平安保险~王家宝</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F247" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G247" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:54</t>
+        </is>
+      </c>
+      <c r="H247" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J247" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K247" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L247" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M247" s="0" t="inlineStr">
+        <is>
+          <t>4500000321202608129139460754</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" spans="1:14">
+      <c r="A248" s="0">
+        <v>49155092</v>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>爱情海</t>
+        </is>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E248" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F248" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G248" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:23</t>
+        </is>
+      </c>
+      <c r="H248" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J248" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K248" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L248" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M248" s="0" t="inlineStr">
+        <is>
+          <t>4500000357202608125918396999</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" spans="1:14">
+      <c r="A249" s="0">
+        <v>49155090</v>
+      </c>
+      <c r="B249" s="0" t="inlineStr">
+        <is>
+          <t>三月桃花</t>
+        </is>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D249" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E249" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F249" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G249" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:26</t>
+        </is>
+      </c>
+      <c r="H249" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J249" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K249" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L249" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M249" s="0" t="inlineStr">
+        <is>
+          <t>4500000382202608128744277768</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" spans="1:14">
+      <c r="A250" s="0">
         <v>49155088</v>
       </c>
-      <c r="B247" s="0" t="inlineStr">
+      <c r="B250" s="0" t="inlineStr">
         <is>
           <t>绘兰艺术李老师</t>
         </is>
       </c>
-      <c r="C247" s="0" t="inlineStr">
-        <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
-        </is>
-      </c>
-      <c r="D247" s="0" t="inlineStr">
-        <is>
-          <t>训练营</t>
-        </is>
-      </c>
-      <c r="E247" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="F247" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="G247" s="0" t="inlineStr">
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D250" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E250" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F250" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G250" s="0" t="inlineStr">
         <is>
           <t>2026-08-12 21:32:20</t>
         </is>
       </c>
-      <c r="H247" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I247" s="0" t="inlineStr">
-        <is>
-          <t>彩虹-抖音1元瑜伽</t>
-        </is>
-      </c>
-      <c r="J247" s="0" t="inlineStr">
-        <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
-        </is>
-      </c>
-      <c r="K247" s="0" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="L247" s="0" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M247" s="0" t="inlineStr">
+      <c r="H250" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J250" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K250" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L250" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M250" s="0" t="inlineStr">
         <is>
           <t>4500000358202608128940402527</t>
         </is>
